--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="1yG/eLgU41PGmotHI2ElPk+sJpWFlJirXKy51IoTgJA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="qG4wC4nVVHGvzzWMC3Ah1xFPXdV+uqPdFbqYEsVd6+8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="206">
   <si>
     <t>nombre</t>
   </si>
@@ -115,6 +115,9 @@
     <t>chicago dorado meta.jpg</t>
   </si>
   <si>
+    <t>chicago dorado meta 2.jpg</t>
+  </si>
+  <si>
     <t>Chicago Crochet Blanco Perla</t>
   </si>
   <si>
@@ -172,12 +175,12 @@
     <t>Kioto Negro</t>
   </si>
   <si>
+    <t>kioto negro puesto 1.jpg</t>
+  </si>
+  <si>
     <t>kioto negro fb.jpg</t>
   </si>
   <si>
-    <t>kioto negro puesto 1.jpg</t>
-  </si>
-  <si>
     <t>Kioto Morado</t>
   </si>
   <si>
@@ -226,12 +229,12 @@
     <t>San Francisco Cotton Camel</t>
   </si>
   <si>
+    <t>sf camel 2.jpg</t>
+  </si>
+  <si>
     <t>sf cotton camel.jpg</t>
   </si>
   <si>
-    <t>sf camel 2.jpg</t>
-  </si>
-  <si>
     <t>San Francisco Cotton Vainilla</t>
   </si>
   <si>
@@ -313,15 +316,15 @@
     <t>Mini Madrid Cotton Verde</t>
   </si>
   <si>
+    <t>mini madrid verde 3.jpg</t>
+  </si>
+  <si>
+    <t>mini madrid verde.jpg</t>
+  </si>
+  <si>
     <t>mini madrid verde fb.jpg</t>
   </si>
   <si>
-    <t>mini madrid verde.jpg</t>
-  </si>
-  <si>
-    <t>mini madrid verde 3.jpg</t>
-  </si>
-  <si>
     <t>Mini Madrid Cotton Fucsia</t>
   </si>
   <si>
@@ -349,12 +352,12 @@
     <t>Madrid Cotton Chocolate</t>
   </si>
   <si>
+    <t>madrid chocolate 2.jpg</t>
+  </si>
+  <si>
     <t>madrid chocolate fb.jpg</t>
   </si>
   <si>
-    <t>madrid chocolate 2.jpg</t>
-  </si>
-  <si>
     <t>Huesca Cotton Chocolate</t>
   </si>
   <si>
@@ -602,6 +605,21 @@
   </si>
   <si>
     <t>Choker beige.jpg</t>
+  </si>
+  <si>
+    <t>Choker Flor</t>
+  </si>
+  <si>
+    <t>Flor</t>
+  </si>
+  <si>
+    <t>choker flor.jpg</t>
+  </si>
+  <si>
+    <t>choker flor 2.jpg</t>
+  </si>
+  <si>
+    <t>choker flor 3.jpg</t>
   </si>
   <si>
     <t>Conjunto Paris y Milan</t>
@@ -661,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -670,6 +688,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -783,7 +804,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I47" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I48" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -800,7 +821,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I73" displayName="Table_10" name="Table_10" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:I75" displayName="Table_10" name="Table_10" id="10">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -826,7 +847,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C18" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C19" displayName="Table_12" name="Table_12" id="12">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -835,7 +856,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A48:I48" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A49:I49" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -852,7 +873,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A49:I49" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A50:I50" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -869,7 +890,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A50:I50" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A51:I51" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -886,7 +907,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A51:I59" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A52:I60" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -903,7 +924,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A60:I60" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A61:I61" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -920,7 +941,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A61:I61" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I62" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -937,7 +958,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I68" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I69" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -954,7 +975,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I69" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I70" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1369,7 +1390,7 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
@@ -1378,10 +1399,10 @@
         <v>11</v>
       </c>
       <c r="D9" s="3">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1389,360 +1410,359 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D11" s="3">
         <v>30.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>34</v>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D12" s="3">
         <v>30.0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>34</v>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>34</v>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" ht="15.0" customHeight="1">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3">
         <v>30.0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3">
         <v>30.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" s="2"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F18" s="2"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3">
         <v>25.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F19" s="2"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="F20" s="2"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F21" s="2"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3">
         <v>25.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F22" s="2"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3">
         <v>25.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3">
         <v>25.0</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="3">
         <v>25.0</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="E25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3">
         <v>25.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="1"/>
@@ -1750,40 +1770,39 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3">
         <v>25.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>76</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1792,19 +1811,19 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -1813,107 +1832,107 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" s="3">
         <v>40.0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D32" s="3">
         <v>25.0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1922,65 +1941,64 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D35" s="3">
         <v>20.0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D36" s="3">
         <v>20.0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="I36" s="1"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D37" s="3">
         <v>20.0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1989,45 +2007,43 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D39" s="3">
         <v>25.0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2035,40 +2051,41 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D40" s="3">
         <v>25.0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+        <v>110</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D41" s="3">
         <v>25.0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2077,19 +2094,19 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D42" s="3">
         <v>25.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2098,19 +2115,19 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D43" s="3">
         <v>25.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2119,19 +2136,19 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D44" s="3">
         <v>25.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2140,84 +2157,84 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D46" s="3">
         <v>30.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D47" s="3">
         <v>30.0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F47" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="F47" s="2"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D48" s="3">
         <v>30.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2226,19 +2243,19 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D49" s="3">
         <v>30.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2247,106 +2264,106 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D50" s="3">
         <v>30.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F50" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D51" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F51" s="1"/>
+      <c r="F51" s="2"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D52" s="3">
         <v>13.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" s="3">
         <v>13.0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D54" s="3">
         <v>13.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2355,40 +2372,40 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D55" s="3">
         <v>13.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F55" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D56" s="3">
         <v>13.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="1"/>
@@ -2397,32 +2414,34 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D57" s="3">
         <v>13.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F57" s="2"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D58" s="3">
         <v>13.0</v>
@@ -2435,32 +2454,32 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D59" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="F59" s="2"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D60" s="3">
         <v>15.0</v>
@@ -2468,39 +2487,39 @@
       <c r="E60" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="F60" s="2"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D61" s="3">
         <v>15.0</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F61" s="2"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D62" s="3">
         <v>15.0</v>
@@ -2513,13 +2532,13 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D63" s="3">
         <v>15.0</v>
@@ -2528,25 +2547,23 @@
         <v>164</v>
       </c>
       <c r="F63" s="2"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D64" s="3">
         <v>15.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="1"/>
@@ -2555,88 +2572,88 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D65" s="3">
         <v>15.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>171</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D66" s="3">
         <v>15.0</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D67" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F67" s="2"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D68" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D68" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="1"/>
@@ -2645,32 +2662,34 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D69" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="F69" s="2"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D70" s="3">
         <v>12.0</v>
@@ -2683,40 +2702,38 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D71" s="3">
         <v>12.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F71" s="2"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D72" s="3">
         <v>12.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="4"/>
@@ -2725,55 +2742,99 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D73" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="F73" s="2"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" ht="14.25" customHeight="1">
+      <c r="A74" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D73" s="3">
+      <c r="B74" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D74" s="3">
         <v>13.0</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="E74" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D75" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H75" s="5"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D74" s="3">
+      <c r="D76" s="3">
         <v>18.0</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="3"/>
-    </row>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
+      <c r="E76" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="3"/>
+    </row>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
     <row r="84" ht="14.25" customHeight="1"/>
@@ -3698,12 +3759,14 @@
     <row r="1003" ht="14.25" customHeight="1"/>
     <row r="1004" ht="14.25" customHeight="1"/>
     <row r="1005" ht="14.25" customHeight="1"/>
+    <row r="1006" ht="14.25" customHeight="1"/>
+    <row r="1007" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C75">
-      <formula1>datos!$C$2:$C$18</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C77">
+      <formula1>datos!$C$2:$C$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B75">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B77">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -3740,7 +3803,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3756,97 +3819,101 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="C19" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
     <row r="20" ht="14.25" customHeight="1"/>
     <row r="21" ht="14.25" customHeight="1"/>
     <row r="22" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="207">
   <si>
     <t>nombre</t>
   </si>
@@ -626,6 +626,9 @@
   </si>
   <si>
     <t>Paris y milan.jpg</t>
+  </si>
+  <si>
+    <t>pendientes rio.jpg</t>
   </si>
   <si>
     <t>tipos</t>
@@ -2834,6 +2837,9 @@
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="3"/>
+      <c r="E77" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
@@ -3803,7 +3809,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3843,7 +3849,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>80</v>
@@ -3851,7 +3857,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -3881,7 +3887,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="206">
   <si>
     <t>nombre</t>
   </si>
@@ -626,9 +626,6 @@
   </si>
   <si>
     <t>Paris y milan.jpg</t>
-  </si>
-  <si>
-    <t>pendientes rio.jpg</t>
   </si>
   <si>
     <t>tipos</t>
@@ -2837,9 +2834,7 @@
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="3"/>
-      <c r="E77" s="4" t="s">
-        <v>202</v>
-      </c>
+      <c r="E77" s="4"/>
     </row>
     <row r="82" ht="14.25" customHeight="1"/>
     <row r="83" ht="14.25" customHeight="1"/>
@@ -3809,7 +3804,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3849,7 +3844,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>80</v>
@@ -3857,7 +3852,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -3887,7 +3882,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="qG4wC4nVVHGvzzWMC3Ah1xFPXdV+uqPdFbqYEsVd6+8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="C9+TJLQA6UVrHgFf5h9dCI+JjKhAMH6EtEwbC7FQrl0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="214">
   <si>
     <t>nombre</t>
   </si>
@@ -211,6 +211,18 @@
     <t>Kioto zebra.jpg</t>
   </si>
   <si>
+    <t>Tenerife Pana</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>tenerife pana.jpg</t>
+  </si>
+  <si>
+    <t>tenerife pana 2.jpg</t>
+  </si>
+  <si>
     <t>San Francisco</t>
   </si>
   <si>
@@ -562,6 +574,12 @@
     <t>cuelgamovil roma largo.jpg</t>
   </si>
   <si>
+    <t>cuelga roma verano.jpg</t>
+  </si>
+  <si>
+    <t>cuelga verano largo.jpg</t>
+  </si>
+  <si>
     <t>Collar Granada</t>
   </si>
   <si>
@@ -587,6 +605,12 @@
   </si>
   <si>
     <t>collar londres marron.jpg</t>
+  </si>
+  <si>
+    <t>Collar Londres Rojo</t>
+  </si>
+  <si>
+    <t>londres rojo.jpg</t>
   </si>
   <si>
     <t>Choker Milán</t>
@@ -804,7 +828,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I48" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I49" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -821,7 +845,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:I75" displayName="Table_10" name="Table_10" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A74:I80" displayName="Table_10" name="Table_10" id="10">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -847,7 +871,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C19" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C20" displayName="Table_12" name="Table_12" id="12">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -856,7 +880,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A49:I49" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A50:I50" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -873,7 +897,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A50:I50" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A51:I51" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -890,7 +914,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A51:I51" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A52:I52" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -907,7 +931,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A52:I60" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A53:I61" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -924,7 +948,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A61:I61" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I62" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -941,7 +965,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I62" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I63" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -958,7 +982,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I69" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I72" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -975,7 +999,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I70" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A73:I73" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1657,7 +1681,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="3">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>62</v>
@@ -1665,7 +1689,7 @@
       <c r="F21" s="2"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
@@ -1673,116 +1697,117 @@
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3">
         <v>25.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F23" s="2"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3">
         <v>25.0</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>69</v>
+      <c r="E24" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="1"/>
+        <v>71</v>
+      </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3">
         <v>25.0</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3">
         <v>25.0</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="E26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D27" s="3">
         <v>25.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
@@ -1790,40 +1815,39 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3">
         <v>25.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="2"/>
+        <v>80</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D29" s="3">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -1832,19 +1856,19 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1853,26 +1877,22 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="D31" s="3">
         <v>40.0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G31" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
@@ -1884,76 +1904,80 @@
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D32" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="1"/>
+      <c r="F32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D33" s="3">
         <v>25.0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D34" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D35" s="3">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1962,26 +1986,23 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D36" s="3">
         <v>20.0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G36" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -1992,7 +2013,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D37" s="3">
         <v>20.0</v>
@@ -2000,26 +2021,29 @@
       <c r="E37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="F37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D38" s="3">
         <v>20.0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2028,23 +2052,21 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D39" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F39" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2057,29 +2079,30 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D40" s="3">
         <v>25.0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>111</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D41" s="3">
         <v>25.0</v>
@@ -2087,26 +2110,27 @@
       <c r="E41" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
+      <c r="F41" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D42" s="3">
         <v>25.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2115,19 +2139,19 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D43" s="3">
         <v>25.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2136,19 +2160,19 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D44" s="3">
         <v>25.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2157,19 +2181,19 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D45" s="3">
         <v>25.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2178,36 +2202,34 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D46" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>126</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D47" s="3">
         <v>30.0</v>
@@ -2215,47 +2237,49 @@
       <c r="E47" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F47" s="2"/>
+      <c r="F47" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D48" s="3">
         <v>30.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F48" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="D49" s="3">
         <v>30.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2264,19 +2288,19 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D50" s="3">
         <v>30.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2285,42 +2309,42 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D51" s="3">
         <v>30.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F51" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>139</v>
+        <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D52" s="3">
-        <v>13.0</v>
+        <v>30.0</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F52" s="1"/>
+      <c r="F52" s="2"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2330,23 +2354,20 @@
         <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D53" s="3">
         <v>13.0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G53" s="2" t="s">
         <v>145</v>
       </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -2354,10 +2375,10 @@
         <v>146</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D54" s="3">
         <v>13.0</v>
@@ -2365,26 +2386,29 @@
       <c r="E54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="F54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D55" s="3">
         <v>13.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2393,40 +2417,40 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D56" s="3">
         <v>13.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F56" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D57" s="3">
         <v>13.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="1"/>
@@ -2435,54 +2459,56 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D58" s="3">
         <v>13.0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F58" s="2"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="3">
         <v>13.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F59" s="2"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D60" s="3">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>160</v>
@@ -2492,99 +2518,97 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D61" s="3">
         <v>15.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F61" s="2"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D62" s="3">
         <v>15.0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F62" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D63" s="3">
         <v>15.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F63" s="2"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D64" s="3">
         <v>15.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F64" s="2"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D65" s="3">
         <v>15.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="1"/>
@@ -2593,88 +2617,88 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D66" s="3">
         <v>15.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F66" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D67" s="3">
         <v>15.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G67" s="1"/>
+        <v>175</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D68" s="3">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F68" s="2"/>
+      <c r="F68" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D69" s="3">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="1"/>
@@ -2683,72 +2707,76 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="D70" s="3">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F70" s="2"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="D71" s="3">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F71" s="2"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D72" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="F72" s="2"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="D73" s="3">
         <v>12.0</v>
@@ -2757,90 +2785,176 @@
         <v>188</v>
       </c>
       <c r="F73" s="2"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D74" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="F74" s="2"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" ht="14.25" customHeight="1">
+      <c r="A75" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D74" s="3">
+      <c r="B75" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D75" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" ht="14.25" customHeight="1">
+      <c r="A76" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" ht="14.25" customHeight="1">
+      <c r="A77" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D77" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" ht="14.25" customHeight="1">
+      <c r="A78" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D78" s="3">
         <v>13.0</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D75" s="3">
+      <c r="E78" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D80" s="3">
         <v>9.0</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F75" s="2" t="s">
+      <c r="E80" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H80" s="5"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H75" s="5"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D76" s="3">
+      <c r="D81" s="3">
         <v>18.0</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="4"/>
-    </row>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
+      <c r="E81" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
+    </row>
     <row r="87" ht="14.25" customHeight="1"/>
     <row r="88" ht="14.25" customHeight="1"/>
     <row r="89" ht="14.25" customHeight="1"/>
@@ -3762,13 +3876,18 @@
     <row r="1005" ht="14.25" customHeight="1"/>
     <row r="1006" ht="14.25" customHeight="1"/>
     <row r="1007" ht="14.25" customHeight="1"/>
+    <row r="1008" ht="14.25" customHeight="1"/>
+    <row r="1009" ht="14.25" customHeight="1"/>
+    <row r="1010" ht="14.25" customHeight="1"/>
+    <row r="1011" ht="14.25" customHeight="1"/>
+    <row r="1012" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C77">
-      <formula1>datos!$C$2:$C$19</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B82">
+      <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B77">
-      <formula1>datos!$A$2:$A$6</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C82">
+      <formula1>datos!$C$2:$C$20</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -3804,7 +3923,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3820,7 +3939,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>35</v>
@@ -3828,94 +3947,98 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="C20" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="21" ht="14.25" customHeight="1"/>
     <row r="22" ht="14.25" customHeight="1"/>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="216">
   <si>
     <t>nombre</t>
   </si>
@@ -629,6 +629,12 @@
   </si>
   <si>
     <t>Choker beige.jpg</t>
+  </si>
+  <si>
+    <t>Choker y Pulsera Milan</t>
+  </si>
+  <si>
+    <t>choker y pulsera.jpg</t>
   </si>
   <si>
     <t>Choker Flor</t>
@@ -2897,11 +2903,21 @@
       <c r="I78" s="1"/>
     </row>
     <row r="79">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="2"/>
+      <c r="A79" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D79" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="5"/>
@@ -2909,32 +2925,32 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D80" s="3">
         <v>9.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="1"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>173</v>
@@ -2946,7 +2962,7 @@
         <v>18.0</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82">
@@ -3923,7 +3939,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3963,7 +3979,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>84</v>
@@ -3971,7 +3987,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -4001,7 +4017,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -4031,7 +4047,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -661,7 +661,7 @@
     <t>tipos</t>
   </si>
   <si>
-    <t>info</t>
+    <t>pendientes</t>
   </si>
   <si>
     <t>Santander</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="C9+TJLQA6UVrHgFf5h9dCI+JjKhAMH6EtEwbC7FQrl0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="k2YKHSllsTZPBZoihDyrBbRFVCqlv09n9KoVgw1eatk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="232">
   <si>
     <t>nombre</t>
   </si>
@@ -448,6 +448,39 @@
     <t>niza velvet mostaza.jpg</t>
   </si>
   <si>
+    <t>Pendientes Río Blanco</t>
+  </si>
+  <si>
+    <t>pendientes</t>
+  </si>
+  <si>
+    <t>Río</t>
+  </si>
+  <si>
+    <t>rio blanco.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>Pendientes Río Verdes</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>Pendientes Río Marrones</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>Pendientes Río Rojo</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
     <t>Paris Gorro Negro</t>
   </si>
   <si>
@@ -538,27 +571,39 @@
     <t>bogota colores.jpg</t>
   </si>
   <si>
+    <t>Collar Bogota Amarillo</t>
+  </si>
+  <si>
+    <t>collar</t>
+  </si>
+  <si>
+    <t>Collar Bogota.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Camel</t>
+  </si>
+  <si>
+    <t>Collar Bogota Camel.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Rojo</t>
+  </si>
+  <si>
+    <t>collar bogota rojo.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Lima</t>
+  </si>
+  <si>
+    <t>Collar Bogota Lima.jpg</t>
+  </si>
+  <si>
     <t>Collar Bogota</t>
   </si>
   <si>
-    <t>collar</t>
-  </si>
-  <si>
-    <t>Collar Bogota.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota Camel.jpg</t>
-  </si>
-  <si>
-    <t>collar bogota rojo.jpg</t>
-  </si>
-  <si>
     <t>Collar Bogota blanco.jpg</t>
   </si>
   <si>
-    <t>Collar Bogota Lima.jpg</t>
-  </si>
-  <si>
     <t>Cuelgamovil Roma</t>
   </si>
   <si>
@@ -580,6 +625,30 @@
     <t>cuelga verano largo.jpg</t>
   </si>
   <si>
+    <t>Conjunto Roma Rosa</t>
+  </si>
+  <si>
+    <t>roma rosa.jpg</t>
+  </si>
+  <si>
+    <t>Conjunto Roma Verde</t>
+  </si>
+  <si>
+    <t>roma verde.jpg</t>
+  </si>
+  <si>
+    <t>Conjunto Roma Turquesa</t>
+  </si>
+  <si>
+    <t>roma turquesa.jpg</t>
+  </si>
+  <si>
+    <t>Conjunto Roma Anarillo</t>
+  </si>
+  <si>
+    <t>roma amarillo.jpg</t>
+  </si>
+  <si>
     <t>Collar Granada</t>
   </si>
   <si>
@@ -592,82 +661,61 @@
     <t>3 granadas.jpg</t>
   </si>
   <si>
-    <t>Collar Londres Verde</t>
+    <t>Choker Milán</t>
+  </si>
+  <si>
+    <t>Milan</t>
+  </si>
+  <si>
+    <t>Choker milan.jpg</t>
+  </si>
+  <si>
+    <t>Choker milan dorado.jpg</t>
+  </si>
+  <si>
+    <t>Choker gris.jpg</t>
+  </si>
+  <si>
+    <t>Choker beige.jpg</t>
+  </si>
+  <si>
+    <t>Choker y Pulsera Milan</t>
+  </si>
+  <si>
+    <t>choker y pulsera.jpg</t>
+  </si>
+  <si>
+    <t>Choker Flor</t>
+  </si>
+  <si>
+    <t>Flor</t>
+  </si>
+  <si>
+    <t>choker flor.jpg</t>
+  </si>
+  <si>
+    <t>choker flor 2.jpg</t>
+  </si>
+  <si>
+    <t>choker flor 3.jpg</t>
+  </si>
+  <si>
+    <t>Conjunto Paris y Milan</t>
+  </si>
+  <si>
+    <t>Paris y milan.jpg</t>
+  </si>
+  <si>
+    <t>tipos</t>
+  </si>
+  <si>
+    <t>Santander</t>
+  </si>
+  <si>
+    <t>Noja</t>
   </si>
   <si>
     <t>Londres</t>
-  </si>
-  <si>
-    <t>collar londres verde.jpg</t>
-  </si>
-  <si>
-    <t>Collar Londres Marron</t>
-  </si>
-  <si>
-    <t>collar londres marron.jpg</t>
-  </si>
-  <si>
-    <t>Collar Londres Rojo</t>
-  </si>
-  <si>
-    <t>londres rojo.jpg</t>
-  </si>
-  <si>
-    <t>Choker Milán</t>
-  </si>
-  <si>
-    <t>Milan</t>
-  </si>
-  <si>
-    <t>Choker milan.jpg</t>
-  </si>
-  <si>
-    <t>Choker milan dorado.jpg</t>
-  </si>
-  <si>
-    <t>Choker gris.jpg</t>
-  </si>
-  <si>
-    <t>Choker beige.jpg</t>
-  </si>
-  <si>
-    <t>Choker y Pulsera Milan</t>
-  </si>
-  <si>
-    <t>choker y pulsera.jpg</t>
-  </si>
-  <si>
-    <t>Choker Flor</t>
-  </si>
-  <si>
-    <t>Flor</t>
-  </si>
-  <si>
-    <t>choker flor.jpg</t>
-  </si>
-  <si>
-    <t>choker flor 2.jpg</t>
-  </si>
-  <si>
-    <t>choker flor 3.jpg</t>
-  </si>
-  <si>
-    <t>Conjunto Paris y Milan</t>
-  </si>
-  <si>
-    <t>Paris y milan.jpg</t>
-  </si>
-  <si>
-    <t>tipos</t>
-  </si>
-  <si>
-    <t>pendientes</t>
-  </si>
-  <si>
-    <t>Santander</t>
-  </si>
-  <si>
-    <t>Noja</t>
   </si>
 </sst>
 </file>
@@ -851,7 +899,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A74:I80" displayName="Table_10" name="Table_10" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A85:I88" displayName="Table_10" name="Table_10" id="10">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -877,7 +925,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C20" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C21" displayName="Table_12" name="Table_12" id="12">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -920,7 +968,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A52:I52" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A52:I56" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -937,7 +985,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A53:I61" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A57:I65" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -954,7 +1002,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I62" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I66" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -971,7 +1019,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I63" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I67" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -988,7 +1036,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I72" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I83" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1005,7 +1053,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A73:I73" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A84:I84" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1224,7 +1272,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="28.14"/>
     <col customWidth="1" min="2" max="2" width="17.71"/>
-    <col customWidth="1" min="3" max="3" width="13.57"/>
+    <col customWidth="1" min="3" max="3" width="16.43"/>
     <col customWidth="1" min="4" max="4" width="14.86"/>
     <col customWidth="1" min="5" max="5" width="29.29"/>
     <col customWidth="1" min="6" max="6" width="27.0"/>
@@ -2366,19 +2414,20 @@
         <v>144</v>
       </c>
       <c r="D53" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
+      <c r="F53" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>143</v>
@@ -2387,22 +2436,19 @@
         <v>144</v>
       </c>
       <c r="D54" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F54" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="F54" s="5"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>143</v>
@@ -2411,19 +2457,19 @@
         <v>144</v>
       </c>
       <c r="D55" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F55" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="F55" s="5"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>143</v>
@@ -2432,214 +2478,221 @@
         <v>144</v>
       </c>
       <c r="D56" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="F56" s="5"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D57" s="3">
         <v>13.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F57" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D58" s="3">
         <v>13.0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="I58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D59" s="3">
         <v>13.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F59" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D60" s="3">
         <v>13.0</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F60" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D61" s="3">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F61" s="2"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D62" s="3">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D63" s="3">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F63" s="2"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D64" s="3">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F64" s="2"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D65" s="3">
         <v>15.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F65" s="2"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D66" s="3">
         <v>15.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
+        <v>176</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -2650,21 +2703,15 @@
         <v>173</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D67" s="3">
         <v>15.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H67" s="1"/>
+        <v>178</v>
+      </c>
+      <c r="F67" s="2"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -2675,36 +2722,32 @@
         <v>173</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D68" s="3">
         <v>15.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
+        <v>179</v>
+      </c>
+      <c r="F68" s="2"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D69" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="1"/>
@@ -2713,19 +2756,19 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D70" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="1"/>
@@ -2734,40 +2777,38 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D71" s="3">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="1"/>
+        <v>185</v>
+      </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D72" s="3">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="1"/>
@@ -2776,209 +2817,368 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="D73" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="2"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="D74" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F74" s="2"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D75" s="3">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
+        <v>193</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D76" s="3">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F76" s="2"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D77" s="3">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F77" s="2"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D78" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>202</v>
-      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D79" s="3">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="5"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D80" s="3">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H80" s="5"/>
+        <v>202</v>
+      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="s">
-        <v>210</v>
+    <row r="81" ht="14.25" customHeight="1">
+      <c r="A81" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D81" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="E81" s="4" t="s">
+        <v>16.0</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" ht="14.25" customHeight="1">
+      <c r="A82" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D82" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" ht="14.25" customHeight="1">
+      <c r="A83" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D83" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" ht="14.25" customHeight="1">
+      <c r="A84" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D84" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="4"/>
-    </row>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
+      <c r="F84" s="2"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" ht="14.25" customHeight="1">
+      <c r="A85" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D85" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" ht="14.25" customHeight="1">
+      <c r="A86" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D86" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D88" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H88" s="5"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="4"/>
+    </row>
     <row r="95" ht="14.25" customHeight="1"/>
     <row r="96" ht="14.25" customHeight="1"/>
     <row r="97" ht="14.25" customHeight="1"/>
@@ -3897,13 +4097,21 @@
     <row r="1010" ht="14.25" customHeight="1"/>
     <row r="1011" ht="14.25" customHeight="1"/>
     <row r="1012" ht="14.25" customHeight="1"/>
+    <row r="1013" ht="14.25" customHeight="1"/>
+    <row r="1014" ht="14.25" customHeight="1"/>
+    <row r="1015" ht="14.25" customHeight="1"/>
+    <row r="1016" ht="14.25" customHeight="1"/>
+    <row r="1017" ht="14.25" customHeight="1"/>
+    <row r="1018" ht="14.25" customHeight="1"/>
+    <row r="1019" ht="14.25" customHeight="1"/>
+    <row r="1020" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B82">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C90">
+      <formula1>datos!$C$2:$C$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B90">
       <formula1>datos!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C82">
-      <formula1>datos!$C$2:$C$20</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -3939,7 +4147,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3955,7 +4163,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>35</v>
@@ -3963,7 +4171,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>67</v>
@@ -3971,7 +4179,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>126</v>
@@ -3979,7 +4187,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>84</v>
@@ -3987,22 +4195,22 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -4017,7 +4225,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -4032,22 +4240,22 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4055,7 +4263,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="C21" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
     <row r="22" ht="14.25" customHeight="1"/>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -241,7 +241,7 @@
     <t>San Francisco Cotton Camel</t>
   </si>
   <si>
-    <t>sf camel 2.jpg</t>
+    <t>sf camel k.jpg</t>
   </si>
   <si>
     <t>sf cotton camel.jpg</t>
@@ -256,7 +256,7 @@
     <t>San Francisco Cotton Burdeos</t>
   </si>
   <si>
-    <t>sf cotton burdeos.jpg</t>
+    <t>sf rojo k.jpg</t>
   </si>
   <si>
     <t>San Francisco Cotton Negro</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -241,10 +241,10 @@
     <t>San Francisco Cotton Camel</t>
   </si>
   <si>
+    <t>sf camel 2.jpg</t>
+  </si>
+  <si>
     <t>sf camel k.jpg</t>
-  </si>
-  <si>
-    <t>sf cotton camel.jpg</t>
   </si>
   <si>
     <t>San Francisco Cotton Vainilla</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -121,7 +121,7 @@
     <t>Chicago Crochet Blanco Perla</t>
   </si>
   <si>
-    <t>chicago blanco perla.jpg</t>
+    <t>chicago blanco k.jpg</t>
   </si>
   <si>
     <t>Kioto Dorado</t>
@@ -160,7 +160,7 @@
     <t>Kioto Verde Claro</t>
   </si>
   <si>
-    <t>kioto verde claro.jpg</t>
+    <t>kioto verde k.jpg</t>
   </si>
   <si>
     <t>kioto verde claro 2.jpg</t>
@@ -178,7 +178,7 @@
     <t>kioto negro puesto 1.jpg</t>
   </si>
   <si>
-    <t>kioto negro fb.jpg</t>
+    <t>kioto negro k.jpg</t>
   </si>
   <si>
     <t>Kioto Morado</t>
@@ -367,7 +367,7 @@
     <t>madrid chocolate 2.jpg</t>
   </si>
   <si>
-    <t>madrid chocolate fb.jpg</t>
+    <t>madrid choco k.jpg</t>
   </si>
   <si>
     <t>Huesca Cotton Chocolate</t>
@@ -466,7 +466,7 @@
     <t>Pendientes Río Verdes</t>
   </si>
   <si>
-    <t>2.jpg</t>
+    <t>rio verde k.jpg</t>
   </si>
   <si>
     <t>Pendientes Río Marrones</t>
@@ -478,7 +478,7 @@
     <t>Pendientes Río Rojo</t>
   </si>
   <si>
-    <t>1.jpg</t>
+    <t>rio rojo k .jpg</t>
   </si>
   <si>
     <t>Paris Gorro Negro</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -457,10 +457,10 @@
     <t>Río</t>
   </si>
   <si>
-    <t>rio blanco.jpg</t>
-  </si>
-  <si>
-    <t>3.jpg</t>
+    <t>rio blanco kk.jpg</t>
+  </si>
+  <si>
+    <t>rio blanco k.jpg</t>
   </si>
   <si>
     <t>Pendientes Río Verdes</t>
@@ -472,7 +472,7 @@
     <t>Pendientes Río Marrones</t>
   </si>
   <si>
-    <t>4.jpg</t>
+    <t>rio marron k.jpg</t>
   </si>
   <si>
     <t>Pendientes Río Rojo</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -145,7 +145,7 @@
     <t>Kioto Plateado</t>
   </si>
   <si>
-    <t>kioto plateado rocas.jpg</t>
+    <t>kioto plateado k.jpg</t>
   </si>
   <si>
     <t>kioto plateado 2</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -376,7 +376,7 @@
     <t>Huesca</t>
   </si>
   <si>
-    <t>huesca chocolate fb.jpg</t>
+    <t>huesca choco k.jpg</t>
   </si>
   <si>
     <t>Huesca Cotton Burdeos</t>
@@ -496,7 +496,7 @@
     <t>Paris Gorro Marron</t>
   </si>
   <si>
-    <t>paris marron 2.jpg</t>
+    <t>paris marron k.jpg</t>
   </si>
   <si>
     <t>gorro paris marrón.jpg</t>
@@ -514,7 +514,7 @@
     <t>Paris Gorro Naranja</t>
   </si>
   <si>
-    <t>gorro paris naranja.jpeg</t>
+    <t>paris naranja k.jpg</t>
   </si>
   <si>
     <t>Paris Gorro Azul</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -313,7 +313,7 @@
     <t>Vancouver Velvet</t>
   </si>
   <si>
-    <t>Vancouver velvet</t>
+    <t>vancouver velvet k.jpg</t>
   </si>
   <si>
     <t>Mini Madrid Cotton Burdeos</t>
@@ -610,13 +610,13 @@
     <t>Roma</t>
   </si>
   <si>
-    <t>Cuelgamovil Roma 1.jpg</t>
+    <t>roma corto k.jpg</t>
   </si>
   <si>
     <t>Cuelgamovil Roma Largo</t>
   </si>
   <si>
-    <t>cuelgamovil roma largo.jpg</t>
+    <t>roma largo k.jpg</t>
   </si>
   <si>
     <t>cuelga roma verano.jpg</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -559,7 +559,7 @@
     <t>bogota rojo.jpeg</t>
   </si>
   <si>
-    <t>bogota amarillo.jpeg</t>
+    <t>bogota amarillo.jpg</t>
   </si>
   <si>
     <t>Bogotá Marron.jpg</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -190,7 +190,7 @@
     <t>Kioto Dorado Metalizado</t>
   </si>
   <si>
-    <t>kioto dorado metalizado.jpg</t>
+    <t>kioto brillante k.jpg</t>
   </si>
   <si>
     <t>Kioto Japo Beige</t>
@@ -520,7 +520,7 @@
     <t>Paris Gorro Azul</t>
   </si>
   <si>
-    <t>paris azul.jpg</t>
+    <t>paris azul k.jpg</t>
   </si>
   <si>
     <t>Paris Gorro Lila</t>
@@ -619,7 +619,7 @@
     <t>roma largo k.jpg</t>
   </si>
   <si>
-    <t>cuelga roma verano.jpg</t>
+    <t>roma verano corto k.jpg</t>
   </si>
   <si>
     <t>cuelga verano largo.jpg</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -217,7 +217,7 @@
     <t>Tenerife</t>
   </si>
   <si>
-    <t>tenerife pana.jpg</t>
+    <t>tenerife pana k.jpg</t>
   </si>
   <si>
     <t>tenerife pana 2.jpg</t>
@@ -241,7 +241,7 @@
     <t>San Francisco Cotton Camel</t>
   </si>
   <si>
-    <t>sf camel 2.jpg</t>
+    <t>bolso sf camel k.jpg</t>
   </si>
   <si>
     <t>sf camel k.jpg</t>
@@ -508,7 +508,7 @@
     <t>Paris Gorro Crudo</t>
   </si>
   <si>
-    <t>paris gorro crudo.jpg</t>
+    <t>paris blanco k.jpg</t>
   </si>
   <si>
     <t>Paris Gorro Naranja</t>
@@ -589,19 +589,19 @@
     <t>Collar Bogota Rojo</t>
   </si>
   <si>
-    <t>collar bogota rojo.jpg</t>
+    <t>collar bogota rojo k.jpg</t>
   </si>
   <si>
     <t>Collar Bogota Lima</t>
   </si>
   <si>
-    <t>Collar Bogota Lima.jpg</t>
+    <t>collar bogota lima k.jpg</t>
   </si>
   <si>
     <t>Collar Bogota</t>
   </si>
   <si>
-    <t>Collar Bogota blanco.jpg</t>
+    <t>collar bogota blanco k.jpg</t>
   </si>
   <si>
     <t>Cuelgamovil Roma</t>
@@ -682,7 +682,7 @@
     <t>Choker y Pulsera Milan</t>
   </si>
   <si>
-    <t>choker y pulsera.jpg</t>
+    <t>choker y pulsera k.jpg</t>
   </si>
   <si>
     <t>Choker Flor</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -382,7 +382,7 @@
     <t>Huesca Cotton Burdeos</t>
   </si>
   <si>
-    <t>huesca burdeos 2.jpg</t>
+    <t>huesca rojo k.jpg</t>
   </si>
   <si>
     <t>Huesca Velvet Gris</t>
@@ -526,7 +526,7 @@
     <t>Paris Gorro Lila</t>
   </si>
   <si>
-    <t>Paris lila.png</t>
+    <t>paris lila k.jpg</t>
   </si>
   <si>
     <t>Paris Gorro Beige</t>
@@ -691,10 +691,10 @@
     <t>Flor</t>
   </si>
   <si>
-    <t>choker flor.jpg</t>
-  </si>
-  <si>
-    <t>choker flor 2.jpg</t>
+    <t>flor k.jpg</t>
+  </si>
+  <si>
+    <t>flor 2 k.jpg</t>
   </si>
   <si>
     <t>choker flor 3.jpg</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -58,7 +58,7 @@
     <t>Chicago</t>
   </si>
   <si>
-    <t>chicago negro terciopelo 3</t>
+    <t>chicago terciopelo k.jpg</t>
   </si>
   <si>
     <t>chicago terciopelo negro.jpg</t>
@@ -70,7 +70,7 @@
     <t>Chicago Blanco Cocodrilo</t>
   </si>
   <si>
-    <t>chicago blanco cocodrilo 2</t>
+    <t>chicago blanco cocodrilo k .jpg</t>
   </si>
   <si>
     <t>chicago blanco cocodrilo.jpg</t>
@@ -79,7 +79,7 @@
     <t>Chicago Naranja</t>
   </si>
   <si>
-    <t>chicago naranja 2.jpg</t>
+    <t>chicago naranja k.jpg</t>
   </si>
   <si>
     <t>chicago naranja.jpg</t>
@@ -88,7 +88,7 @@
     <t>Chicago Bordado Negro</t>
   </si>
   <si>
-    <t>chicago bordado negro 2.jpg</t>
+    <t>chicago bordado k.jpg</t>
   </si>
   <si>
     <t>chicago bordado negro fb.jpg</t>
@@ -115,7 +115,7 @@
     <t>chicago dorado meta.jpg</t>
   </si>
   <si>
-    <t>chicago dorado meta 2.jpg</t>
+    <t>chicago brillante k.jpg</t>
   </si>
   <si>
     <t>Chicago Crochet Blanco Perla</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="231">
   <si>
     <t>nombre</t>
   </si>
@@ -130,7 +130,7 @@
     <t>Kioto</t>
   </si>
   <si>
-    <t>kioto dorado 2.jpg</t>
+    <t>kioto dorado k.jpg</t>
   </si>
   <si>
     <t>kiotos.jpg</t>
@@ -160,7 +160,7 @@
     <t>Kioto Verde Claro</t>
   </si>
   <si>
-    <t>kioto verde k.jpg</t>
+    <t>kioto verde claro k.jpg</t>
   </si>
   <si>
     <t>kioto verde claro 2.jpg</t>
@@ -175,9 +175,6 @@
     <t>Kioto Negro</t>
   </si>
   <si>
-    <t>kioto negro puesto 1.jpg</t>
-  </si>
-  <si>
     <t>kioto negro k.jpg</t>
   </si>
   <si>
@@ -226,7 +223,7 @@
     <t>San Francisco</t>
   </si>
   <si>
-    <t>sf playaa.jpg</t>
+    <t>sf playa k.jpg</t>
   </si>
   <si>
     <t>San Francisco Cotton Azul</t>
@@ -1643,14 +1640,14 @@
         <v>51</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>10</v>
@@ -1662,14 +1659,14 @@
         <v>30.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17" s="2"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>10</v>
@@ -1681,14 +1678,14 @@
         <v>30.0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="2"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>10</v>
@@ -1700,14 +1697,14 @@
         <v>25.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F19" s="2"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -1719,14 +1716,14 @@
         <v>25.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
@@ -1738,109 +1735,109 @@
         <v>25.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3">
         <v>28.0</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="I22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3">
         <v>25.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23" s="2"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3">
         <v>25.0</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="3">
         <v>25.0</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" s="3">
         <v>25.0</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1849,19 +1846,19 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3">
         <v>25.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
@@ -1869,19 +1866,19 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D28" s="3">
         <v>25.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="1"/>
@@ -1889,19 +1886,19 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D29" s="3">
         <v>25.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -1910,19 +1907,19 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30" s="3">
         <v>20.0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1931,19 +1928,19 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D31" s="3">
         <v>40.0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -1952,44 +1949,44 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32" s="3">
         <v>40.0</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D33" s="3">
         <v>25.0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="1"/>
@@ -1998,19 +1995,19 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D34" s="3">
         <v>25.0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -2019,19 +2016,19 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" s="3">
         <v>30.0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -2040,19 +2037,19 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" s="3">
         <v>20.0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2061,43 +2058,43 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3">
         <v>20.0</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" s="3">
         <v>20.0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2106,19 +2103,19 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="3">
         <v>20.0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2127,22 +2124,22 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D40" s="3">
         <v>25.0</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2150,41 +2147,41 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D41" s="3">
         <v>25.0</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D42" s="3">
         <v>25.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2193,19 +2190,19 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D43" s="3">
         <v>25.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2214,19 +2211,19 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D44" s="3">
         <v>25.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2235,19 +2232,19 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D45" s="3">
         <v>25.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2256,19 +2253,19 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D46" s="3">
         <v>25.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2277,22 +2274,22 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D47" s="3">
         <v>30.0</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2300,19 +2297,19 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D48" s="3">
         <v>30.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="1"/>
@@ -2321,19 +2318,19 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D49" s="3">
         <v>30.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2342,19 +2339,19 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D50" s="3">
         <v>30.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2363,19 +2360,19 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D51" s="3">
         <v>30.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2384,19 +2381,19 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D52" s="3">
         <v>30.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="1"/>
@@ -2405,41 +2402,41 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D53" s="3">
         <v>11.0</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D54" s="3">
         <v>11.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="1"/>
@@ -2448,19 +2445,19 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D55" s="3">
         <v>11.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="1"/>
@@ -2469,19 +2466,19 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D56" s="3">
         <v>11.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="1"/>
@@ -2490,19 +2487,19 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D57" s="3">
         <v>13.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2511,43 +2508,43 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D58" s="3">
         <v>13.0</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="I58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D59" s="3">
         <v>13.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2556,19 +2553,19 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D60" s="3">
         <v>13.0</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -2577,19 +2574,19 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D61" s="3">
         <v>13.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="1"/>
@@ -2598,19 +2595,19 @@
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D62" s="3">
         <v>13.0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="1"/>
@@ -2619,135 +2616,135 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D63" s="3">
         <v>13.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F63" s="2"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D64" s="3">
         <v>13.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F64" s="2"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D65" s="3">
         <v>15.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F65" s="2"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D66" s="3">
         <v>15.0</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D67" s="3">
         <v>15.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F67" s="2"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D68" s="3">
         <v>15.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F68" s="2"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D69" s="3">
         <v>15.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="1"/>
@@ -2756,19 +2753,19 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D70" s="3">
         <v>15.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="1"/>
@@ -2777,38 +2774,38 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="C71" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D71" s="3">
         <v>15.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="1"/>
@@ -2817,19 +2814,19 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="1"/>
@@ -2838,19 +2835,19 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="1"/>
@@ -2859,19 +2856,19 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -2879,19 +2876,19 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="D76" s="3">
         <v>6.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="1"/>
@@ -2900,19 +2897,19 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D77" s="3">
         <v>10.0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="1"/>
@@ -2921,19 +2918,19 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="D78" s="3">
         <v>6.0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="1"/>
@@ -2942,19 +2939,19 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D79" s="3">
         <v>10.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2963,19 +2960,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D80" s="3">
         <v>16.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2984,19 +2981,19 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D81" s="3">
         <v>16.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="1"/>
@@ -3005,19 +3002,19 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D82" s="3">
         <v>16.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="1"/>
@@ -3026,19 +3023,19 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D83" s="3">
         <v>16.0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="1"/>
@@ -3047,84 +3044,84 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="D84" s="3">
         <v>12.0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F84" s="2"/>
       <c r="I84" s="1"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="D85" s="3">
         <v>12.0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F85" s="2"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="D86" s="3">
         <v>13.0</v>
       </c>
       <c r="E86" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="G86" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="H86" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="I86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D87" s="3">
         <v>20.0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -3133,44 +3130,44 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="D88" s="3">
         <v>9.0</v>
       </c>
       <c r="E88" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="1"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D89" s="3">
         <v>20.0</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90">
@@ -4147,7 +4144,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4163,7 +4160,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>35</v>
@@ -4171,101 +4168,101 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -286,7 +286,7 @@
     <t>Vancouver Lazo Dorado</t>
   </si>
   <si>
-    <t>vancouver lazo dorado.jpg</t>
+    <t>vancouver lazo dorado kk.jpg</t>
   </si>
   <si>
     <t>vancouver lazo dorado 2.jpg</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="k2YKHSllsTZPBZoihDyrBbRFVCqlv09n9KoVgw1eatk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="PDWVkrIutMZ8DCBE/M6H0VmYfdLE+m6e0hGy6mDGhL4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="238">
   <si>
     <t>nombre</t>
   </si>
@@ -295,6 +295,12 @@
     <t>vancouver dorado puesto 3.jpg</t>
   </si>
   <si>
+    <t>Vancouver Lazo Negro</t>
+  </si>
+  <si>
+    <t>vancouver lazo negro k.jpg</t>
+  </si>
+  <si>
     <t>Vancouver Vintage Rosa</t>
   </si>
   <si>
@@ -325,7 +331,7 @@
     <t>Mini Madrid Cotton Verde</t>
   </si>
   <si>
-    <t>mini madrid verde 3.jpg</t>
+    <t>mini madrid k.jpg</t>
   </si>
   <si>
     <t>mini madrid verde.jpg</t>
@@ -367,12 +373,24 @@
     <t>madrid choco k.jpg</t>
   </si>
   <si>
+    <t>Huesca Cotton Beige</t>
+  </si>
+  <si>
+    <t>Huesca</t>
+  </si>
+  <si>
+    <t>huesca beige k.jpg</t>
+  </si>
+  <si>
+    <t>Huesca Cotton Verde</t>
+  </si>
+  <si>
+    <t>huesca verde k.jpg</t>
+  </si>
+  <si>
     <t>Huesca Cotton Chocolate</t>
   </si>
   <si>
-    <t>Huesca</t>
-  </si>
-  <si>
     <t>huesca choco k.jpg</t>
   </si>
   <si>
@@ -478,7 +496,7 @@
     <t>rio rojo k .jpg</t>
   </si>
   <si>
-    <t>Paris Gorro Negro</t>
+    <t>Paris Gorro Marron</t>
   </si>
   <si>
     <t>gorros</t>
@@ -487,12 +505,6 @@
     <t>Paris</t>
   </si>
   <si>
-    <t>Paris gorro negrooo.jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Marron</t>
-  </si>
-  <si>
     <t>paris marron k.jpg</t>
   </si>
   <si>
@@ -568,18 +580,12 @@
     <t>bogota colores.jpg</t>
   </si>
   <si>
-    <t>Collar Bogota Amarillo</t>
+    <t>Collar Bogota Camel</t>
   </si>
   <si>
     <t>collar</t>
   </si>
   <si>
-    <t>Collar Bogota.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota Camel</t>
-  </si>
-  <si>
     <t>Collar Bogota Camel.jpg</t>
   </si>
   <si>
@@ -595,6 +601,12 @@
     <t>collar bogota lima k.jpg</t>
   </si>
   <si>
+    <t>Coolar Bogota Azul</t>
+  </si>
+  <si>
+    <t>collar bogota azul k.jpg</t>
+  </si>
+  <si>
     <t>Collar Bogota</t>
   </si>
   <si>
@@ -701,6 +713,15 @@
   </si>
   <si>
     <t>Paris y milan.jpg</t>
+  </si>
+  <si>
+    <t>Bandana Venecia</t>
+  </si>
+  <si>
+    <t>Venecia</t>
+  </si>
+  <si>
+    <t>venecia azul k.jpg</t>
   </si>
   <si>
     <t>tipos</t>
@@ -879,7 +900,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I49" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I52" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -896,7 +917,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A85:I88" displayName="Table_10" name="Table_10" id="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I90" displayName="Table_10" name="Table_10" id="10">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -922,7 +943,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C21" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C22" displayName="Table_12" name="Table_12" id="12">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -931,7 +952,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A50:I50" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A53:I53" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -948,7 +969,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A51:I51" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A54:I54" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -965,7 +986,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A52:I56" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A55:I59" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -982,7 +1003,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A57:I65" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A60:I67" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -999,7 +1020,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I66" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I68" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1016,7 +1037,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I67" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I69" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1033,7 +1054,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I83" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I85" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1050,7 +1071,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A84:I84" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I86" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1983,7 +2004,7 @@
         <v>83</v>
       </c>
       <c r="D33" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>92</v>
@@ -2010,7 +2031,7 @@
         <v>94</v>
       </c>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
@@ -2025,13 +2046,13 @@
         <v>83</v>
       </c>
       <c r="D35" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
@@ -2043,13 +2064,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D36" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2058,13 +2079,13 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D37" s="3">
         <v>20.0</v>
@@ -2072,33 +2093,33 @@
       <c r="E37" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D38" s="3">
         <v>20.0</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -2109,7 +2130,7 @@
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D39" s="3">
         <v>20.0</v>
@@ -2130,73 +2151,73 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D40" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D41" s="3">
         <v>25.0</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D42" s="3">
         <v>25.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="D43" s="3">
         <v>25.0</v>
@@ -2217,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D44" s="3">
         <v>25.0</v>
@@ -2238,7 +2259,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D45" s="3">
         <v>25.0</v>
@@ -2259,13 +2280,13 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D46" s="3">
         <v>25.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2274,51 +2295,49 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D48" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F48" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>10</v>
@@ -2327,10 +2346,10 @@
         <v>131</v>
       </c>
       <c r="D49" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2339,7 +2358,7 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>10</v>
@@ -2351,22 +2370,24 @@
         <v>30.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F50" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="D51" s="3">
         <v>30.0</v>
@@ -2374,7 +2395,7 @@
       <c r="E51" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F51" s="1"/>
+      <c r="F51" s="2"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -2387,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D52" s="3">
         <v>30.0</v>
@@ -2395,7 +2416,7 @@
       <c r="E52" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F52" s="2"/>
+      <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2405,83 +2426,83 @@
         <v>141</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D53" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D54" s="3">
-        <v>11.0</v>
+        <v>30.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F54" s="5"/>
+        <v>144</v>
+      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D55" s="3">
-        <v>11.0</v>
+        <v>30.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F55" s="5"/>
+        <v>146</v>
+      </c>
+      <c r="F55" s="2"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D56" s="3">
         <v>11.0</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F56" s="5"/>
-      <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
@@ -2490,86 +2511,86 @@
         <v>152</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D57" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F57" s="1"/>
+      <c r="F57" s="5"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D58" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>159</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F58" s="5"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D59" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F59" s="1"/>
+        <v>157</v>
+      </c>
+      <c r="F59" s="5"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D60" s="3">
         <v>13.0</v>
       </c>
       <c r="E60" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -2577,10 +2598,10 @@
         <v>164</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D61" s="3">
         <v>13.0</v>
@@ -2588,7 +2609,7 @@
       <c r="E61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F61" s="2"/>
+      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2598,10 +2619,10 @@
         <v>166</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D62" s="3">
         <v>13.0</v>
@@ -2609,7 +2630,7 @@
       <c r="E62" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F62" s="2"/>
+      <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -2619,10 +2640,10 @@
         <v>168</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D63" s="3">
         <v>13.0</v>
@@ -2631,181 +2652,183 @@
         <v>169</v>
       </c>
       <c r="F63" s="2"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D64" s="3">
         <v>13.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F64" s="2"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="D65" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="F65" s="2"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D66" s="3">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F66" s="2"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D67" s="3">
         <v>15.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F67" s="2"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D68" s="3">
         <v>15.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F68" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D69" s="3">
         <v>15.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F69" s="2"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D70" s="3">
         <v>15.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="2"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D71" s="3">
         <v>15.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>184</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="1"/>
@@ -2814,13 +2837,13 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="C73" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
@@ -2838,10 +2861,10 @@
         <v>189</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
@@ -2859,10 +2882,10 @@
         <v>191</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
@@ -2870,6 +2893,7 @@
       <c r="E75" s="2" t="s">
         <v>192</v>
       </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2879,58 +2903,56 @@
         <v>193</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D76" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D76" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F76" s="2"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D77" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F77" s="2"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D78" s="3">
         <v>6.0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="1"/>
@@ -2939,19 +2961,19 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D79" s="3">
         <v>10.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2960,19 +2982,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D80" s="3">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2981,16 +3003,16 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D81" s="3">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>203</v>
@@ -3005,10 +3027,10 @@
         <v>204</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D82" s="3">
         <v>16.0</v>
@@ -3026,10 +3048,10 @@
         <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D83" s="3">
         <v>16.0</v>
@@ -3047,37 +3069,41 @@
         <v>208</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C84" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D84" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D84" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F84" s="2"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D85" s="3">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>211</v>
       </c>
       <c r="F85" s="2"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -3085,99 +3111,146 @@
         <v>212</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>213</v>
       </c>
       <c r="D86" s="3">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="F86" s="2"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>213</v>
       </c>
       <c r="D87" s="3">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E87" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="A88" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D88" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="s">
+      <c r="G88" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="H88" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D88" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E88" s="2" t="s">
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H88" s="5"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D89" s="3">
         <v>20.0</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D90" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="4"/>
-    </row>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
+      <c r="F90" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H90" s="5"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D91" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D92" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
     <row r="97" ht="14.25" customHeight="1"/>
     <row r="98" ht="14.25" customHeight="1"/>
     <row r="99" ht="14.25" customHeight="1"/>
@@ -4102,12 +4175,14 @@
     <row r="1018" ht="14.25" customHeight="1"/>
     <row r="1019" ht="14.25" customHeight="1"/>
     <row r="1020" ht="14.25" customHeight="1"/>
+    <row r="1021" ht="14.25" customHeight="1"/>
+    <row r="1022" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C90">
-      <formula1>datos!$C$2:$C$21</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C92">
+      <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B90">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B92">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4144,7 +4219,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4160,7 +4235,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>35</v>
@@ -4168,7 +4243,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>66</v>
@@ -4176,15 +4251,15 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>83</v>
@@ -4192,67 +4267,67 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4262,10 +4337,14 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="C22" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
     <row r="23" ht="14.25" customHeight="1"/>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="PDWVkrIutMZ8DCBE/M6H0VmYfdLE+m6e0hGy6mDGhL4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="JkU2KEdMCgyobvmW6xDkSHa1k4td1rsN/KVbpOQI4iw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="229">
   <si>
     <t>nombre</t>
   </si>
@@ -547,7 +547,7 @@
     <t>paris colores</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuelgamovil Bogota </t>
+    <t>Bogota colores</t>
   </si>
   <si>
     <t>cuelgamovil</t>
@@ -556,27 +556,6 @@
     <t>Bogota</t>
   </si>
   <si>
-    <t>bogota 1.png</t>
-  </si>
-  <si>
-    <t>bogota verde.jpeg</t>
-  </si>
-  <si>
-    <t>bogota verde 2.jpg</t>
-  </si>
-  <si>
-    <t>bogota rojo.jpeg</t>
-  </si>
-  <si>
-    <t>bogota amarillo.jpg</t>
-  </si>
-  <si>
-    <t>Bogotá Marron.jpg</t>
-  </si>
-  <si>
-    <t>Bogota colores</t>
-  </si>
-  <si>
     <t>bogota colores.jpg</t>
   </si>
   <si>
@@ -601,7 +580,7 @@
     <t>collar bogota lima k.jpg</t>
   </si>
   <si>
-    <t>Coolar Bogota Azul</t>
+    <t>Collar Bogota Azul</t>
   </si>
   <si>
     <t>collar bogota azul k.jpg</t>
@@ -631,31 +610,31 @@
     <t>roma verano corto k.jpg</t>
   </si>
   <si>
-    <t>cuelga verano largo.jpg</t>
+    <t>cuelga roma verano k.jpg</t>
   </si>
   <si>
     <t>Conjunto Roma Rosa</t>
   </si>
   <si>
-    <t>roma rosa.jpg</t>
+    <t>conjunto roma rosa k.jpg</t>
   </si>
   <si>
     <t>Conjunto Roma Verde</t>
   </si>
   <si>
-    <t>roma verde.jpg</t>
+    <t>conjunto roma verde k.jpg</t>
   </si>
   <si>
     <t>Conjunto Roma Turquesa</t>
   </si>
   <si>
-    <t>roma turquesa.jpg</t>
+    <t>conjunto roma terqueas k.jpg</t>
   </si>
   <si>
     <t>Conjunto Roma Anarillo</t>
   </si>
   <si>
-    <t>roma amarillo.jpg</t>
+    <t>conjunto roma amarillo k.jpg</t>
   </si>
   <si>
     <t>Collar Granada</t>
@@ -707,12 +686,6 @@
   </si>
   <si>
     <t>choker flor 3.jpg</t>
-  </si>
-  <si>
-    <t>Conjunto Paris y Milan</t>
-  </si>
-  <si>
-    <t>Paris y milan.jpg</t>
   </si>
   <si>
     <t>Bandana Venecia</t>
@@ -835,7 +808,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="12">
+  <tableStyles count="10">
     <tableStyle count="3" pivot="0" name="catalogo-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -862,18 +835,10 @@
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="2" pivot="0" name="catalogo-style 7">
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 8">
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 9">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 10">
+    <tableStyle count="2" pivot="0" name="catalogo-style 8">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
@@ -917,33 +882,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I90" displayName="Table_10" name="Table_10" id="10">
-  <tableColumns count="9">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-  </tableColumns>
-  <tableStyleInfo name="catalogo-style 10" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:A6" displayName="Table_11" name="Table_11" id="11">
-  <tableColumns count="1">
-    <tableColumn name="tipos" id="1"/>
-  </tableColumns>
-  <tableStyleInfo name="datos-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C22" displayName="Table_12" name="Table_12" id="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C22" displayName="Table_10" name="Table_10" id="10">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -1003,7 +942,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A60:I67" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A60:I66" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1020,7 +959,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I68" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I80" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1037,7 +976,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I69" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A81:I81" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1054,7 +993,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I85" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A82:I85" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1071,19 +1010,11 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I86" displayName="Table_9" name="Table_9" id="9">
-  <tableColumns count="9">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:A6" displayName="Table_9" name="Table_9" id="9">
+  <tableColumns count="1">
+    <tableColumn name="tipos" id="1"/>
   </tableColumns>
-  <tableStyleInfo name="catalogo-style 9" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="datos-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -2732,14 +2663,16 @@
         <v>178</v>
       </c>
       <c r="F67" s="2"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>177</v>
@@ -2748,19 +2681,19 @@
         <v>15.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>180</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>177</v>
@@ -2769,17 +2702,19 @@
         <v>15.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F69" s="2"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>177</v>
@@ -2788,17 +2723,19 @@
         <v>15.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F70" s="2"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>177</v>
@@ -2807,19 +2744,18 @@
         <v>15.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F71" s="2"/>
+        <v>187</v>
+      </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>177</v>
@@ -2828,28 +2764,27 @@
         <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F72" s="2"/>
+        <v>189</v>
+      </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D73" s="3">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="1"/>
@@ -2858,19 +2793,19 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D74" s="3">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="1"/>
@@ -2879,19 +2814,19 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="D75" s="3">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="1"/>
@@ -2903,56 +2838,58 @@
         <v>193</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D76" s="3">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>194</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D77" s="3">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="F77" s="2"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D78" s="3">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="1"/>
@@ -2961,19 +2898,19 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D79" s="3">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2982,19 +2919,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D80" s="3">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -3003,254 +2940,138 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D81" s="3">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F81" s="2"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D82" s="3">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F82" s="2"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D83" s="3">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F83" s="2"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>214</v>
+      </c>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84">
       <c r="A84" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D84" s="3">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F84" s="2"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="5"/>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85">
       <c r="A85" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D85" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
+        <v>219</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H85" s="5"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="2" t="s">
-        <v>212</v>
+    <row r="86">
+      <c r="A86" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D86" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F86" s="2"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D87" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F87" s="2"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D88" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D89" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="s">
+        <v>15.0</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D90" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H90" s="5"/>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D91" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D92" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
+    </row>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
     <row r="97" ht="14.25" customHeight="1"/>
     <row r="98" ht="14.25" customHeight="1"/>
     <row r="99" ht="14.25" customHeight="1"/>
@@ -4171,18 +3992,12 @@
     <row r="1014" ht="14.25" customHeight="1"/>
     <row r="1015" ht="14.25" customHeight="1"/>
     <row r="1016" ht="14.25" customHeight="1"/>
-    <row r="1017" ht="14.25" customHeight="1"/>
-    <row r="1018" ht="14.25" customHeight="1"/>
-    <row r="1019" ht="14.25" customHeight="1"/>
-    <row r="1020" ht="14.25" customHeight="1"/>
-    <row r="1021" ht="14.25" customHeight="1"/>
-    <row r="1022" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C92">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C86">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B92">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B86">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4190,17 +4005,15 @@
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
-  <tableParts count="10">
+  <tableParts count="8">
+    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
     <tablePart r:id="rId15"/>
     <tablePart r:id="rId16"/>
     <tablePart r:id="rId17"/>
-    <tablePart r:id="rId18"/>
-    <tablePart r:id="rId19"/>
-    <tablePart r:id="rId20"/>
-    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4219,7 +4032,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4251,7 +4064,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>131</v>
@@ -4267,12 +4080,12 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -4297,7 +4110,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -4312,22 +4125,22 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4342,7 +4155,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="JkU2KEdMCgyobvmW6xDkSHa1k4td1rsN/KVbpOQI4iw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="gvMw+GiBHWpiljbedo6JX6qK9NTUXCeq4Zg+/yqLjV8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="231">
   <si>
     <t>nombre</t>
   </si>
@@ -488,6 +488,12 @@
   </si>
   <si>
     <t>rio marron k.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendientes Río Mar </t>
+  </si>
+  <si>
+    <t>rio mar k .jpg</t>
   </si>
   <si>
     <t>Pendientes Río Rojo</t>
@@ -925,7 +931,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A55:I59" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A55:I60" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -942,7 +948,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A60:I66" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A61:I67" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -959,7 +965,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I80" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I81" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -976,7 +982,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A81:I81" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A82:I82" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -993,7 +999,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A82:I85" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A83:I86" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -2505,44 +2511,44 @@
         <v>158</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D60" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D61" s="3">
         <v>13.0</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -2550,10 +2556,10 @@
         <v>166</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D62" s="3">
         <v>13.0</v>
@@ -2571,10 +2577,10 @@
         <v>168</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D63" s="3">
         <v>13.0</v>
@@ -2582,7 +2588,7 @@
       <c r="E63" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F63" s="2"/>
+      <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -2592,10 +2598,10 @@
         <v>170</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D64" s="3">
         <v>13.0</v>
@@ -2613,10 +2619,10 @@
         <v>172</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D65" s="3">
         <v>13.0</v>
@@ -2625,63 +2631,63 @@
         <v>173</v>
       </c>
       <c r="F65" s="2"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3">
         <v>13.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" s="2"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D67" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F67" s="2"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D68" s="3">
         <v>15.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="1"/>
@@ -2690,13 +2696,13 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="C69" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D69" s="3">
         <v>15.0</v>
@@ -2714,10 +2720,10 @@
         <v>184</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D70" s="3">
         <v>15.0</v>
@@ -2735,10 +2741,10 @@
         <v>186</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D71" s="3">
         <v>15.0</v>
@@ -2746,6 +2752,7 @@
       <c r="E71" s="2" t="s">
         <v>187</v>
       </c>
+      <c r="F71" s="2"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -2755,10 +2762,10 @@
         <v>188</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
@@ -2775,34 +2782,33 @@
         <v>190</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D73" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D73" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F73" s="2"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="D74" s="3">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>194</v>
@@ -2814,19 +2820,19 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D75" s="3">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="1"/>
@@ -2835,19 +2841,19 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="D76" s="3">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="1"/>
@@ -2856,16 +2862,16 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D77" s="3">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>198</v>
@@ -2880,10 +2886,10 @@
         <v>199</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D78" s="3">
         <v>16.0</v>
@@ -2901,10 +2907,10 @@
         <v>201</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D79" s="3">
         <v>16.0</v>
@@ -2922,10 +2928,10 @@
         <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D80" s="3">
         <v>16.0</v>
@@ -2943,85 +2949,85 @@
         <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D81" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D81" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="F81" s="2"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D82" s="3">
         <v>12.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F82" s="2"/>
       <c r="I82" s="1"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D83" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D83" s="3">
+      <c r="F83" s="2"/>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" ht="14.25" customHeight="1">
+      <c r="A84" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D84" s="3">
         <v>13.0</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G83" s="4" t="s">
+      <c r="E84" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="H83" s="4" t="s">
+      <c r="F84" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="s">
+      <c r="G84" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D84" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E84" s="2" t="s">
+      <c r="H84" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="5"/>
       <c r="I84" s="1"/>
     </row>
     <row r="85">
@@ -3029,44 +3035,64 @@
         <v>217</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D85" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D85" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>221</v>
-      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
       <c r="H85" s="5"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D86" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C86" s="2" t="s">
+      <c r="G86" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D86" s="3">
+      <c r="H86" s="5"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D87" s="3">
         <v>15.0</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="91" ht="14.25" customHeight="1"/>
+      <c r="E87" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
     <row r="92" ht="14.25" customHeight="1"/>
     <row r="93" ht="14.25" customHeight="1"/>
     <row r="94" ht="14.25" customHeight="1"/>
@@ -3992,12 +4018,13 @@
     <row r="1014" ht="14.25" customHeight="1"/>
     <row r="1015" ht="14.25" customHeight="1"/>
     <row r="1016" ht="14.25" customHeight="1"/>
+    <row r="1017" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C86">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C87">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B86">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B87">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4032,7 +4059,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4048,7 +4075,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>35</v>
@@ -4056,7 +4083,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>66</v>
@@ -4064,7 +4091,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>131</v>
@@ -4080,22 +4107,22 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -4110,7 +4137,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -4125,22 +4152,22 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4155,7 +4182,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="gvMw+GiBHWpiljbedo6JX6qK9NTUXCeq4Zg+/yqLjV8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="sLavV584LfK7/TT/FzFVGFPq0oMdx3IFDCfhwnsuOPc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="233">
   <si>
     <t>nombre</t>
   </si>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>tenerife pana 2.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Naranja Bordado</t>
+  </si>
+  <si>
+    <t>tenerife naranja k.jpg</t>
   </si>
   <si>
     <t>San Francisco</t>
@@ -871,7 +877,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I52" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I53" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -897,7 +903,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A53:I53" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A54:I54" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -914,7 +920,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A54:I54" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A55:I55" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -931,7 +937,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A55:I60" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A56:I61" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -948,7 +954,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A61:I67" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I68" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -965,7 +971,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I81" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I82" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -982,7 +988,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A82:I82" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A83:I83" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -999,7 +1005,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A83:I86" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A84:I87" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1727,10 +1733,10 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>67</v>
@@ -1738,7 +1744,7 @@
       <c r="F23" s="2"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="s">
         <v>68</v>
       </c>
@@ -1746,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3">
         <v>25.0</v>
@@ -1754,51 +1760,49 @@
       <c r="E24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D25" s="3">
         <v>25.0</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3">
         <v>25.0</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
@@ -1810,14 +1814,15 @@
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D27" s="3">
         <v>25.0</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1830,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3">
         <v>25.0</v>
@@ -1850,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D29" s="3">
         <v>25.0</v>
@@ -1858,7 +1863,6 @@
       <c r="E29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1871,13 +1875,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="D30" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1886,16 +1890,16 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D31" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>86</v>
@@ -1913,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32" s="3">
         <v>40.0</v>
@@ -1921,33 +1925,33 @@
       <c r="E32" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D33" s="3">
         <v>40.0</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
@@ -1959,10 +1963,10 @@
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D34" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>94</v>
@@ -1980,7 +1984,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D35" s="3">
         <v>25.0</v>
@@ -1989,7 +1993,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
@@ -2001,16 +2005,16 @@
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D36" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
@@ -2022,13 +2026,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D37" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -2037,13 +2041,13 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D38" s="3">
         <v>20.0</v>
@@ -2051,33 +2055,33 @@
       <c r="E38" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D39" s="3">
         <v>20.0</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
@@ -2088,7 +2092,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D40" s="3">
         <v>20.0</v>
@@ -2109,73 +2113,73 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D41" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D42" s="3">
         <v>25.0</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D43" s="3">
         <v>25.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="D44" s="3">
         <v>25.0</v>
@@ -2196,7 +2200,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D45" s="3">
         <v>25.0</v>
@@ -2217,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D46" s="3">
         <v>25.0</v>
@@ -2238,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D47" s="3">
         <v>25.0</v>
@@ -2259,7 +2263,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D48" s="3">
         <v>25.0</v>
@@ -2280,13 +2284,13 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D49" s="3">
         <v>25.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2295,57 +2299,57 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="D50" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D51" s="3">
         <v>30.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F51" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="D52" s="3">
         <v>30.0</v>
@@ -2353,7 +2357,7 @@
       <c r="E52" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F52" s="1"/>
+      <c r="F52" s="2"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -2366,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D53" s="3">
         <v>30.0</v>
@@ -2387,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D54" s="3">
         <v>30.0</v>
@@ -2408,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D55" s="3">
         <v>30.0</v>
@@ -2416,7 +2420,7 @@
       <c r="E55" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F55" s="2"/>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -2426,41 +2430,41 @@
         <v>147</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D56" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D56" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D57" s="3">
         <v>11.0</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
@@ -2469,10 +2473,10 @@
         <v>154</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D58" s="3">
         <v>11.0</v>
@@ -2490,10 +2494,10 @@
         <v>156</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D59" s="3">
         <v>11.0</v>
@@ -2511,10 +2515,10 @@
         <v>158</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D60" s="3">
         <v>11.0</v>
@@ -2532,44 +2536,44 @@
         <v>160</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D61" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="F61" s="5"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D62" s="3">
         <v>13.0</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -2577,10 +2581,10 @@
         <v>168</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D63" s="3">
         <v>13.0</v>
@@ -2598,10 +2602,10 @@
         <v>170</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D64" s="3">
         <v>13.0</v>
@@ -2609,7 +2613,7 @@
       <c r="E64" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F64" s="2"/>
+      <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -2619,10 +2623,10 @@
         <v>172</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D65" s="3">
         <v>13.0</v>
@@ -2640,10 +2644,10 @@
         <v>174</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D66" s="3">
         <v>13.0</v>
@@ -2652,63 +2656,63 @@
         <v>175</v>
       </c>
       <c r="F66" s="2"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D67" s="3">
         <v>13.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F67" s="2"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D68" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="F68" s="2"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="D69" s="3">
         <v>15.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="1"/>
@@ -2717,13 +2721,13 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D70" s="3">
         <v>15.0</v>
@@ -2741,10 +2745,10 @@
         <v>186</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D71" s="3">
         <v>15.0</v>
@@ -2762,10 +2766,10 @@
         <v>188</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
@@ -2773,6 +2777,7 @@
       <c r="E72" s="2" t="s">
         <v>189</v>
       </c>
+      <c r="F72" s="2"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -2782,10 +2787,10 @@
         <v>190</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
@@ -2802,34 +2807,33 @@
         <v>192</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D74" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D74" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F74" s="2"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="D75" s="3">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>196</v>
@@ -2841,19 +2845,19 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D76" s="3">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="1"/>
@@ -2862,19 +2866,19 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="D77" s="3">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="1"/>
@@ -2883,16 +2887,16 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D78" s="3">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>200</v>
@@ -2907,10 +2911,10 @@
         <v>201</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D79" s="3">
         <v>16.0</v>
@@ -2928,10 +2932,10 @@
         <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D80" s="3">
         <v>16.0</v>
@@ -2949,10 +2953,10 @@
         <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D81" s="3">
         <v>16.0</v>
@@ -2970,85 +2974,85 @@
         <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C82" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D82" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D82" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F82" s="2"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D83" s="3">
         <v>12.0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F83" s="2"/>
       <c r="I83" s="1"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D84" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D84" s="3">
+      <c r="F84" s="2"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" ht="14.25" customHeight="1">
+      <c r="A85" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D85" s="3">
         <v>13.0</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G84" s="4" t="s">
+      <c r="E85" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="H84" s="4" t="s">
+      <c r="F85" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I84" s="1"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="s">
+      <c r="G85" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D85" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="H85" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="5"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86">
@@ -3056,44 +3060,64 @@
         <v>219</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D86" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D86" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>223</v>
-      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
       <c r="H86" s="5"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D87" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C87" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D87" s="3">
+      <c r="H87" s="5"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D88" s="3">
         <v>15.0</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="92" ht="14.25" customHeight="1"/>
+      <c r="E88" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
     <row r="93" ht="14.25" customHeight="1"/>
     <row r="94" ht="14.25" customHeight="1"/>
     <row r="95" ht="14.25" customHeight="1"/>
@@ -4019,12 +4043,13 @@
     <row r="1015" ht="14.25" customHeight="1"/>
     <row r="1016" ht="14.25" customHeight="1"/>
     <row r="1017" ht="14.25" customHeight="1"/>
+    <row r="1018" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C87">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C88">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B87">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B88">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4059,7 +4084,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4075,7 +4100,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>35</v>
@@ -4083,91 +4108,91 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4177,12 +4202,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="sLavV584LfK7/TT/FzFVGFPq0oMdx3IFDCfhwnsuOPc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="xBqBH6t+q+UJibfewq7dg927tUmlP0NWFnv+zSkvkGU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="234">
   <si>
     <t>nombre</t>
   </si>
@@ -49,6 +49,57 @@
     <t>imagen5</t>
   </si>
   <si>
+    <t>Paris Gorro Marron</t>
+  </si>
+  <si>
+    <t>gorros</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>paris marron k.jpg</t>
+  </si>
+  <si>
+    <t>gorro paris marrón.jpg</t>
+  </si>
+  <si>
+    <t>paris marron 3.jpg</t>
+  </si>
+  <si>
+    <t>Paris Gorro Crudo</t>
+  </si>
+  <si>
+    <t>paris blanco k.jpg</t>
+  </si>
+  <si>
+    <t>Paris Gorro Naranja</t>
+  </si>
+  <si>
+    <t>paris naranja k.jpg</t>
+  </si>
+  <si>
+    <t>Paris Gorro Azul</t>
+  </si>
+  <si>
+    <t>paris azul k.jpg</t>
+  </si>
+  <si>
+    <t>Paris Gorro Lila</t>
+  </si>
+  <si>
+    <t>paris lila k.jpg</t>
+  </si>
+  <si>
+    <t>Paris Gorro Beige</t>
+  </si>
+  <si>
+    <t>paris beige.jpg</t>
+  </si>
+  <si>
+    <t>paris colores</t>
+  </si>
+  <si>
     <t>Chicago Terciopelo Negro</t>
   </si>
   <si>
@@ -226,6 +277,12 @@
     <t>tenerife naranja k.jpg</t>
   </si>
   <si>
+    <t>Tenerife Flores</t>
+  </si>
+  <si>
+    <t>tenerife verano k.jpg</t>
+  </si>
+  <si>
     <t>San Francisco</t>
   </si>
   <si>
@@ -310,13 +367,10 @@
     <t>Vancouver Vintage Rosa</t>
   </si>
   <si>
-    <t>vancouver vintage rosa.jpg</t>
-  </si>
-  <si>
     <t>Vancouver Vintage Figuras</t>
   </si>
   <si>
-    <t>vancouver vintage figuras.jpg</t>
+    <t>vancouver vintage f k.jpg</t>
   </si>
   <si>
     <t>Vancouver Velvet</t>
@@ -506,57 +560,6 @@
   </si>
   <si>
     <t>rio rojo k .jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Marron</t>
-  </si>
-  <si>
-    <t>gorros</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>paris marron k.jpg</t>
-  </si>
-  <si>
-    <t>gorro paris marrón.jpg</t>
-  </si>
-  <si>
-    <t>paris marron 3.jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Crudo</t>
-  </si>
-  <si>
-    <t>paris blanco k.jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Naranja</t>
-  </si>
-  <si>
-    <t>paris naranja k.jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Azul</t>
-  </si>
-  <si>
-    <t>paris azul k.jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Lila</t>
-  </si>
-  <si>
-    <t>paris lila k.jpg</t>
-  </si>
-  <si>
-    <t>Paris Gorro Beige</t>
-  </si>
-  <si>
-    <t>paris beige.jpg</t>
-  </si>
-  <si>
-    <t>paris colores</t>
   </si>
   <si>
     <t>Bogota colores</t>
@@ -820,7 +823,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="10">
+  <tableStyles count="9">
     <tableStyle count="3" pivot="0" name="catalogo-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -839,18 +842,14 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="2" pivot="0" name="catalogo-style 5">
+      <tableStyleElement dxfId="3" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="catalogo-style 6">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 6">
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
     <tableStyle count="2" pivot="0" name="catalogo-style 7">
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-    </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 8">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
@@ -877,7 +876,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I53" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I61" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -893,17 +892,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C22" displayName="Table_10" name="Table_10" id="10">
-  <tableColumns count="1">
-    <tableColumn name="categoría" id="1"/>
-  </tableColumns>
-  <tableStyleInfo name="datos-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A54:I54" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I62" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -920,7 +910,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A55:I55" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I63" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -937,7 +927,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A56:I61" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I69" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -954,7 +944,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I68" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I83" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -971,7 +961,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I82" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A84:I84" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -988,7 +978,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A83:I83" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A85:I88" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1005,28 +995,20 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A84:I87" displayName="Table_8" name="Table_8" id="8">
-  <tableColumns count="9">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:A6" displayName="Table_8" name="Table_8" id="8">
+  <tableColumns count="1">
+    <tableColumn name="tipos" id="1"/>
   </tableColumns>
-  <tableStyleInfo name="catalogo-style 8" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="datos-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:A6" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C22" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="1">
-    <tableColumn name="tipos" id="1"/>
+    <tableColumn name="categoría" id="1"/>
   </tableColumns>
-  <tableStyleInfo name="datos-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="datos-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1283,7 +1265,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
@@ -1297,54 +1279,50 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
@@ -1353,42 +1331,40 @@
         <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>13.0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="3">
-        <v>25.0</v>
+        <v>13.0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -1397,19 +1373,17 @@
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>25.0</v>
+        <v>13.0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>10</v>
@@ -1418,69 +1392,73 @@
         <v>11</v>
       </c>
       <c r="D8" s="3">
-        <v>35.0</v>
+        <v>13.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="H8" s="2"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D10" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>36</v>
@@ -1488,300 +1466,313 @@
       <c r="F11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="H15" s="2"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D18" s="3">
         <v>30.0</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D19" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D21" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D22" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D23" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F24" s="2"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D25" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="F25" s="2"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -1789,145 +1780,134 @@
         <v>73</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D26" s="3">
         <v>25.0</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="1"/>
+      <c r="F26" s="2"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D27" s="3">
         <v>25.0</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>77</v>
+      <c r="E27" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D28" s="3">
         <v>25.0</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="D29" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D30" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="3">
         <v>25.0</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="3">
-        <v>20.0</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32">
       <c r="A32" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D32" s="3">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>88</v>
       </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -1935,13 +1915,13 @@
         <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D33" s="3">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>90</v>
@@ -1949,30 +1929,27 @@
       <c r="F33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
@@ -1981,19 +1958,19 @@
         <v>95</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D35" s="3">
         <v>25.0</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="4" t="s">
         <v>96</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="1"/>
+      <c r="G35" s="2"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
@@ -2002,10 +1979,10 @@
         <v>97</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D36" s="3">
         <v>25.0</v>
@@ -2013,7 +1990,6 @@
       <c r="E36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2023,19 +1999,18 @@
         <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D37" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="G37" s="2"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
@@ -2044,31 +2019,31 @@
         <v>101</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D39" s="3">
         <v>20.0</v>
@@ -2076,53 +2051,54 @@
       <c r="E39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D40" s="3">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="G41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
@@ -2131,82 +2107,77 @@
         <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D42" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D43" s="3">
         <v>25.0</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D44" s="3">
         <v>25.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D45" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2215,19 +2186,19 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D46" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2236,40 +2207,43 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D47" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D48" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2278,19 +2252,19 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D49" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2299,84 +2273,85 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D50" s="3">
         <v>25.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F50" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D51" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D52" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F52" s="2"/>
+      <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D53" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2385,19 +2360,19 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D54" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2406,19 +2381,19 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D55" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D55" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2427,170 +2402,168 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D56" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F56" s="2"/>
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D57" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>151</v>
       </c>
       <c r="D58" s="3">
-        <v>11.0</v>
+        <v>25.0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F58" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>151</v>
       </c>
       <c r="D59" s="3">
-        <v>11.0</v>
+        <v>30.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F59" s="5"/>
+        <v>154</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D60" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F60" s="5"/>
+      <c r="F60" s="2"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D61" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D62" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D62" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>163</v>
+        <v>27</v>
       </c>
       <c r="C63" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="D63" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -2599,141 +2572,146 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>163</v>
+        <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D64" s="3">
-        <v>13.0</v>
+        <v>30.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F64" s="1"/>
+        <v>166</v>
+      </c>
+      <c r="F64" s="2"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D65" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="1"/>
+        <v>170</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D66" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F66" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="F66" s="5"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D67" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F67" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D68" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F68" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="F68" s="5"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D69" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F69" s="2"/>
+      <c r="F69" s="5"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D70" s="3">
         <v>15.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="1"/>
@@ -2742,19 +2720,19 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D71" s="3">
         <v>15.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="1"/>
@@ -2763,19 +2741,19 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="1"/>
@@ -2784,39 +2762,40 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>191</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="F73" s="2"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -2824,40 +2803,39 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D75" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D75" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F75" s="2"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D76" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D76" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="1"/>
@@ -2866,16 +2844,16 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D77" s="3">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>199</v>
@@ -2887,16 +2865,16 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D78" s="3">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>200</v>
@@ -2908,19 +2886,19 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D79" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2929,19 +2907,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D80" s="3">
         <v>16.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2950,19 +2928,19 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D81" s="3">
         <v>16.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="1"/>
@@ -2971,19 +2949,19 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D82" s="3">
         <v>16.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="1"/>
@@ -2992,32 +2970,34 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D83" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D83" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F83" s="2"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D84" s="3">
         <v>12.0</v>
@@ -3030,102 +3010,113 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D85" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="F85" s="2"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" ht="14.25" customHeight="1">
+      <c r="A86" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D85" s="3">
+      <c r="B86" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D86" s="3">
         <v>13.0</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F85" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="F86" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="H85" s="4" t="s">
+      <c r="G86" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="s">
+      <c r="H86" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D86" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="5"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D87" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D87" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>225</v>
-      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
       <c r="H87" s="5"/>
       <c r="I87" s="1"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D88" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="H88" s="5"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D88" s="3">
+      <c r="B89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D89" s="3">
         <v>15.0</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
+      <c r="E89" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
     <row r="101" ht="14.25" customHeight="1"/>
     <row r="102" ht="14.25" customHeight="1"/>
     <row r="103" ht="14.25" customHeight="1"/>
@@ -4044,12 +4035,20 @@
     <row r="1016" ht="14.25" customHeight="1"/>
     <row r="1017" ht="14.25" customHeight="1"/>
     <row r="1018" ht="14.25" customHeight="1"/>
+    <row r="1019" ht="14.25" customHeight="1"/>
+    <row r="1020" ht="14.25" customHeight="1"/>
+    <row r="1021" ht="14.25" customHeight="1"/>
+    <row r="1022" ht="14.25" customHeight="1"/>
+    <row r="1023" ht="14.25" customHeight="1"/>
+    <row r="1024" ht="14.25" customHeight="1"/>
+    <row r="1025" ht="14.25" customHeight="1"/>
+    <row r="1026" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C88">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C89">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B88">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B89">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4057,15 +4056,14 @@
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
-  <tableParts count="8">
+  <tableParts count="7">
+    <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
     <tablePart r:id="rId15"/>
-    <tablePart r:id="rId16"/>
-    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4084,7 +4082,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4092,122 +4090,122 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="xBqBH6t+q+UJibfewq7dg927tUmlP0NWFnv+zSkvkGU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="hyUUJUoeOhLU/XFRbEnEqMrM381457Gm0KQi3jkbXoI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="239">
   <si>
     <t>nombre</t>
   </si>
@@ -175,6 +175,42 @@
     <t>chicago blanco k.jpg</t>
   </si>
   <si>
+    <t>Tenerife Pana</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>tenerife pana k.jpg</t>
+  </si>
+  <si>
+    <t>tenerife pana 2.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Naranja Bordado</t>
+  </si>
+  <si>
+    <t>tenerife naranja k.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Flores</t>
+  </si>
+  <si>
+    <t>tenerife verano k.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Rayas</t>
+  </si>
+  <si>
+    <t>tenerife rayas j.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Vintage</t>
+  </si>
+  <si>
+    <t>Tenerife vintage k.jpg</t>
+  </si>
+  <si>
     <t>Kioto Dorado</t>
   </si>
   <si>
@@ -259,30 +295,6 @@
     <t>Kioto zebra.jpg</t>
   </si>
   <si>
-    <t>Tenerife Pana</t>
-  </si>
-  <si>
-    <t>Tenerife</t>
-  </si>
-  <si>
-    <t>tenerife pana k.jpg</t>
-  </si>
-  <si>
-    <t>tenerife pana 2.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Naranja Bordado</t>
-  </si>
-  <si>
-    <t>tenerife naranja k.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Flores</t>
-  </si>
-  <si>
-    <t>tenerife verano k.jpg</t>
-  </si>
-  <si>
     <t>San Francisco</t>
   </si>
   <si>
@@ -365,6 +377,9 @@
   </si>
   <si>
     <t>Vancouver Vintage Rosa</t>
+  </si>
+  <si>
+    <t>vancouver vintage rosa k.jpg</t>
   </si>
   <si>
     <t>Vancouver Vintage Figuras</t>
@@ -876,7 +891,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I61" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I63" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -893,7 +908,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A62:I62" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I64" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -910,7 +925,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I63" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I65" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -927,7 +942,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I69" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I71" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -944,7 +959,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I83" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:I85" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -961,7 +976,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A84:I84" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I86" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -978,7 +993,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A85:I88" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I90" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1597,18 +1612,18 @@
       <c r="H17" s="2"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1" t="s">
+    <row r="18">
+      <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="3">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>53</v>
@@ -1616,42 +1631,30 @@
       <c r="F18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="F19" s="2"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
@@ -1660,44 +1663,38 @@
         <v>52</v>
       </c>
       <c r="D20" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D21" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
@@ -1706,46 +1703,52 @@
         <v>52</v>
       </c>
       <c r="D22" s="3">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>52</v>
+      <c r="A23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D23" s="3">
         <v>30.0</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" ht="15.0" customHeight="1">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>52</v>
+      <c r="C24" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D24" s="3">
         <v>30.0</v>
@@ -1753,107 +1756,123 @@
       <c r="E24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" ht="15.0" customHeight="1">
+    <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D25" s="3">
         <v>30.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>52</v>
+      <c r="C26" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D26" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D27" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D28" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D29" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="F29" s="2"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>83</v>
       </c>
@@ -1861,10 +1880,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D30" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>84</v>
@@ -1872,7 +1891,7 @@
       <c r="F30" s="2"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
@@ -1880,7 +1899,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D31" s="3">
         <v>25.0</v>
@@ -1891,7 +1910,7 @@
       <c r="F31" s="2"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>87</v>
       </c>
@@ -1899,7 +1918,7 @@
         <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D32" s="3">
         <v>25.0</v>
@@ -1918,7 +1937,7 @@
         <v>27</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D33" s="3">
         <v>25.0</v>
@@ -1926,71 +1945,68 @@
       <c r="E33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="2"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="B34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3">
         <v>25.0</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="1"/>
+      <c r="E34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="2"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D35" s="3">
         <v>25.0</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
+      <c r="E35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="I35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3">
         <v>25.0</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="2"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
@@ -2002,14 +2018,15 @@
         <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D37" s="3">
         <v>25.0</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="4" t="s">
         <v>100</v>
       </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2022,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D38" s="3">
         <v>25.0</v>
@@ -2030,7 +2047,6 @@
       <c r="E38" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2043,34 +2059,33 @@
         <v>27</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2079,129 +2094,131 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D41" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D42" s="3">
         <v>40.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F42" s="2"/>
-      <c r="G42" s="1"/>
+      <c r="G42" s="2"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="1"/>
+      <c r="G43" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D44" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D45" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F45" s="1"/>
+        <v>119</v>
+      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D46" s="3">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
@@ -2213,37 +2230,34 @@
         <v>27</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D47" s="3">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D48" s="3">
         <v>20.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2252,109 +2266,112 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D49" s="3">
         <v>20.0</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="G49" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="I49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D50" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D51" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>136</v>
-      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D52" s="3">
         <v>25.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F52" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D53" s="3">
         <v>25.0</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
@@ -2366,13 +2383,13 @@
         <v>27</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D54" s="3">
         <v>25.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2381,19 +2398,19 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D55" s="3">
         <v>25.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2402,19 +2419,19 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D56" s="3">
         <v>25.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2423,19 +2440,19 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D57" s="3">
         <v>25.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2444,13 +2461,13 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D58" s="3">
         <v>25.0</v>
@@ -2471,59 +2488,59 @@
         <v>27</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D59" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>155</v>
-      </c>
+      <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F60" s="2"/>
+      <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D61" s="3">
         <v>30.0</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2536,34 +2553,34 @@
         <v>27</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D62" s="3">
         <v>30.0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F62" s="1"/>
+        <v>163</v>
+      </c>
+      <c r="F62" s="2"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D63" s="3">
         <v>30.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -2572,104 +2589,104 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D64" s="3">
         <v>30.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F64" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>168</v>
+        <v>27</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D65" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D65" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>171</v>
-      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>168</v>
+        <v>27</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3">
-        <v>11.0</v>
+        <v>30.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F66" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="F66" s="2"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="D67" s="3">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F67" s="5"/>
-      <c r="G67" s="1"/>
+      <c r="F67" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D68" s="3">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="1"/>
@@ -2678,19 +2695,19 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D69" s="3">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="1"/>
@@ -2699,55 +2716,55 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D70" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F70" s="2"/>
+      <c r="F70" s="5"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D71" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F71" s="2"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
@@ -2765,16 +2782,16 @@
         <v>189</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="1"/>
@@ -2783,61 +2800,62 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="F74" s="2"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>194</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D76" s="3">
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F76" s="2"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2847,37 +2865,36 @@
         <v>198</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D77" s="3">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F77" s="2"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D78" s="3">
         <v>6.0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="1"/>
@@ -2886,19 +2903,19 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D79" s="3">
         <v>10.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2907,19 +2924,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D80" s="3">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2928,19 +2945,19 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D81" s="3">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="1"/>
@@ -2949,19 +2966,19 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D82" s="3">
         <v>16.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="1"/>
@@ -2970,19 +2987,19 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D83" s="3">
         <v>16.0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="1"/>
@@ -2991,134 +3008,174 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D84" s="3">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>212</v>
       </c>
       <c r="F84" s="2"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D85" s="3">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F85" s="2"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D86" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" ht="14.25" customHeight="1">
+      <c r="A87" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D86" s="3">
+      <c r="B87" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D87" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="A88" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D88" s="3">
         <v>13.0</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="s">
+      <c r="E88" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D87" s="3">
+      <c r="D89" s="3">
         <v>20.0</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D88" s="3">
+      <c r="E89" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D90" s="3">
         <v>9.0</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H88" s="5"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B89" s="2" t="s">
+      <c r="E90" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H90" s="5"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D89" s="3">
+      <c r="C91" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D91" s="3">
         <v>15.0</v>
       </c>
-      <c r="E89" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
+      <c r="E91" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
     <row r="103" ht="14.25" customHeight="1"/>
     <row r="104" ht="14.25" customHeight="1"/>
     <row r="105" ht="14.25" customHeight="1"/>
@@ -4043,12 +4100,14 @@
     <row r="1024" ht="14.25" customHeight="1"/>
     <row r="1025" ht="14.25" customHeight="1"/>
     <row r="1026" ht="14.25" customHeight="1"/>
+    <row r="1027" ht="14.25" customHeight="1"/>
+    <row r="1028" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C89">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C91">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B89">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B91">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4082,7 +4141,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4098,10 +4157,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -4109,38 +4168,38 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -4150,62 +4209,62 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="C20" s="2" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="hyUUJUoeOhLU/XFRbEnEqMrM381457Gm0KQi3jkbXoI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="OOpl6Ez51fyPdgQdgHxvN/Brm4/Wp9RzXqypP2zzWZE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="237">
   <si>
     <t>nombre</t>
   </si>
@@ -91,12 +91,6 @@
     <t>paris lila k.jpg</t>
   </si>
   <si>
-    <t>Paris Gorro Beige</t>
-  </si>
-  <si>
-    <t>paris beige.jpg</t>
-  </si>
-  <si>
     <t>paris colores</t>
   </si>
   <si>
@@ -190,7 +184,7 @@
     <t>Tenerife Naranja Bordado</t>
   </si>
   <si>
-    <t>tenerife naranja k.jpg</t>
+    <t>tenerife naranja ok.jpg</t>
   </si>
   <si>
     <t>Tenerife Flores</t>
@@ -202,13 +196,13 @@
     <t>Tenerife Rayas</t>
   </si>
   <si>
-    <t>tenerife rayas j.jpg</t>
+    <t>tenerife rayas k.jpg</t>
   </si>
   <si>
     <t>Tenerife Vintage</t>
   </si>
   <si>
-    <t>Tenerife vintage k.jpg</t>
+    <t>tenerife vintage k.jpg</t>
   </si>
   <si>
     <t>Kioto Dorado</t>
@@ -891,7 +885,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I63" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I62" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -908,7 +902,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I64" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I63" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -925,7 +919,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I65" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I64" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -942,7 +936,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I71" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I70" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -959,7 +953,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:I85" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:I84" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -976,7 +970,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I86" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A85:I85" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -993,7 +987,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I90" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I89" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1379,7 +1373,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -1391,142 +1385,144 @@
         <v>13.0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D9" s="3">
         <v>20.0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3">
         <v>20.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>20.0</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="F11" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D12" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="4" t="s">
+        <v>25.0</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>40</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D13" s="3">
         <v>25.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -1534,54 +1530,54 @@
         <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="3">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3">
         <v>35.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16" s="3">
-        <v>35.0</v>
+        <v>25.0</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>48</v>
@@ -1591,46 +1587,44 @@
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3">
         <v>28.0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="F18" s="2"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19">
@@ -1638,13 +1632,13 @@
         <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>56</v>
@@ -1652,15 +1646,15 @@
       <c r="F19" s="2"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3">
         <v>25.0</v>
@@ -1669,6 +1663,8 @@
         <v>58</v>
       </c>
       <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -1676,13 +1672,13 @@
         <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>60</v>
@@ -1693,75 +1689,75 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>52</v>
+      <c r="B22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D22" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="3">
         <v>30.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>68</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D24" s="3">
         <v>30.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
@@ -1770,10 +1766,10 @@
         <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D25" s="3">
         <v>30.0</v>
@@ -1781,33 +1777,32 @@
       <c r="E25" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D26" s="3">
         <v>30.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
@@ -1816,10 +1811,10 @@
         <v>77</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27" s="3">
         <v>30.0</v>
@@ -1827,19 +1822,21 @@
       <c r="E27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="F27" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D28" s="3">
         <v>30.0</v>
@@ -1847,10 +1844,7 @@
       <c r="E28" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="1"/>
+      <c r="F28" s="2"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
@@ -1858,10 +1852,10 @@
         <v>81</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3">
         <v>30.0</v>
@@ -1872,18 +1866,18 @@
       <c r="F29" s="2"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" ht="15.0" customHeight="1">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D30" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>84</v>
@@ -1896,10 +1890,10 @@
         <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31" s="3">
         <v>25.0</v>
@@ -1915,10 +1909,10 @@
         <v>87</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D32" s="3">
         <v>25.0</v>
@@ -1929,15 +1923,15 @@
       <c r="F32" s="2"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33">
       <c r="A33" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="D33" s="3">
         <v>25.0</v>
@@ -1948,15 +1942,15 @@
       <c r="F33" s="2"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D34" s="3">
         <v>25.0</v>
@@ -1964,49 +1958,51 @@
       <c r="E34" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D35" s="3">
         <v>25.0</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>94</v>
+      <c r="E35" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>95</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" s="3">
         <v>25.0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
@@ -2015,18 +2011,17 @@
         <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D37" s="3">
         <v>25.0</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2036,10 +2031,10 @@
         <v>101</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D38" s="3">
         <v>25.0</v>
@@ -2056,10 +2051,10 @@
         <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D39" s="3">
         <v>25.0</v>
@@ -2067,6 +2062,7 @@
       <c r="E39" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2076,16 +2072,16 @@
         <v>105</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D40" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2094,16 +2090,16 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D41" s="3">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>109</v>
@@ -2118,10 +2114,10 @@
         <v>110</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D42" s="3">
         <v>40.0</v>
@@ -2129,33 +2125,33 @@
       <c r="E42" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
+      <c r="F42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D43" s="3">
         <v>40.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G43" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
@@ -2164,13 +2160,13 @@
         <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D44" s="3">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>117</v>
@@ -2185,10 +2181,10 @@
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D45" s="3">
         <v>25.0</v>
@@ -2197,7 +2193,7 @@
         <v>119</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="1"/>
+      <c r="G45" s="2"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
@@ -2206,19 +2202,19 @@
         <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D46" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
@@ -2227,16 +2223,16 @@
         <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D47" s="3">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2245,13 +2241,13 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D48" s="3">
         <v>20.0</v>
@@ -2259,33 +2255,33 @@
       <c r="E48" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
+      <c r="F48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="I48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D49" s="3">
         <v>20.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G49" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
@@ -2293,10 +2289,10 @@
         <v>131</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D50" s="3">
         <v>20.0</v>
@@ -2314,76 +2310,76 @@
         <v>133</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D51" s="3">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F51" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D52" s="3">
         <v>25.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>139</v>
+      </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D53" s="3">
         <v>25.0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D54" s="3">
         <v>25.0</v>
@@ -2401,10 +2397,10 @@
         <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D55" s="3">
         <v>25.0</v>
@@ -2422,10 +2418,10 @@
         <v>147</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D56" s="3">
         <v>25.0</v>
@@ -2443,10 +2439,10 @@
         <v>149</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D57" s="3">
         <v>25.0</v>
@@ -2464,10 +2460,10 @@
         <v>151</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D58" s="3">
         <v>25.0</v>
@@ -2485,16 +2481,16 @@
         <v>153</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2503,57 +2499,57 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D60" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F60" s="1"/>
+      <c r="F60" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D61" s="3">
         <v>30.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>160</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="F61" s="2"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D62" s="3">
         <v>30.0</v>
@@ -2561,7 +2557,7 @@
       <c r="E62" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F62" s="2"/>
+      <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -2571,10 +2567,10 @@
         <v>164</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D63" s="3">
         <v>30.0</v>
@@ -2592,10 +2588,10 @@
         <v>166</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D64" s="3">
         <v>30.0</v>
@@ -2613,10 +2609,10 @@
         <v>168</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D65" s="3">
         <v>30.0</v>
@@ -2624,7 +2620,7 @@
       <c r="E65" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F65" s="1"/>
+      <c r="F65" s="2"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -2634,41 +2630,41 @@
         <v>170</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D66" s="3">
-        <v>30.0</v>
+        <v>9.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="1"/>
+        <v>173</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D67" s="3">
         <v>9.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F67" s="2" t="s">
         <v>176</v>
       </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
@@ -2677,10 +2673,10 @@
         <v>177</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D68" s="3">
         <v>9.0</v>
@@ -2698,10 +2694,10 @@
         <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D69" s="3">
         <v>9.0</v>
@@ -2719,10 +2715,10 @@
         <v>181</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D70" s="3">
         <v>9.0</v>
@@ -2740,37 +2736,37 @@
         <v>183</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D71" s="3">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F71" s="5"/>
+        <v>186</v>
+      </c>
+      <c r="F71" s="2"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="D72" s="3">
         <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="1"/>
@@ -2779,13 +2775,13 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
@@ -2803,10 +2799,10 @@
         <v>192</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
@@ -2824,10 +2820,10 @@
         <v>194</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
@@ -2835,7 +2831,6 @@
       <c r="E75" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F75" s="2"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2845,10 +2840,10 @@
         <v>196</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
@@ -2865,33 +2860,34 @@
         <v>198</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D77" s="3">
-        <v>15.0</v>
+        <v>6.0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="F77" s="2"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D78" s="3">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>202</v>
@@ -2903,19 +2899,19 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D79" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D79" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2924,19 +2920,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D80" s="3">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2945,16 +2941,16 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D81" s="3">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>206</v>
@@ -2969,10 +2965,10 @@
         <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D82" s="3">
         <v>16.0</v>
@@ -2990,10 +2986,10 @@
         <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D83" s="3">
         <v>16.0</v>
@@ -3011,10 +3007,10 @@
         <v>211</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D84" s="3">
         <v>16.0</v>
@@ -3032,85 +3028,85 @@
         <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D85" s="3">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F85" s="2"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D86" s="3">
         <v>12.0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F86" s="2"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D87" s="3">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E87" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="F87" s="2"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D88" s="3">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H88" s="4" t="s">
         <v>224</v>
       </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="5"/>
       <c r="I88" s="1"/>
     </row>
     <row r="89">
@@ -3118,64 +3114,44 @@
         <v>225</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D89" s="3">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="H89" s="5"/>
       <c r="I89" s="1"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="s">
-        <v>227</v>
+      <c r="A90" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>190</v>
+        <v>10</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D90" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H90" s="5"/>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="s">
+        <v>15.0</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D91" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
+    </row>
+    <row r="102" ht="14.25" customHeight="1"/>
     <row r="103" ht="14.25" customHeight="1"/>
     <row r="104" ht="14.25" customHeight="1"/>
     <row r="105" ht="14.25" customHeight="1"/>
@@ -4101,13 +4077,12 @@
     <row r="1025" ht="14.25" customHeight="1"/>
     <row r="1026" ht="14.25" customHeight="1"/>
     <row r="1027" ht="14.25" customHeight="1"/>
-    <row r="1028" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C91">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C90">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B91">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B90">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4141,7 +4116,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4149,18 +4124,18 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -4168,38 +4143,38 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -4209,62 +4184,62 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -655,7 +655,7 @@
     <t>conjunto roma terqueas k.jpg</t>
   </si>
   <si>
-    <t>Conjunto Roma Anarillo</t>
+    <t>Conjunto Roma Amarillo</t>
   </si>
   <si>
     <t>conjunto roma amarillo k.jpg</t>
@@ -2866,7 +2866,7 @@
         <v>199</v>
       </c>
       <c r="D77" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>200</v>
@@ -2908,7 +2908,7 @@
         <v>199</v>
       </c>
       <c r="D79" s="3">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>203</v>
@@ -2929,7 +2929,7 @@
         <v>199</v>
       </c>
       <c r="D80" s="3">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>204</v>
@@ -2950,7 +2950,7 @@
         <v>199</v>
       </c>
       <c r="D81" s="3">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>206</v>
@@ -2971,7 +2971,7 @@
         <v>199</v>
       </c>
       <c r="D82" s="3">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>208</v>
@@ -2992,7 +2992,7 @@
         <v>199</v>
       </c>
       <c r="D83" s="3">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>210</v>
@@ -3013,7 +3013,7 @@
         <v>199</v>
       </c>
       <c r="D84" s="3">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>212</v>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -574,49 +574,49 @@
     <t>Bogota colores</t>
   </si>
   <si>
+    <t>collar</t>
+  </si>
+  <si>
+    <t>Bogota</t>
+  </si>
+  <si>
+    <t>bogota colores.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Camel</t>
+  </si>
+  <si>
+    <t>Collar Bogota Camel.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Rojo</t>
+  </si>
+  <si>
+    <t>collar bogota rojo k.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Lima</t>
+  </si>
+  <si>
+    <t>collar bogota lima k.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota Azul</t>
+  </si>
+  <si>
+    <t>collar bogota azul k.jpg</t>
+  </si>
+  <si>
+    <t>Collar Bogota</t>
+  </si>
+  <si>
+    <t>collar bogota blanco k.jpg</t>
+  </si>
+  <si>
+    <t>Cuelgamovil Roma</t>
+  </si>
+  <si>
     <t>cuelgamovil</t>
-  </si>
-  <si>
-    <t>Bogota</t>
-  </si>
-  <si>
-    <t>bogota colores.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota Camel</t>
-  </si>
-  <si>
-    <t>collar</t>
-  </si>
-  <si>
-    <t>Collar Bogota Camel.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota Rojo</t>
-  </si>
-  <si>
-    <t>collar bogota rojo k.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota Lima</t>
-  </si>
-  <si>
-    <t>collar bogota lima k.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota Azul</t>
-  </si>
-  <si>
-    <t>collar bogota azul k.jpg</t>
-  </si>
-  <si>
-    <t>Collar Bogota</t>
-  </si>
-  <si>
-    <t>collar bogota blanco k.jpg</t>
-  </si>
-  <si>
-    <t>Cuelgamovil Roma</t>
   </si>
   <si>
     <t>Roma</t>
@@ -2757,7 +2757,7 @@
         <v>187</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>185</v>
@@ -2766,7 +2766,7 @@
         <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="1"/>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>185</v>
@@ -2787,7 +2787,7 @@
         <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="1"/>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>185</v>
@@ -2808,7 +2808,7 @@
         <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="1"/>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>185</v>
@@ -2829,7 +2829,7 @@
         <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>185</v>
@@ -2849,7 +2849,7 @@
         <v>15.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>199</v>
@@ -2881,7 +2881,7 @@
         <v>201</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>199</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>199</v>
@@ -2923,7 +2923,7 @@
         <v>201</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>199</v>
@@ -2944,7 +2944,7 @@
         <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>199</v>
@@ -2965,7 +2965,7 @@
         <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>199</v>
@@ -2986,7 +2986,7 @@
         <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>199</v>
@@ -3007,7 +3007,7 @@
         <v>211</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>199</v>
@@ -3028,7 +3028,7 @@
         <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>214</v>
@@ -3047,7 +3047,7 @@
         <v>213</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>214</v>
@@ -3066,7 +3066,7 @@
         <v>217</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>218</v>
@@ -3093,7 +3093,7 @@
         <v>223</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>218</v>
@@ -3114,7 +3114,7 @@
         <v>225</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>226</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>62</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>154</v>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -2908,7 +2908,7 @@
         <v>199</v>
       </c>
       <c r="D79" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>203</v>
@@ -2950,7 +2950,7 @@
         <v>199</v>
       </c>
       <c r="D81" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>206</v>
@@ -2971,7 +2971,7 @@
         <v>199</v>
       </c>
       <c r="D82" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>208</v>
@@ -2992,7 +2992,7 @@
         <v>199</v>
       </c>
       <c r="D83" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>210</v>
@@ -3013,7 +3013,7 @@
         <v>199</v>
       </c>
       <c r="D84" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>212</v>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="OOpl6Ez51fyPdgQdgHxvN/Brm4/Wp9RzXqypP2zzWZE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="KJSuP+6ql5nFDbhw6RVUwxDGzX1XUcfxeEm1c6KPCMc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="242">
   <si>
     <t>nombre</t>
   </si>
@@ -49,6 +49,147 @@
     <t>imagen5</t>
   </si>
   <si>
+    <t>Tenerife Pana</t>
+  </si>
+  <si>
+    <t>bolsos</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>tenerife pana k.jpg</t>
+  </si>
+  <si>
+    <t>tenerife pana 2.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Naranja Bordado</t>
+  </si>
+  <si>
+    <t>tenerife naranja ok.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Marrón Bordado</t>
+  </si>
+  <si>
+    <t>tenerife bordado marron.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Tie Die</t>
+  </si>
+  <si>
+    <t>tenerife tie die.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Primavera</t>
+  </si>
+  <si>
+    <t>tenerife primavera.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Flores</t>
+  </si>
+  <si>
+    <t>tenerife verano k.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Rayas</t>
+  </si>
+  <si>
+    <t>tenerife rayas k.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Vintage</t>
+  </si>
+  <si>
+    <t>tenerife vintage k.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Dorado</t>
+  </si>
+  <si>
+    <t>Kioto</t>
+  </si>
+  <si>
+    <t>kioto dorado k.jpg</t>
+  </si>
+  <si>
+    <t>kiotos.jpg</t>
+  </si>
+  <si>
+    <t>kioto dorado.jpg</t>
+  </si>
+  <si>
+    <t>kioto dorado 3.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Plateado</t>
+  </si>
+  <si>
+    <t>kioto plateado k.jpg</t>
+  </si>
+  <si>
+    <t>kioto plateado 2</t>
+  </si>
+  <si>
+    <t>Kioto Rosa Palo</t>
+  </si>
+  <si>
+    <t>kioto rosa palo fb.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Verde Claro</t>
+  </si>
+  <si>
+    <t>kioto verde claro k.jpg</t>
+  </si>
+  <si>
+    <t>kioto verde claro 2.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Burdeos</t>
+  </si>
+  <si>
+    <t>kioto burdeos fb.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Negro</t>
+  </si>
+  <si>
+    <t>kioto negro k.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Morado</t>
+  </si>
+  <si>
+    <t>kioto morado.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Dorado Metalizado</t>
+  </si>
+  <si>
+    <t>kioto brillante k.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Japo Beige</t>
+  </si>
+  <si>
+    <t>Kioto japo beige</t>
+  </si>
+  <si>
+    <t>Kioto Japo Sombrillas</t>
+  </si>
+  <si>
+    <t>Kioto japo sombrillas</t>
+  </si>
+  <si>
+    <t>Kioto Zebra</t>
+  </si>
+  <si>
+    <t>Kioto zebra.jpg</t>
+  </si>
+  <si>
     <t>Paris Gorro Marron</t>
   </si>
   <si>
@@ -97,9 +238,6 @@
     <t>Chicago Terciopelo Negro</t>
   </si>
   <si>
-    <t>bolsos</t>
-  </si>
-  <si>
     <t>Chicago</t>
   </si>
   <si>
@@ -169,126 +307,6 @@
     <t>chicago blanco k.jpg</t>
   </si>
   <si>
-    <t>Tenerife Pana</t>
-  </si>
-  <si>
-    <t>Tenerife</t>
-  </si>
-  <si>
-    <t>tenerife pana k.jpg</t>
-  </si>
-  <si>
-    <t>tenerife pana 2.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Naranja Bordado</t>
-  </si>
-  <si>
-    <t>tenerife naranja ok.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Flores</t>
-  </si>
-  <si>
-    <t>tenerife verano k.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Rayas</t>
-  </si>
-  <si>
-    <t>tenerife rayas k.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Vintage</t>
-  </si>
-  <si>
-    <t>tenerife vintage k.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Dorado</t>
-  </si>
-  <si>
-    <t>Kioto</t>
-  </si>
-  <si>
-    <t>kioto dorado k.jpg</t>
-  </si>
-  <si>
-    <t>kiotos.jpg</t>
-  </si>
-  <si>
-    <t>kioto dorado.jpg</t>
-  </si>
-  <si>
-    <t>kioto dorado 3.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Plateado</t>
-  </si>
-  <si>
-    <t>kioto plateado k.jpg</t>
-  </si>
-  <si>
-    <t>kioto plateado 2</t>
-  </si>
-  <si>
-    <t>Kioto Rosa Palo</t>
-  </si>
-  <si>
-    <t>kioto rosa palo fb.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Verde Claro</t>
-  </si>
-  <si>
-    <t>kioto verde claro k.jpg</t>
-  </si>
-  <si>
-    <t>kioto verde claro 2.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Burdeos</t>
-  </si>
-  <si>
-    <t>kioto burdeos fb.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Negro</t>
-  </si>
-  <si>
-    <t>kioto negro k.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Morado</t>
-  </si>
-  <si>
-    <t>kioto morado.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Dorado Metalizado</t>
-  </si>
-  <si>
-    <t>kioto brillante k.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Japo Beige</t>
-  </si>
-  <si>
-    <t>Kioto japo beige</t>
-  </si>
-  <si>
-    <t>Kioto Japo Sombrillas</t>
-  </si>
-  <si>
-    <t>Kioto japo sombrillas</t>
-  </si>
-  <si>
-    <t>Kioto Zebra</t>
-  </si>
-  <si>
-    <t>Kioto zebra.jpg</t>
-  </si>
-  <si>
     <t>San Francisco</t>
   </si>
   <si>
@@ -493,10 +511,7 @@
     <t>Munich Dorado Metalizado</t>
   </si>
   <si>
-    <t>munich dorado metalizado.jpg</t>
-  </si>
-  <si>
-    <t>munich dorado metalizado 2.jpg</t>
+    <t>munich doradoo brillante.jpg</t>
   </si>
   <si>
     <t>Niza Velvet Gris</t>
@@ -885,7 +900,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I62" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I65" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -902,7 +917,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A63:I63" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I66" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -919,7 +934,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I64" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I67" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -936,7 +951,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I70" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I73" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -953,7 +968,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:I84" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A74:I87" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -970,7 +985,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A85:I85" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A88:I88" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -987,7 +1002,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I89" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A89:I92" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1263,7 +1278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1274,7 +1289,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
@@ -1282,14 +1297,11 @@
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
@@ -1298,19 +1310,17 @@
         <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -1319,19 +1329,17 @@
         <v>11</v>
       </c>
       <c r="D4" s="3">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
@@ -1340,19 +1348,17 @@
         <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
@@ -1361,19 +1367,17 @@
         <v>11</v>
       </c>
       <c r="D6" s="3">
-        <v>13.0</v>
+        <v>28.0</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -1382,7 +1386,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>23</v>
@@ -1395,154 +1399,159 @@
         <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="D12" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D13" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="H14" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -1550,350 +1559,346 @@
         <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D15" s="3">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" ht="15.0" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="F16" s="2"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" ht="15.0" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="3">
         <v>25.0</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F18" s="2"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D19" s="3">
         <v>25.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F19" s="2"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3">
         <v>25.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="B22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="D22" s="3">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D23" s="3">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>69</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D25" s="3">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="F26" s="2"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="2"/>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>62</v>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="D31" s="3">
         <v>25.0</v>
@@ -1901,148 +1906,154 @@
       <c r="E31" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D32" s="3">
         <v>25.0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D33" s="3">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F33" s="2"/>
+      <c r="H33" s="2"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D34" s="3">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D35" s="3">
         <v>25.0</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="B36" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D36" s="3">
         <v>25.0</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>98</v>
+      <c r="E36" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D37" s="3">
         <v>25.0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D38" s="3">
         <v>25.0</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="2"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
@@ -2051,15 +2062,15 @@
         <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D39" s="3">
         <v>25.0</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F39" s="2"/>
@@ -2072,128 +2083,126 @@
         <v>105</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D43" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F43" s="2"/>
-      <c r="G43" s="1"/>
+      <c r="G43" s="2"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D44" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F44" s="2"/>
-      <c r="G44" s="1"/>
+      <c r="G44" s="2"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
@@ -2202,18 +2211,18 @@
         <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D46" s="3">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F46" s="1"/>
+      <c r="F46" s="2"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -2223,61 +2232,58 @@
         <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F47" s="1"/>
+      <c r="F47" s="2"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>128</v>
-      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D49" s="3">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2286,19 +2292,19 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D50" s="3">
         <v>20.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2307,64 +2313,64 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="G51" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D52" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>139</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D53" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2373,55 +2379,58 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54" s="3">
         <v>25.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F54" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D55" s="3">
         <v>25.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="D56" s="3">
         <v>25.0</v>
@@ -2439,10 +2448,10 @@
         <v>149</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D57" s="3">
         <v>25.0</v>
@@ -2460,10 +2469,10 @@
         <v>151</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D58" s="3">
         <v>25.0</v>
@@ -2481,16 +2490,16 @@
         <v>153</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2499,63 +2508,61 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D60" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D61" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F61" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D62" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -2564,10 +2571,10 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>160</v>
@@ -2576,155 +2583,155 @@
         <v>30.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>163</v>
+      </c>
+      <c r="F63" s="2"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D64" s="3">
         <v>30.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F64" s="1"/>
+        <v>166</v>
+      </c>
+      <c r="F64" s="2"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D65" s="3">
         <v>30.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F65" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D66" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D66" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D67" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D68" s="3">
-        <v>9.0</v>
+        <v>30.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F68" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="F68" s="2"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D69" s="3">
         <v>9.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="1"/>
+        <v>178</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D70" s="3">
         <v>9.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="1"/>
@@ -2733,82 +2740,82 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D71" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D71" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F71" s="2"/>
+      <c r="F71" s="5"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D72" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F72" s="2"/>
+      <c r="F72" s="5"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D73" s="3">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F73" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="F73" s="5"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="1"/>
@@ -2817,59 +2824,61 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>194</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D77" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="1"/>
@@ -2878,61 +2887,59 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D78" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D78" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F78" s="2"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D79" s="3">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F79" s="2"/>
+        <v>201</v>
+      </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D80" s="3">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2941,19 +2948,19 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D81" s="3">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="1"/>
@@ -2962,16 +2969,16 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D82" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>208</v>
@@ -2983,19 +2990,19 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D83" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D83" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="1"/>
@@ -3004,19 +3011,19 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D84" s="3">
         <v>11.0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="1"/>
@@ -3025,135 +3032,195 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D85" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F85" s="2"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D86" s="3">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F86" s="2"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D87" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C87" s="2" t="s">
+      <c r="F87" s="2"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="A88" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D87" s="3">
+      <c r="B88" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D88" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
+      <c r="A89" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
+      <c r="A90" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D90" s="3">
         <v>13.0</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="s">
+      <c r="E90" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D88" s="3">
+      <c r="D91" s="3">
         <v>20.0</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D89" s="3">
+      <c r="E91" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D92" s="3">
         <v>9.0</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H89" s="5"/>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D90" s="3">
+      <c r="E92" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H92" s="5"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D93" s="3">
         <v>15.0</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
+      <c r="E93" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
     <row r="105" ht="14.25" customHeight="1"/>
     <row r="106" ht="14.25" customHeight="1"/>
     <row r="107" ht="14.25" customHeight="1"/>
@@ -4077,12 +4144,15 @@
     <row r="1025" ht="14.25" customHeight="1"/>
     <row r="1026" ht="14.25" customHeight="1"/>
     <row r="1027" ht="14.25" customHeight="1"/>
+    <row r="1028" ht="14.25" customHeight="1"/>
+    <row r="1029" ht="14.25" customHeight="1"/>
+    <row r="1030" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C90">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C93">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B90">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B93">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4116,7 +4186,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4124,122 +4194,122 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -1289,7 +1289,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
@@ -1310,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -1329,7 +1329,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>17</v>
@@ -1348,7 +1348,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>19</v>
@@ -1367,7 +1367,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>21</v>
@@ -1386,7 +1386,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>23</v>
@@ -1405,7 +1405,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>25</v>
@@ -1426,7 +1426,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>27</v>
@@ -1901,7 +1901,7 @@
         <v>72</v>
       </c>
       <c r="D31" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>86</v>
@@ -1923,7 +1923,7 @@
         <v>72</v>
       </c>
       <c r="D32" s="3">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>89</v>
@@ -1985,7 +1985,7 @@
         <v>72</v>
       </c>
       <c r="D35" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>94</v>
@@ -2006,7 +2006,7 @@
         <v>95</v>
       </c>
       <c r="D36" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>96</v>
@@ -2025,7 +2025,7 @@
         <v>95</v>
       </c>
       <c r="D37" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>98</v>
@@ -2046,7 +2046,7 @@
         <v>95</v>
       </c>
       <c r="D38" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>101</v>
@@ -2068,7 +2068,7 @@
         <v>95</v>
       </c>
       <c r="D39" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>104</v>
@@ -2089,7 +2089,7 @@
         <v>95</v>
       </c>
       <c r="D40" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>106</v>
@@ -2109,7 +2109,7 @@
         <v>95</v>
       </c>
       <c r="D41" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>108</v>
@@ -2129,7 +2129,7 @@
         <v>95</v>
       </c>
       <c r="D42" s="3">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>110</v>
@@ -2301,7 +2301,7 @@
         <v>129</v>
       </c>
       <c r="D50" s="3">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>130</v>
@@ -2322,7 +2322,7 @@
         <v>129</v>
       </c>
       <c r="D51" s="3">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>132</v>
@@ -2346,7 +2346,7 @@
         <v>129</v>
       </c>
       <c r="D52" s="3">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>136</v>
@@ -2367,7 +2367,7 @@
         <v>129</v>
       </c>
       <c r="D53" s="3">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>138</v>
@@ -2388,7 +2388,7 @@
         <v>140</v>
       </c>
       <c r="D54" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>141</v>
@@ -2411,7 +2411,7 @@
         <v>140</v>
       </c>
       <c r="D55" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>144</v>
@@ -2706,7 +2706,7 @@
         <v>177</v>
       </c>
       <c r="D69" s="3">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>178</v>
@@ -2728,7 +2728,7 @@
         <v>177</v>
       </c>
       <c r="D70" s="3">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>181</v>
@@ -2749,7 +2749,7 @@
         <v>177</v>
       </c>
       <c r="D71" s="3">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>183</v>
@@ -2770,7 +2770,7 @@
         <v>177</v>
       </c>
       <c r="D72" s="3">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>185</v>
@@ -2791,7 +2791,7 @@
         <v>177</v>
       </c>
       <c r="D73" s="3">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>187</v>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="KJSuP+6ql5nFDbhw6RVUwxDGzX1XUcfxeEm1c6KPCMc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="hyUUJUoeOhLU/XFRbEnEqMrM381457Gm0KQi3jkbXoI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="238">
   <si>
     <t>nombre</t>
   </si>
@@ -64,19 +64,13 @@
     <t>tenerife pana 2.jpg</t>
   </si>
   <si>
-    <t>Tenerife Naranja Bordado</t>
-  </si>
-  <si>
-    <t>tenerife naranja ok.jpg</t>
-  </si>
-  <si>
     <t>Tenerife Marrón Bordado</t>
   </si>
   <si>
     <t>tenerife bordado marron.jpg</t>
   </si>
   <si>
-    <t>Tenerife Tie Die</t>
+    <t>Tenerife Tie Dye</t>
   </si>
   <si>
     <t>tenerife tie die.jpg</t>
@@ -92,12 +86,6 @@
   </si>
   <si>
     <t>tenerife verano k.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Rayas</t>
-  </si>
-  <si>
-    <t>tenerife rayas k.jpg</t>
   </si>
   <si>
     <t>Tenerife Vintage</t>
@@ -900,7 +888,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I65" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I63" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -917,7 +905,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I66" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I64" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -934,7 +922,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I67" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I65" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -951,7 +939,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I73" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I71" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -968,7 +956,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A74:I87" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:I85" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -985,7 +973,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A88:I88" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I86" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1002,7 +990,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A89:I92" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I90" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1375,7 +1363,7 @@
       <c r="F6" s="2"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -1392,149 +1380,151 @@
         <v>23</v>
       </c>
       <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>30.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D9" s="3">
         <v>30.0</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>29</v>
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D10" s="3">
         <v>30.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3">
         <v>30.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3">
         <v>30.0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
+      <c r="C13" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>42</v>
       </c>
@@ -1542,7 +1532,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
@@ -1550,11 +1540,10 @@
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="2"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
@@ -1562,7 +1551,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
@@ -1570,13 +1559,10 @@
       <c r="E15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="1"/>
+      <c r="F15" s="2"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" ht="15.0" customHeight="1">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
@@ -1584,10 +1570,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D16" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>47</v>
@@ -1595,7 +1581,7 @@
       <c r="F16" s="2"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" ht="15.0" customHeight="1">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
@@ -1603,10 +1589,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D17" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>49</v>
@@ -1622,7 +1608,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D18" s="3">
         <v>25.0</v>
@@ -1638,61 +1624,65 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3">
-        <v>25.0</v>
+        <v>13.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D20" s="3">
-        <v>25.0</v>
+        <v>13.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" s="3">
         <v>13.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
@@ -1700,10 +1690,10 @@
         <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D22" s="3">
         <v>13.0</v>
@@ -1711,7 +1701,7 @@
       <c r="E22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1721,10 +1711,10 @@
         <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D23" s="3">
         <v>13.0</v>
@@ -1732,201 +1722,200 @@
       <c r="E23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="1"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D24" s="3">
         <v>13.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="D25" s="3">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>58</v>
+      <c r="A26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D26" s="3">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>72</v>
+      <c r="C27" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D27" s="3">
         <v>20.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>72</v>
+      <c r="A28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="D28" s="3">
         <v>20.0</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="E28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D29" s="3">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G29" s="2"/>
+        <v>83</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D30" s="3">
         <v>20.0</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="1"/>
+      <c r="E30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="D31" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="H31" s="2"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1935,43 +1924,42 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34">
       <c r="A34" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
@@ -1982,78 +1970,79 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D35" s="3">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="I35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3">
         <v>28.0</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="2"/>
+      <c r="E36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D37" s="3">
         <v>28.0</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="E37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D38" s="3">
         <v>28.0</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>102</v>
       </c>
+      <c r="G38" s="2"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
@@ -2065,15 +2054,14 @@
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D39" s="3">
         <v>28.0</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2086,7 +2074,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
@@ -2094,6 +2082,7 @@
       <c r="E40" s="2" t="s">
         <v>106</v>
       </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2106,33 +2095,34 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D41" s="3">
-        <v>28.0</v>
+        <v>20.0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D42" s="3">
-        <v>28.0</v>
+        <v>40.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -2141,68 +2131,68 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D43" s="3">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D44" s="3">
         <v>40.0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D45" s="3">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G45" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
@@ -2214,16 +2204,16 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D46" s="3">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>121</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="1"/>
+      <c r="G46" s="2"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
@@ -2235,15 +2225,15 @@
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D47" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F47" s="2"/>
+      <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2256,55 +2246,58 @@
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D48" s="3">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D49" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="I49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D50" s="3">
         <v>22.0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2313,26 +2306,23 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D51" s="3">
         <v>22.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G51" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -2343,94 +2333,94 @@
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D52" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F52" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D53" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D54" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>142</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="D55" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D56" s="3">
         <v>25.0</v>
@@ -2451,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D57" s="3">
         <v>25.0</v>
@@ -2472,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D58" s="3">
         <v>25.0</v>
@@ -2493,7 +2483,7 @@
         <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
@@ -2514,13 +2504,13 @@
         <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D60" s="3">
         <v>25.0</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -2529,76 +2519,76 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D61" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F61" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="F61" s="2"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D62" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F62" s="1"/>
+        <v>162</v>
+      </c>
+      <c r="F62" s="2"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D63" s="3">
         <v>30.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F63" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D64" s="3">
         <v>30.0</v>
@@ -2606,7 +2596,7 @@
       <c r="E64" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F64" s="2"/>
+      <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -2619,7 +2609,7 @@
         <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D65" s="3">
         <v>30.0</v>
@@ -2640,7 +2630,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D66" s="3">
         <v>30.0</v>
@@ -2648,7 +2638,7 @@
       <c r="E66" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F66" s="1"/>
+      <c r="F66" s="2"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -2658,62 +2648,62 @@
         <v>171</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D67" s="3">
-        <v>30.0</v>
+        <v>12.0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
+        <v>174</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D68" s="3">
-        <v>30.0</v>
+        <v>12.0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F68" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="F68" s="5"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D69" s="3">
         <v>12.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F69" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
@@ -2722,10 +2712,10 @@
         <v>180</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D70" s="3">
         <v>12.0</v>
@@ -2743,10 +2733,10 @@
         <v>182</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D71" s="3">
         <v>12.0</v>
@@ -2764,52 +2754,52 @@
         <v>184</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D72" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F72" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="F72" s="2"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="D73" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F73" s="5"/>
+        <v>189</v>
+      </c>
+      <c r="F73" s="2"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
@@ -2827,10 +2817,10 @@
         <v>192</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
@@ -2848,10 +2838,10 @@
         <v>194</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
@@ -2859,7 +2849,6 @@
       <c r="E76" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F76" s="2"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2869,10 +2858,10 @@
         <v>196</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D77" s="3">
         <v>15.0</v>
@@ -2880,7 +2869,6 @@
       <c r="E77" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F77" s="2"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2890,56 +2878,58 @@
         <v>198</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D78" s="3">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="F78" s="2"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="D79" s="3">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F79" s="2"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D80" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="D80" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2948,19 +2938,19 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D81" s="3">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="1"/>
@@ -2969,19 +2959,19 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D82" s="3">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="1"/>
@@ -2990,16 +2980,16 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D83" s="3">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>209</v>
@@ -3014,10 +3004,10 @@
         <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D84" s="3">
         <v>11.0</v>
@@ -3035,10 +3025,10 @@
         <v>212</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D85" s="3">
         <v>11.0</v>
@@ -3056,41 +3046,37 @@
         <v>214</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D86" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F86" s="2"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D87" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>217</v>
       </c>
       <c r="F87" s="2"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -3098,129 +3084,93 @@
         <v>218</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>219</v>
       </c>
       <c r="D88" s="3">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F88" s="2"/>
+      <c r="F88" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>223</v>
+      </c>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89">
       <c r="A89" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>219</v>
       </c>
       <c r="D89" s="3">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="5"/>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90">
       <c r="A90" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D90" s="3">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>227</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H90" s="5"/>
       <c r="I90" s="1"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="s">
-        <v>228</v>
+      <c r="A91" s="4" t="s">
+        <v>231</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D91" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D92" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F92" s="2" t="s">
+        <v>15.0</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H92" s="5"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D93" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
+    </row>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
     <row r="105" ht="14.25" customHeight="1"/>
     <row r="106" ht="14.25" customHeight="1"/>
     <row r="107" ht="14.25" customHeight="1"/>
@@ -4145,14 +4095,12 @@
     <row r="1026" ht="14.25" customHeight="1"/>
     <row r="1027" ht="14.25" customHeight="1"/>
     <row r="1028" ht="14.25" customHeight="1"/>
-    <row r="1029" ht="14.25" customHeight="1"/>
-    <row r="1030" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C93">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C91">
       <formula1>datos!$C$2:$C$22</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B93">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B91">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4186,7 +4134,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4197,104 +4145,104 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4304,12 +4252,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -3168,6 +3168,9 @@
       <c r="E91" s="4" t="s">
         <v>233</v>
       </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4"/>
     </row>
     <row r="103" ht="14.25" customHeight="1"/>
     <row r="104" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="hyUUJUoeOhLU/XFRbEnEqMrM381457Gm0KQi3jkbXoI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="jmReSprLFD8W0mrXhbKIKvwUEK1k6tyhzL57Ki2gb7Y="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="241">
   <si>
     <t>nombre</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>tenerife vintage k.jpg</t>
+  </si>
+  <si>
+    <t>Pontevedra Negro</t>
+  </si>
+  <si>
+    <t>Pontevedra</t>
+  </si>
+  <si>
+    <t>pontevedra negro.jpg</t>
   </si>
   <si>
     <t>Kioto Dorado</t>
@@ -888,7 +897,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I63" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I64" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -905,7 +914,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A64:I64" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I65" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -922,7 +931,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I65" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I66" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -939,7 +948,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I71" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I72" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -956,7 +965,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:I85" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A73:I86" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -973,7 +982,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A86:I86" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I87" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -990,7 +999,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I90" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A88:I91" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1016,7 +1025,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C22" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C23" displayName="Table_9" name="Table_9" id="9">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -1385,55 +1394,51 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D9" s="3">
         <v>30.0</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -1443,8 +1448,8 @@
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>25</v>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D10" s="3">
         <v>30.0</v>
@@ -1452,33 +1457,33 @@
       <c r="E10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
+      <c r="C11" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D11" s="3">
         <v>30.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
@@ -1489,8 +1494,8 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>30.0</v>
@@ -1498,187 +1503,191 @@
       <c r="E12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="F12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" ht="15.0" customHeight="1">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="2"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D16" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="2"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3">
         <v>25.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D18" s="3">
         <v>25.0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="F19" s="2"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3">
         <v>13.0</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="G20" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3">
         <v>13.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1687,40 +1696,40 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D22" s="3">
         <v>13.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D23" s="3">
         <v>13.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="1"/>
@@ -1729,79 +1738,77 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D24" s="3">
         <v>13.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F24" s="2"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="2"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="D26" s="3">
         <v>20.0</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D27" s="3">
         <v>20.0</v>
@@ -1813,7 +1820,7 @@
         <v>77</v>
       </c>
       <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
+      <c r="H27" s="2"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
@@ -1823,18 +1830,19 @@
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>68</v>
+      <c r="C28" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D28" s="3">
         <v>20.0</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="G28" s="2"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
@@ -1842,19 +1850,19 @@
       <c r="A29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>68</v>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="D29" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E29" s="2" t="s">
+        <v>20.0</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="4" t="s">
         <v>83</v>
       </c>
       <c r="H29" s="1"/>
@@ -1864,61 +1872,62 @@
       <c r="A30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>68</v>
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D30" s="3">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D31" s="3">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D32" s="3">
         <v>35.0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
     </row>
@@ -1930,57 +1939,57 @@
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D33" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D34" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D35" s="3">
         <v>28.0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="F35" s="2"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -1991,18 +2000,17 @@
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D36" s="3">
         <v>28.0</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="2" t="s">
         <v>97</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -2013,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D37" s="3">
         <v>28.0</v>
@@ -2021,46 +2029,48 @@
       <c r="E37" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="F37" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D38" s="3">
         <v>28.0</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="E38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D39" s="3">
         <v>28.0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
@@ -2068,37 +2078,36 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" s="2"/>
+        <v>107</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D41" s="3">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>109</v>
@@ -2116,13 +2125,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D42" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -2131,65 +2140,65 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D43" s="3">
         <v>40.0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F43" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D44" s="3">
         <v>40.0</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="1"/>
+      <c r="G44" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D45" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="1"/>
@@ -2198,58 +2207,58 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D46" s="3">
         <v>25.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
+      <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D47" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+        <v>124</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D48" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>126</v>
@@ -2267,58 +2276,58 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D49" s="3">
         <v>22.0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F49" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D50" s="3">
         <v>22.0</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
+      <c r="G50" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D51" s="3">
         <v>22.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2327,36 +2336,34 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D52" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>138</v>
-      </c>
+      <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="D53" s="3">
         <v>30.0</v>
@@ -2367,6 +2374,7 @@
       <c r="F53" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
@@ -2378,16 +2386,17 @@
         <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D54" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
@@ -2399,13 +2408,13 @@
         <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D55" s="3">
         <v>25.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2414,19 +2423,19 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D56" s="3">
         <v>25.0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2435,19 +2444,19 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D57" s="3">
         <v>25.0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2456,19 +2465,19 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D58" s="3">
         <v>25.0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -2477,19 +2486,19 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2498,13 +2507,13 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D60" s="3">
         <v>25.0</v>
@@ -2525,28 +2534,28 @@
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D61" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F61" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D62" s="3">
         <v>30.0</v>
@@ -2567,34 +2576,34 @@
         <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D63" s="3">
         <v>30.0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F63" s="1"/>
+        <v>165</v>
+      </c>
+      <c r="F63" s="2"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D64" s="3">
         <v>30.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2603,19 +2612,19 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D65" s="3">
         <v>30.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -2624,56 +2633,55 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D66" s="3">
         <v>30.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F66" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D67" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D68" s="3">
         <v>12.0</v>
@@ -2681,26 +2689,27 @@
       <c r="E68" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F68" s="5"/>
-      <c r="G68" s="1"/>
+      <c r="F68" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D69" s="3">
         <v>12.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="1"/>
@@ -2709,19 +2718,19 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D70" s="3">
         <v>12.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="1"/>
@@ -2730,19 +2739,19 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D71" s="3">
         <v>12.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="1"/>
@@ -2751,40 +2760,40 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D72" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D72" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F72" s="2"/>
+      <c r="F72" s="5"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="C73" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D73" s="3">
         <v>15.0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="1"/>
@@ -2793,19 +2802,19 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D74" s="3">
         <v>15.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="1"/>
@@ -2814,19 +2823,19 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="1"/>
@@ -2835,39 +2844,40 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D77" s="3">
         <v>15.0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -2875,40 +2885,39 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D78" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F78" s="2"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="C79" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D79" s="3">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2917,19 +2926,19 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D80" s="3">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="1"/>
@@ -2938,19 +2947,19 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="C81" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D81" s="3">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="1"/>
@@ -2959,19 +2968,19 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D82" s="3">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="1"/>
@@ -2980,19 +2989,19 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D83" s="3">
         <v>11.0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="1"/>
@@ -3001,19 +3010,19 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D84" s="3">
         <v>11.0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="1"/>
@@ -3022,19 +3031,19 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D85" s="3">
         <v>11.0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="1"/>
@@ -3043,139 +3052,223 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D86" s="3">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>216</v>
       </c>
       <c r="F86" s="2"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D87" s="3">
         <v>12.0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F87" s="2"/>
       <c r="I87" s="1"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="D88" s="3">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="F88" s="2"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
+      <c r="A89" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="B89" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="H88" s="4" t="s">
+      <c r="D89" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="s">
+      <c r="F89" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D89" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="G89" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="5"/>
+      <c r="H89" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="I89" s="1"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D90" s="3">
-        <v>9.0</v>
+        <v>20.0</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
       <c r="H90" s="5"/>
       <c r="I90" s="1"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D91" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D91" s="3">
+      <c r="G91" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H91" s="5"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D92" s="3">
         <v>15.0</v>
       </c>
-      <c r="E91" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
+      <c r="E92" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="3"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="3"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="3"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="3"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="3"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="3"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="3"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="3"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="3"/>
+    </row>
     <row r="107" ht="14.25" customHeight="1"/>
     <row r="108" ht="14.25" customHeight="1"/>
     <row r="109" ht="14.25" customHeight="1"/>
@@ -4098,13 +4191,14 @@
     <row r="1026" ht="14.25" customHeight="1"/>
     <row r="1027" ht="14.25" customHeight="1"/>
     <row r="1028" ht="14.25" customHeight="1"/>
+    <row r="1029" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C91">
-      <formula1>datos!$C$2:$C$22</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B106">
+      <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B91">
-      <formula1>datos!$A$2:$A$6</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C106">
+      <formula1>datos!$C$2:$C$23</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -4137,7 +4231,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4148,104 +4242,104 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4255,15 +4349,19 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="C23" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="24" ht="14.25" customHeight="1"/>
     <row r="25" ht="14.25" customHeight="1"/>
     <row r="26" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="jmReSprLFD8W0mrXhbKIKvwUEK1k6tyhzL57Ki2gb7Y="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="wj72iILHmE/3kbSjNXtec8XJurz0B2m7eaqfHBSE/1Y="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="247">
   <si>
     <t>nombre</t>
   </si>
@@ -94,6 +94,12 @@
     <t>tenerife vintage k.jpg</t>
   </si>
   <si>
+    <t>Tenerife Lentejuelas Plateado</t>
+  </si>
+  <si>
+    <t>Tenerife lentejuelas plateado.jpg</t>
+  </si>
+  <si>
     <t>Pontevedra Negro</t>
   </si>
   <si>
@@ -103,6 +109,12 @@
     <t>pontevedra negro.jpg</t>
   </si>
   <si>
+    <t>Pontevedra Beige</t>
+  </si>
+  <si>
+    <t>pontevedra beige.jpg</t>
+  </si>
+  <si>
     <t>Kioto Dorado</t>
   </si>
   <si>
@@ -352,10 +364,16 @@
     <t>Sf fucsia</t>
   </si>
   <si>
+    <t>Vancouver Icon</t>
+  </si>
+  <si>
+    <t>Vancouver</t>
+  </si>
+  <si>
+    <t>vancouver icon.jpg</t>
+  </si>
+  <si>
     <t>Vancouver Rafia Verde</t>
-  </si>
-  <si>
-    <t>Vancouver</t>
   </si>
   <si>
     <t>vancouver rafia.jpg</t>
@@ -897,7 +915,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I64" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I67" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -914,7 +932,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A65:I65" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I68" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -931,7 +949,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A66:I66" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I69" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -948,7 +966,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A67:I72" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I75" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -965,7 +983,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A73:I86" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A76:I89" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -982,7 +1000,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A87:I87" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A90:I90" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -999,7 +1017,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A88:I91" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A91:I94" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1401,13 +1419,13 @@
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>38.0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1415,146 +1433,146 @@
       <c r="I8" s="1"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D10" s="3">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="1"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D11" s="3">
         <v>30.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3">
         <v>30.0</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" ht="15.0" customHeight="1">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>45</v>
       </c>
@@ -1562,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
@@ -1570,10 +1588,11 @@
       <c r="E15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" ht="15.0" customHeight="1">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>47</v>
       </c>
@@ -1581,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D16" s="3">
         <v>30.0</v>
@@ -1589,10 +1608,13 @@
       <c r="E16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1600,10 +1622,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D17" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>50</v>
@@ -1611,7 +1633,7 @@
       <c r="F17" s="2"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
@@ -1619,10 +1641,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D18" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>52</v>
@@ -1638,7 +1660,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" s="3">
         <v>25.0</v>
@@ -1654,65 +1676,61 @@
         <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="D21" s="3">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="F21" s="2"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3">
         <v>13.0</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -1720,10 +1738,10 @@
         <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D23" s="3">
         <v>13.0</v>
@@ -1731,7 +1749,7 @@
       <c r="E23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="2"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1741,10 +1759,10 @@
         <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D24" s="3">
         <v>13.0</v>
@@ -1752,200 +1770,201 @@
       <c r="E24" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D25" s="3">
         <v>13.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F25" s="2"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D26" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="2"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="F27" s="2"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>71</v>
+      <c r="C28" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="D28" s="3">
         <v>20.0</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>71</v>
+      <c r="B29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D29" s="3">
         <v>20.0</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" s="1"/>
+      <c r="E29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
       <c r="I29" s="1"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="G30" s="2"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D31" s="3">
         <v>20.0</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
+      <c r="E31" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D33" s="3">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1954,42 +1973,43 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D35" s="3">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>95</v>
       </c>
       <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -2000,79 +2020,78 @@
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D36" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3">
         <v>28.0</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H37" s="1"/>
+      <c r="E37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="2"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D38" s="3">
         <v>28.0</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="1"/>
+      <c r="E38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D39" s="3">
         <v>28.0</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G39" s="2"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
@@ -2084,14 +2103,15 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="4" t="s">
         <v>107</v>
       </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2104,7 +2124,7 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
@@ -2112,7 +2132,6 @@
       <c r="E41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2125,34 +2144,33 @@
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D42" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -2161,89 +2179,89 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="D44" s="3">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D45" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="1"/>
+      <c r="G45" s="2"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D46" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="1"/>
+      <c r="G46" s="2"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D47" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
@@ -2255,15 +2273,15 @@
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D48" s="3">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="1"/>
+      <c r="F48" s="2"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -2276,58 +2294,55 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D49" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F49" s="1"/>
+      <c r="F49" s="2"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D51" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2336,19 +2351,19 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D52" s="3">
         <v>22.0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -2357,64 +2372,64 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" s="3">
+        <v>22.0</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="G53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D54" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D55" s="3">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2423,55 +2438,58 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F56" s="1"/>
+      <c r="F56" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D57" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="D58" s="3">
         <v>25.0</v>
@@ -2492,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
@@ -2513,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D60" s="3">
         <v>25.0</v>
@@ -2534,13 +2552,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D61" s="3">
         <v>25.0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -2549,61 +2567,61 @@
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D62" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F62" s="2"/>
+      <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D63" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D63" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F63" s="2"/>
+      <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D64" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D64" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2612,34 +2630,34 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D65" s="3">
         <v>30.0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F65" s="1"/>
+        <v>168</v>
+      </c>
+      <c r="F65" s="2"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="D66" s="3">
         <v>30.0</v>
@@ -2647,7 +2665,7 @@
       <c r="E66" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F66" s="1"/>
+      <c r="F66" s="2"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -2660,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D67" s="3">
         <v>30.0</v>
@@ -2668,7 +2686,7 @@
       <c r="E67" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F67" s="2"/>
+      <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -2678,83 +2696,83 @@
         <v>174</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D68" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D68" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D69" s="3">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F69" s="5"/>
+        <v>177</v>
+      </c>
+      <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D70" s="3">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F70" s="5"/>
+        <v>179</v>
+      </c>
+      <c r="F70" s="2"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D71" s="3">
         <v>12.0</v>
       </c>
       <c r="E71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F71" s="5"/>
-      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
@@ -2763,10 +2781,10 @@
         <v>185</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D72" s="3">
         <v>12.0</v>
@@ -2784,73 +2802,73 @@
         <v>187</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D73" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D73" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F73" s="2"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D74" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F74" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="F74" s="5"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D75" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F75" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="F75" s="5"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
@@ -2868,10 +2886,10 @@
         <v>197</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D77" s="3">
         <v>15.0</v>
@@ -2879,6 +2897,7 @@
       <c r="E77" s="2" t="s">
         <v>198</v>
       </c>
+      <c r="F77" s="2"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2888,10 +2907,10 @@
         <v>199</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D78" s="3">
         <v>15.0</v>
@@ -2899,6 +2918,7 @@
       <c r="E78" s="2" t="s">
         <v>200</v>
       </c>
+      <c r="F78" s="2"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2908,16 +2928,16 @@
         <v>201</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D79" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D79" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="1"/>
@@ -2926,61 +2946,59 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D80" s="3">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F80" s="2"/>
+        <v>204</v>
+      </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D81" s="3">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F81" s="2"/>
+        <v>206</v>
+      </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D82" s="3">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="1"/>
@@ -2989,19 +3007,19 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="D83" s="3">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="1"/>
@@ -3010,19 +3028,19 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D84" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="1"/>
@@ -3031,16 +3049,16 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D85" s="3">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>214</v>
@@ -3055,10 +3073,10 @@
         <v>215</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D86" s="3">
         <v>11.0</v>
@@ -3076,37 +3094,41 @@
         <v>217</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D87" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D87" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F87" s="2"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D88" s="3">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>220</v>
       </c>
       <c r="F88" s="2"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
       <c r="I88" s="1"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -3114,105 +3136,149 @@
         <v>221</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D89" s="3">
+      <c r="F89" s="2"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
+      <c r="A90" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D90" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" ht="14.25" customHeight="1">
+      <c r="A91" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D92" s="3">
         <v>13.0</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D90" s="3">
+      <c r="E92" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D93" s="3">
         <v>20.0</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D91" s="3">
+      <c r="E93" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D94" s="3">
         <v>9.0</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H91" s="5"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D92" s="3">
+      <c r="E94" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D95" s="3">
         <v>15.0</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="3"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="3"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="3"/>
+      <c r="E95" s="4" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="2"/>
@@ -3269,9 +3335,21 @@
       <c r="C106" s="2"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="107">
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="3"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="3"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="3"/>
+    </row>
     <row r="110" ht="14.25" customHeight="1"/>
     <row r="111" ht="14.25" customHeight="1"/>
     <row r="112" ht="14.25" customHeight="1"/>
@@ -4192,12 +4270,15 @@
     <row r="1027" ht="14.25" customHeight="1"/>
     <row r="1028" ht="14.25" customHeight="1"/>
     <row r="1029" ht="14.25" customHeight="1"/>
+    <row r="1030" ht="14.25" customHeight="1"/>
+    <row r="1031" ht="14.25" customHeight="1"/>
+    <row r="1032" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B106">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B109">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C106">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C109">
       <formula1>datos!$C$2:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -4231,7 +4312,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4242,104 +4323,104 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4349,17 +4430,17 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -364,7 +364,7 @@
     <t>Sf fucsia</t>
   </si>
   <si>
-    <t>Vancouver Icon</t>
+    <t>Vancouver Lux</t>
   </si>
   <si>
     <t>Vancouver</t>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="wj72iILHmE/3kbSjNXtec8XJurz0B2m7eaqfHBSE/1Y="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="Rhq3LPhHXaijst1qpkJ1zxPCVpswki5++27SWyObVOg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="245">
   <si>
     <t>nombre</t>
   </si>
@@ -49,39 +49,39 @@
     <t>imagen5</t>
   </si>
   <si>
+    <t>Tenerife Primavera</t>
+  </si>
+  <si>
+    <t>bolsos</t>
+  </si>
+  <si>
+    <t>Tenerife</t>
+  </si>
+  <si>
+    <t>tenerife primavera.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Marrón Bordado</t>
+  </si>
+  <si>
+    <t>tenerife bordado marron.jpg</t>
+  </si>
+  <si>
+    <t>Tenerife Tie Dye</t>
+  </si>
+  <si>
+    <t>tenerife tie die.jpg</t>
+  </si>
+  <si>
     <t>Tenerife Pana</t>
   </si>
   <si>
-    <t>bolsos</t>
-  </si>
-  <si>
-    <t>Tenerife</t>
-  </si>
-  <si>
     <t>tenerife pana k.jpg</t>
   </si>
   <si>
     <t>tenerife pana 2.jpg</t>
   </si>
   <si>
-    <t>Tenerife Marrón Bordado</t>
-  </si>
-  <si>
-    <t>tenerife bordado marron.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Tie Dye</t>
-  </si>
-  <si>
-    <t>tenerife tie die.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Primavera</t>
-  </si>
-  <si>
-    <t>tenerife primavera.jpg</t>
-  </si>
-  <si>
     <t>Tenerife Flores</t>
   </si>
   <si>
@@ -115,12 +115,18 @@
     <t>pontevedra beige.jpg</t>
   </si>
   <si>
+    <t>Kioto Dorado Lux</t>
+  </si>
+  <si>
+    <t>Kioto</t>
+  </si>
+  <si>
+    <t>Kioto Dorado lux.jpg</t>
+  </si>
+  <si>
     <t>Kioto Dorado</t>
   </si>
   <si>
-    <t>Kioto</t>
-  </si>
-  <si>
     <t>kioto dorado k.jpg</t>
   </si>
   <si>
@@ -361,7 +367,7 @@
     <t>San Francisco Cotton Fucsia</t>
   </si>
   <si>
-    <t>Sf fucsia</t>
+    <t>San Fran fucsia</t>
   </si>
   <si>
     <t>Vancouver Lux</t>
@@ -538,18 +544,6 @@
     <t>niza velvet gris.jpg</t>
   </si>
   <si>
-    <t>Niza Velvet Teja</t>
-  </si>
-  <si>
-    <t>niza velvet teja.jpg</t>
-  </si>
-  <si>
-    <t>Niza Velvet Mora</t>
-  </si>
-  <si>
-    <t>niza velvet mora.jpg</t>
-  </si>
-  <si>
     <t>Niza Velvet Topo</t>
   </si>
   <si>
@@ -610,7 +604,7 @@
     <t>Bogota</t>
   </si>
   <si>
-    <t>bogota colores.jpg</t>
+    <t>Bogota colores.jpg</t>
   </si>
   <si>
     <t>Collar Bogota Camel</t>
@@ -862,7 +856,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="9">
+  <tableStyles count="8">
     <tableStyle count="3" pivot="0" name="catalogo-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
@@ -877,18 +871,14 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="2" pivot="0" name="catalogo-style 4">
+      <tableStyleElement dxfId="3" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="catalogo-style 5">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 5">
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
     <tableStyle count="2" pivot="0" name="catalogo-style 6">
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-    </tableStyle>
-    <tableStyle count="2" pivot="0" name="catalogo-style 7">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
@@ -949,7 +939,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I69" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I74" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -966,7 +956,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:I75" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A75:I88" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -983,7 +973,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A76:I89" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A89:I89" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1000,7 +990,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A90:I90" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A90:I93" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="9">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1017,24 +1007,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A91:I94" displayName="Table_7" name="Table_7" id="7">
-  <tableColumns count="9">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
-    <tableColumn name="Column7" id="7"/>
-    <tableColumn name="Column8" id="8"/>
-    <tableColumn name="Column9" id="9"/>
-  </tableColumns>
-  <tableStyleInfo name="catalogo-style 7" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:A6" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:A6" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="1">
     <tableColumn name="tipos" id="1"/>
   </tableColumns>
@@ -1042,8 +1015,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C23" displayName="Table_9" name="Table_9" id="9">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C23" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -1309,14 +1282,12 @@
       <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="F2" s="2"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
@@ -1328,14 +1299,14 @@
         <v>30.0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -1347,14 +1318,14 @@
         <v>30.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
@@ -1366,9 +1337,11 @@
         <v>30.0</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6">
@@ -1475,37 +1448,31 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1515,35 +1482,41 @@
         <v>30.0</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
@@ -1554,7 +1527,7 @@
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="3">
@@ -1563,32 +1536,33 @@
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
@@ -1608,13 +1582,11 @@
       <c r="E16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" ht="15.0" customHeight="1">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
@@ -1630,7 +1602,10 @@
       <c r="E17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -1652,7 +1627,7 @@
       <c r="F18" s="2"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>53</v>
       </c>
@@ -1663,7 +1638,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>54</v>
@@ -1714,44 +1689,42 @@
         <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3">
         <v>13.0</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -1759,10 +1732,10 @@
         <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3">
         <v>13.0</v>
@@ -1780,10 +1753,10 @@
         <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" s="3">
         <v>13.0</v>
@@ -1791,7 +1764,7 @@
       <c r="E25" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F25" s="2"/>
+      <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1801,10 +1774,10 @@
         <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3">
         <v>13.0</v>
@@ -1819,156 +1792,156 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3">
         <v>13.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F27" s="2"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="D29" s="3">
         <v>20.0</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D30" s="3">
         <v>20.0</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
+      <c r="H30" s="2"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>75</v>
+      <c r="C31" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D31" s="3">
         <v>20.0</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>87</v>
-      </c>
+      <c r="G31" s="2"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
+      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -1979,51 +1952,51 @@
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D34" s="3">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D35" s="3">
         <v>35.0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>97</v>
@@ -2033,7 +2006,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>98</v>
       </c>
@@ -2041,18 +2014,20 @@
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D37" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>99</v>
       </c>
       <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>100</v>
       </c>
@@ -2060,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D38" s="3">
         <v>28.0</v>
@@ -2068,51 +2043,49 @@
       <c r="E38" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="F38" s="2"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D39" s="3">
         <v>28.0</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
@@ -2124,14 +2097,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="4" t="s">
         <v>109</v>
       </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2144,7 +2118,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3">
         <v>28.0</v>
@@ -2164,7 +2138,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D43" s="3">
         <v>28.0</v>
@@ -2172,7 +2146,6 @@
       <c r="E43" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2185,13 +2158,13 @@
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D44" s="3">
-        <v>45.0</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -2200,16 +2173,16 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="D45" s="3">
-        <v>20.0</v>
+        <v>45.0</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>118</v>
@@ -2227,10 +2200,10 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D46" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>120</v>
@@ -2248,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D47" s="3">
         <v>40.0</v>
@@ -2256,33 +2229,33 @@
       <c r="E47" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D48" s="3">
         <v>40.0</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
@@ -2294,10 +2267,10 @@
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D49" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>128</v>
@@ -2315,7 +2288,7 @@
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D50" s="3">
         <v>25.0</v>
@@ -2324,7 +2297,7 @@
         <v>130</v>
       </c>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
+      <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
@@ -2336,16 +2309,16 @@
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D51" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
@@ -2357,13 +2330,13 @@
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D52" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -2372,13 +2345,13 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="D53" s="3">
         <v>22.0</v>
@@ -2386,33 +2359,33 @@
       <c r="E53" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D54" s="3">
         <v>22.0</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
@@ -2423,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D55" s="3">
         <v>22.0</v>
@@ -2444,73 +2417,73 @@
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="3">
+        <v>22.0</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D56" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D57" s="3">
         <v>30.0</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D58" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
@@ -2531,7 +2504,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D60" s="3">
         <v>25.0</v>
@@ -2552,7 +2525,7 @@
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D61" s="3">
         <v>25.0</v>
@@ -2573,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D62" s="3">
         <v>25.0</v>
@@ -2594,7 +2567,7 @@
         <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D63" s="3">
         <v>25.0</v>
@@ -2615,13 +2588,13 @@
         <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D64" s="3">
         <v>25.0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2630,21 +2603,21 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D65" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F65" s="2"/>
+      <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -2657,13 +2630,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D66" s="3">
         <v>30.0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="1"/>
@@ -2672,13 +2645,13 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="D67" s="3">
         <v>30.0</v>
@@ -2686,7 +2659,7 @@
       <c r="E67" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F67" s="1"/>
+      <c r="F67" s="2"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -2699,7 +2672,7 @@
         <v>10</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D68" s="3">
         <v>30.0</v>
@@ -2720,7 +2693,7 @@
         <v>10</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D69" s="3">
         <v>30.0</v>
@@ -2728,7 +2701,7 @@
       <c r="E69" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F69" s="1"/>
+      <c r="F69" s="2"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -2738,41 +2711,41 @@
         <v>178</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D70" s="3">
-        <v>30.0</v>
+        <v>12.0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F70" s="2"/>
-      <c r="G70" s="1"/>
+        <v>181</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D71" s="3">
         <v>12.0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F71" s="2" t="s">
         <v>184</v>
       </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
@@ -2781,10 +2754,10 @@
         <v>185</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D72" s="3">
         <v>12.0</v>
@@ -2802,10 +2775,10 @@
         <v>187</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D73" s="3">
         <v>12.0</v>
@@ -2823,10 +2796,10 @@
         <v>189</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D74" s="3">
         <v>12.0</v>
@@ -2844,31 +2817,31 @@
         <v>191</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D75" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F75" s="5"/>
+        <v>194</v>
+      </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
@@ -2886,10 +2859,10 @@
         <v>197</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D77" s="3">
         <v>15.0</v>
@@ -2907,10 +2880,10 @@
         <v>199</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D78" s="3">
         <v>15.0</v>
@@ -2928,10 +2901,10 @@
         <v>201</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D79" s="3">
         <v>15.0</v>
@@ -2939,7 +2912,6 @@
       <c r="E79" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F79" s="2"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2949,10 +2921,10 @@
         <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D80" s="3">
         <v>15.0</v>
@@ -2969,33 +2941,34 @@
         <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="D81" s="3">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="F81" s="2"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="D82" s="3">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>210</v>
@@ -3007,19 +2980,19 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D83" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D83" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="1"/>
@@ -3028,19 +3001,19 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="D84" s="3">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="1"/>
@@ -3049,16 +3022,16 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D85" s="3">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>214</v>
@@ -3073,10 +3046,10 @@
         <v>215</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D86" s="3">
         <v>11.0</v>
@@ -3094,10 +3067,10 @@
         <v>217</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D87" s="3">
         <v>11.0</v>
@@ -3115,10 +3088,10 @@
         <v>219</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D88" s="3">
         <v>11.0</v>
@@ -3136,85 +3109,85 @@
         <v>221</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="D89" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F89" s="2"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
       <c r="I89" s="1"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D90" s="3">
         <v>12.0</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F90" s="2"/>
       <c r="I90" s="1"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D91" s="3">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E91" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F91" s="2"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="D92" s="3">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H92" s="4" t="s">
         <v>232</v>
       </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="5"/>
       <c r="I92" s="1"/>
     </row>
     <row r="93">
@@ -3222,63 +3195,47 @@
         <v>233</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D93" s="3">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>237</v>
+      </c>
       <c r="H93" s="5"/>
       <c r="I93" s="1"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="s">
-        <v>235</v>
+      <c r="A94" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D94" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H94" s="5"/>
-      <c r="I94" s="1"/>
+        <v>15.0</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D95" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>242</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="3"/>
     </row>
     <row r="96">
       <c r="B96" s="2"/>
@@ -3345,11 +3302,7 @@
       <c r="C108" s="2"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109">
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="3"/>
-    </row>
+    <row r="109" ht="14.25" customHeight="1"/>
     <row r="110" ht="14.25" customHeight="1"/>
     <row r="111" ht="14.25" customHeight="1"/>
     <row r="112" ht="14.25" customHeight="1"/>
@@ -4272,13 +4225,12 @@
     <row r="1029" ht="14.25" customHeight="1"/>
     <row r="1030" ht="14.25" customHeight="1"/>
     <row r="1031" ht="14.25" customHeight="1"/>
-    <row r="1032" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B109">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B108">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C109">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C108">
       <formula1>datos!$C$2:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -4286,14 +4238,13 @@
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
-  <tableParts count="7">
+  <tableParts count="6">
+    <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
-    <tablePart r:id="rId14"/>
-    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4312,7 +4263,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4323,12 +4274,12 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -4336,91 +4287,91 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4430,12 +4381,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="Rhq3LPhHXaijst1qpkJ1zxPCVpswki5++27SWyObVOg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="sElMmEI8C2J1LfMmdhuflHWNc8M1yCCqoYSHzdZTttg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="246">
   <si>
     <t>nombre</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>precio</t>
+  </si>
+  <si>
+    <t>stock</t>
   </si>
   <si>
     <t>imagen1</t>
@@ -905,25 +908,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I67" displayName="Table_1" name="Table_1" id="1">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J67" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="10">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
     <tableColumn name="categoría" id="3"/>
     <tableColumn name="precio" id="4"/>
-    <tableColumn name="imagen1" id="5"/>
-    <tableColumn name="imagen2" id="6"/>
-    <tableColumn name="imagen3" id="7"/>
-    <tableColumn name="imagen4" id="8"/>
-    <tableColumn name="imagen5" id="9"/>
+    <tableColumn name="stock" id="5"/>
+    <tableColumn name="imagen1" id="6"/>
+    <tableColumn name="imagen2" id="7"/>
+    <tableColumn name="imagen3" id="8"/>
+    <tableColumn name="imagen4" id="9"/>
+    <tableColumn name="imagen5" id="10"/>
   </tableColumns>
   <tableStyleInfo name="catalogo-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:I68" displayName="Table_2" name="Table_2" id="2">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:J68" displayName="Table_2" name="Table_2" id="2">
+  <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
@@ -933,14 +937,15 @@
     <tableColumn name="Column7" id="7"/>
     <tableColumn name="Column8" id="8"/>
     <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
   </tableColumns>
   <tableStyleInfo name="catalogo-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:I74" displayName="Table_3" name="Table_3" id="3">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:J74" displayName="Table_3" name="Table_3" id="3">
+  <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
@@ -950,14 +955,15 @@
     <tableColumn name="Column7" id="7"/>
     <tableColumn name="Column8" id="8"/>
     <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
   </tableColumns>
   <tableStyleInfo name="catalogo-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A75:I88" displayName="Table_4" name="Table_4" id="4">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A75:J88" displayName="Table_4" name="Table_4" id="4">
+  <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
@@ -967,14 +973,15 @@
     <tableColumn name="Column7" id="7"/>
     <tableColumn name="Column8" id="8"/>
     <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
   </tableColumns>
   <tableStyleInfo name="catalogo-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A89:I89" displayName="Table_5" name="Table_5" id="5">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A89:J89" displayName="Table_5" name="Table_5" id="5">
+  <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
@@ -984,14 +991,15 @@
     <tableColumn name="Column7" id="7"/>
     <tableColumn name="Column8" id="8"/>
     <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
   </tableColumns>
   <tableStyleInfo name="catalogo-style 5" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A90:I93" displayName="Table_6" name="Table_6" id="6">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A90:J93" displayName="Table_6" name="Table_6" id="6">
+  <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
@@ -1001,6 +1009,7 @@
     <tableColumn name="Column7" id="7"/>
     <tableColumn name="Column8" id="8"/>
     <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
   </tableColumns>
   <tableStyleInfo name="catalogo-style 6" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -1229,12 +1238,12 @@
     <col customWidth="1" min="2" max="2" width="17.71"/>
     <col customWidth="1" min="3" max="3" width="16.43"/>
     <col customWidth="1" min="4" max="4" width="14.86"/>
-    <col customWidth="1" min="5" max="5" width="29.29"/>
-    <col customWidth="1" min="6" max="6" width="27.0"/>
-    <col customWidth="1" min="7" max="7" width="32.0"/>
-    <col customWidth="1" min="8" max="8" width="26.71"/>
-    <col customWidth="1" min="9" max="9" width="19.29"/>
-    <col customWidth="1" min="10" max="26" width="10.71"/>
+    <col customWidth="1" min="5" max="6" width="29.29"/>
+    <col customWidth="1" min="7" max="7" width="27.0"/>
+    <col customWidth="1" min="8" max="8" width="32.0"/>
+    <col customWidth="1" min="9" max="9" width="26.71"/>
+    <col customWidth="1" min="10" max="10" width="19.29"/>
+    <col customWidth="1" min="11" max="27" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -1250,7 +1259,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1265,224 +1274,257 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3">
         <v>30.0</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="I2" s="1"/>
+      <c r="E2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>30.0</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="I3" s="1"/>
+      <c r="E3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>30.0</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="I4" s="1"/>
+      <c r="E4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3">
         <v>30.0</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
+      <c r="E5" s="2">
+        <v>1.0</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3">
         <v>30.0</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="I6" s="1"/>
+      <c r="E6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3">
         <v>30.0</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="2"/>
+      <c r="E7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="1"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3">
         <v>25.0</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2"/>
+      <c r="E8" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
         <v>38.0</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="2"/>
+      <c r="E9" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3">
         <v>38.0</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="2"/>
+      <c r="E10" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="1"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3">
         <v>35.0</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="2"/>
+      <c r="E11" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="3">
         <v>30.0</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>35</v>
+      <c r="E12" s="2">
+        <v>1.0</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>36</v>
@@ -1493,231 +1535,264 @@
       <c r="H12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>40</v>
+      <c r="E13" s="2">
+        <v>1.0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="2"/>
+      <c r="E14" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>45</v>
+      <c r="E15" s="2">
+        <v>1.0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="1"/>
+        <v>37</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3">
         <v>30.0</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="1"/>
+      <c r="E16" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="3">
         <v>30.0</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>50</v>
+      <c r="E17" s="2">
+        <v>1.0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="3">
         <v>30.0</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="I18" s="1"/>
+      <c r="E18" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="3">
         <v>30.0</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="I19" s="1"/>
+      <c r="E19" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" s="3">
         <v>25.0</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="I20" s="1"/>
+      <c r="E20" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="3">
         <v>25.0</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="I21" s="1"/>
+      <c r="E21" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="3">
         <v>25.0</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="I22" s="1"/>
+      <c r="E22" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="3">
         <v>13.0</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>64</v>
+      <c r="E23" s="2">
+        <v>1.0</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
@@ -1725,126 +1800,144 @@
       <c r="G23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="H23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" s="3">
         <v>13.0</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="1"/>
+      <c r="E24" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" s="3">
         <v>13.0</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="1"/>
+      <c r="E25" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="3">
         <v>13.0</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
+      <c r="E26" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D27" s="3">
         <v>13.0</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
+      <c r="E27" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="2"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D28" s="3">
         <v>13.0</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="I28" s="1"/>
+      <c r="E28" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="J28" s="1"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D29" s="3">
         <v>20.0</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>78</v>
+      <c r="E29" s="2">
+        <v>1.0</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
@@ -1852,403 +1945,460 @@
       <c r="G29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="H29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J29" s="1"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" s="3">
         <v>20.0</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>82</v>
+      <c r="E30" s="2">
+        <v>1.0</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="H30" s="2"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D31" s="3">
         <v>20.0</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>85</v>
+      <c r="E31" s="2">
+        <v>1.0</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
+      <c r="G31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="2"/>
       <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D32" s="3">
         <v>20.0</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>88</v>
+      <c r="E32" s="4">
+        <v>1.0</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="G32" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D33" s="3">
         <v>30.0</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>91</v>
+      <c r="E33" s="2">
+        <v>1.0</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="G33" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D34" s="3">
         <v>20.0</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F34" s="2"/>
+      <c r="E34" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D35" s="3">
         <v>35.0</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
+      <c r="E35" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="3">
         <v>35.0</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="2"/>
+      <c r="E36" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="1"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D37" s="3">
         <v>30.0</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F37" s="2"/>
+      <c r="E37" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38" s="3">
         <v>28.0</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="I38" s="1"/>
+      <c r="E38" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="J38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D39" s="3">
         <v>28.0</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>103</v>
+      <c r="E39" s="2">
+        <v>1.0</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I39" s="1"/>
+      <c r="G39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J39" s="1"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="E40" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H40" s="1"/>
+      <c r="G40" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" s="2"/>
+      <c r="E41" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="G41" s="2"/>
-      <c r="H41" s="1"/>
+      <c r="H41" s="2"/>
       <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D42" s="3">
         <v>28.0</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="1"/>
+      <c r="E42" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D43" s="3">
         <v>28.0</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="1"/>
+      <c r="E43" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H43" s="2"/>
       <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44" s="3">
         <v>28.0</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44" s="2"/>
+      <c r="E44" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="G44" s="2"/>
-      <c r="H44" s="1"/>
+      <c r="H44" s="2"/>
       <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D45" s="3">
         <v>45.0</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F45" s="2"/>
+      <c r="E45" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="G45" s="2"/>
-      <c r="H45" s="1"/>
+      <c r="H45" s="2"/>
       <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D46" s="3">
         <v>20.0</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F46" s="2"/>
+      <c r="E46" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="G46" s="2"/>
-      <c r="H46" s="1"/>
+      <c r="H46" s="2"/>
       <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D47" s="3">
         <v>40.0</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F47" s="2"/>
+      <c r="E47" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="G47" s="2"/>
-      <c r="H47" s="1"/>
+      <c r="H47" s="2"/>
       <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D48" s="3">
         <v>40.0</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>124</v>
+      <c r="E48" s="2">
+        <v>1.0</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>125</v>
@@ -2256,129 +2406,147 @@
       <c r="G48" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H48" s="1"/>
+      <c r="H48" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D49" s="3">
         <v>40.0</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="1"/>
+      <c r="E49" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="2"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D50" s="3">
         <v>25.0</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="1"/>
+      <c r="E50" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" s="2"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D51" s="3">
         <v>25.0</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F51" s="2"/>
+      <c r="E51" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="G51" s="2"/>
-      <c r="H51" s="1"/>
+      <c r="H51" s="2"/>
       <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D52" s="3">
         <v>30.0</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" s="1"/>
+      <c r="E52" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D53" s="3">
         <v>22.0</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F53" s="1"/>
+      <c r="E53" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D54" s="3">
         <v>22.0</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>139</v>
+      <c r="E54" s="2">
+        <v>1.0</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>140</v>
@@ -2386,825 +2554,942 @@
       <c r="G54" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="I54" s="1"/>
+      <c r="H54" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D55" s="3">
         <v>22.0</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F55" s="1"/>
+      <c r="E55" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D56" s="3">
         <v>22.0</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F56" s="1"/>
+      <c r="E56" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D57" s="3">
         <v>30.0</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>148</v>
+      <c r="E57" s="2">
+        <v>1.0</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G57" s="1"/>
+      <c r="G57" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D58" s="3">
         <v>30.0</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>151</v>
+      <c r="E58" s="2">
+        <v>1.0</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="H58" s="1"/>
+      <c r="G58" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D59" s="3">
         <v>25.0</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F59" s="1"/>
+      <c r="E59" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D60" s="3">
         <v>25.0</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F60" s="1"/>
+      <c r="E60" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D61" s="3">
         <v>25.0</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F61" s="1"/>
+      <c r="E61" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D62" s="3">
         <v>25.0</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F62" s="1"/>
+      <c r="E62" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D63" s="3">
         <v>25.0</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F63" s="1"/>
+      <c r="E63" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D64" s="3">
         <v>25.0</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F64" s="1"/>
+      <c r="E64" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D65" s="3">
         <v>25.0</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F65" s="1"/>
+      <c r="E65" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D66" s="3">
         <v>30.0</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="1"/>
+      <c r="E66" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G66" s="2"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D67" s="3">
         <v>30.0</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F67" s="2"/>
-      <c r="G67" s="1"/>
+      <c r="E67" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G67" s="2"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D68" s="3">
         <v>30.0</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F68" s="1"/>
+      <c r="E68" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D69" s="3">
         <v>30.0</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="1"/>
+      <c r="E69" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G69" s="2"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D70" s="3">
         <v>12.0</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>181</v>
+      <c r="E70" s="2">
+        <v>1.0</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H70" s="1"/>
+      <c r="G70" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D71" s="3">
         <v>12.0</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F71" s="5"/>
-      <c r="G71" s="1"/>
+      <c r="E71" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G71" s="5"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D72" s="3">
         <v>12.0</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F72" s="5"/>
-      <c r="G72" s="1"/>
+      <c r="E72" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G72" s="5"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D73" s="3">
         <v>12.0</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F73" s="5"/>
-      <c r="G73" s="1"/>
+      <c r="E73" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G73" s="5"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D74" s="3">
         <v>12.0</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="1"/>
+      <c r="E74" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G74" s="5"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D75" s="3">
         <v>15.0</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="1"/>
+      <c r="E75" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G75" s="2"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D76" s="3">
         <v>15.0</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="1"/>
+      <c r="E76" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G76" s="2"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D77" s="3">
         <v>15.0</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F77" s="2"/>
-      <c r="G77" s="1"/>
+      <c r="E77" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G77" s="2"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D78" s="3">
         <v>15.0</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F78" s="2"/>
-      <c r="G78" s="1"/>
+      <c r="E78" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G78" s="2"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D79" s="3">
         <v>15.0</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G79" s="1"/>
+      <c r="E79" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D80" s="3">
         <v>15.0</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G80" s="1"/>
+      <c r="E80" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D81" s="3">
         <v>5.0</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="1"/>
+      <c r="E81" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G81" s="2"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D82" s="3">
         <v>10.0</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F82" s="2"/>
-      <c r="G82" s="1"/>
+      <c r="E82" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G82" s="2"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D83" s="3">
         <v>4.0</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F83" s="2"/>
-      <c r="G83" s="1"/>
+      <c r="E83" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G83" s="2"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D84" s="3">
         <v>8.0</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F84" s="2"/>
-      <c r="G84" s="1"/>
+      <c r="E84" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G84" s="2"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D85" s="3">
         <v>11.0</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="1"/>
+      <c r="E85" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G85" s="2"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D86" s="3">
         <v>11.0</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="1"/>
+      <c r="E86" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G86" s="2"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D87" s="3">
         <v>11.0</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="1"/>
+      <c r="E87" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G87" s="2"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D88" s="3">
         <v>11.0</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F88" s="2"/>
-      <c r="G88" s="1"/>
+      <c r="E88" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G88" s="2"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D89" s="3">
         <v>12.0</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F89" s="2"/>
-      <c r="I89" s="1"/>
+      <c r="E89" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G89" s="2"/>
+      <c r="J89" s="1"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D90" s="3">
         <v>12.0</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F90" s="2"/>
-      <c r="I90" s="1"/>
+      <c r="E90" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="J90" s="1"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D91" s="3">
         <v>13.0</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>227</v>
+      <c r="E91" s="2">
+        <v>1.0</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="2" t="s">
         <v>229</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="I91" s="1"/>
+      <c r="I91" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="J91" s="1"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D92" s="3">
         <v>20.0</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F92" s="2"/>
+      <c r="E92" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="1"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D93" s="3">
         <v>9.0</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>235</v>
+      <c r="E93" s="2">
+        <v>1.0</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>236</v>
@@ -3212,24 +3497,30 @@
       <c r="G93" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="H93" s="5"/>
-      <c r="I93" s="1"/>
+      <c r="H93" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I93" s="5"/>
+      <c r="J93" s="1"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D94" s="3">
         <v>15.0</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>240</v>
+      <c r="E94" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="95">
@@ -4263,7 +4554,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4271,127 +4562,127 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="C23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -1291,9 +1291,7 @@
       <c r="D2" s="3">
         <v>30.0</v>
       </c>
-      <c r="E2" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
@@ -1313,9 +1311,7 @@
       <c r="D3" s="3">
         <v>30.0</v>
       </c>
-      <c r="E3" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1335,9 +1331,7 @@
       <c r="D4" s="3">
         <v>30.0</v>
       </c>
-      <c r="E4" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1357,9 +1351,7 @@
       <c r="D5" s="3">
         <v>30.0</v>
       </c>
-      <c r="E5" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1381,9 +1373,7 @@
       <c r="D6" s="3">
         <v>30.0</v>
       </c>
-      <c r="E6" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1403,9 +1393,7 @@
       <c r="D7" s="3">
         <v>30.0</v>
       </c>
-      <c r="E7" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
         <v>24</v>
       </c>
@@ -1427,9 +1415,7 @@
       <c r="D8" s="3">
         <v>25.0</v>
       </c>
-      <c r="E8" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1451,9 +1437,7 @@
       <c r="D9" s="3">
         <v>38.0</v>
       </c>
-      <c r="E9" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>29</v>
       </c>
@@ -1475,9 +1459,7 @@
       <c r="D10" s="3">
         <v>38.0</v>
       </c>
-      <c r="E10" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
         <v>31</v>
       </c>
@@ -1499,9 +1481,7 @@
       <c r="D11" s="3">
         <v>35.0</v>
       </c>
-      <c r="E11" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
         <v>34</v>
       </c>
@@ -1523,9 +1503,7 @@
       <c r="D12" s="3">
         <v>30.0</v>
       </c>
-      <c r="E12" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>36</v>
       </c>
@@ -1553,9 +1531,7 @@
       <c r="D13" s="3">
         <v>30.0</v>
       </c>
-      <c r="E13" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>41</v>
       </c>
@@ -1581,9 +1557,7 @@
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
-      <c r="E14" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>44</v>
       </c>
@@ -1605,9 +1579,7 @@
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
-      <c r="E15" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
         <v>46</v>
       </c>
@@ -1633,9 +1605,7 @@
       <c r="D16" s="3">
         <v>30.0</v>
       </c>
-      <c r="E16" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
         <v>49</v>
       </c>
@@ -1656,9 +1626,7 @@
       <c r="D17" s="3">
         <v>30.0</v>
       </c>
-      <c r="E17" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
         <v>51</v>
       </c>
@@ -1681,9 +1649,7 @@
       <c r="D18" s="3">
         <v>30.0</v>
       </c>
-      <c r="E18" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
         <v>53</v>
       </c>
@@ -1703,9 +1669,7 @@
       <c r="D19" s="3">
         <v>30.0</v>
       </c>
-      <c r="E19" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
         <v>55</v>
       </c>
@@ -1725,9 +1689,7 @@
       <c r="D20" s="3">
         <v>25.0</v>
       </c>
-      <c r="E20" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
         <v>57</v>
       </c>
@@ -1747,9 +1709,7 @@
       <c r="D21" s="3">
         <v>25.0</v>
       </c>
-      <c r="E21" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
         <v>59</v>
       </c>
@@ -1769,9 +1729,7 @@
       <c r="D22" s="3">
         <v>25.0</v>
       </c>
-      <c r="E22" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
         <v>61</v>
       </c>
@@ -1791,9 +1749,7 @@
       <c r="D23" s="3">
         <v>13.0</v>
       </c>
-      <c r="E23" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
@@ -1818,9 +1774,7 @@
       <c r="D24" s="3">
         <v>13.0</v>
       </c>
-      <c r="E24" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
@@ -1842,9 +1796,7 @@
       <c r="D25" s="3">
         <v>13.0</v>
       </c>
-      <c r="E25" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
@@ -1866,9 +1818,7 @@
       <c r="D26" s="3">
         <v>13.0</v>
       </c>
-      <c r="E26" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
         <v>73</v>
       </c>
@@ -1890,9 +1840,7 @@
       <c r="D27" s="3">
         <v>13.0</v>
       </c>
-      <c r="E27" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
         <v>75</v>
       </c>
@@ -1914,9 +1862,7 @@
       <c r="D28" s="3">
         <v>13.0</v>
       </c>
-      <c r="E28" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
         <v>76</v>
       </c>
@@ -1936,9 +1882,7 @@
       <c r="D29" s="3">
         <v>20.0</v>
       </c>
-      <c r="E29" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
         <v>79</v>
       </c>
@@ -1963,9 +1907,7 @@
       <c r="D30" s="3">
         <v>20.0</v>
       </c>
-      <c r="E30" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
         <v>83</v>
       </c>
@@ -1989,9 +1931,7 @@
       <c r="D31" s="3">
         <v>20.0</v>
       </c>
-      <c r="E31" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
         <v>86</v>
       </c>
@@ -2015,9 +1955,6 @@
       <c r="D32" s="3">
         <v>20.0</v>
       </c>
-      <c r="E32" s="4">
-        <v>1.0</v>
-      </c>
       <c r="F32" s="4" t="s">
         <v>89</v>
       </c>
@@ -2040,9 +1977,7 @@
       <c r="D33" s="3">
         <v>30.0</v>
       </c>
-      <c r="E33" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
         <v>92</v>
       </c>
@@ -2065,9 +2000,7 @@
       <c r="D34" s="3">
         <v>20.0</v>
       </c>
-      <c r="E34" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
         <v>95</v>
       </c>
@@ -2089,9 +2022,7 @@
       <c r="D35" s="3">
         <v>35.0</v>
       </c>
-      <c r="E35" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
         <v>97</v>
       </c>
@@ -2112,9 +2043,7 @@
       <c r="D36" s="3">
         <v>35.0</v>
       </c>
-      <c r="E36" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
         <v>98</v>
       </c>
@@ -2136,9 +2065,7 @@
       <c r="D37" s="3">
         <v>30.0</v>
       </c>
-      <c r="E37" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
         <v>100</v>
       </c>
@@ -2160,9 +2087,7 @@
       <c r="D38" s="3">
         <v>28.0</v>
       </c>
-      <c r="E38" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
         <v>102</v>
       </c>
@@ -2182,9 +2107,7 @@
       <c r="D39" s="3">
         <v>28.0</v>
       </c>
-      <c r="E39" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
         <v>104</v>
       </c>
@@ -2206,9 +2129,6 @@
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
-      <c r="E40" s="4">
-        <v>1.0</v>
-      </c>
       <c r="F40" s="4" t="s">
         <v>107</v>
       </c>
@@ -2230,9 +2150,6 @@
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
-      </c>
-      <c r="E41" s="4">
-        <v>1.0</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>110</v>
@@ -2255,9 +2172,7 @@
       <c r="D42" s="3">
         <v>28.0</v>
       </c>
-      <c r="E42" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
         <v>112</v>
       </c>
@@ -2278,9 +2193,7 @@
       <c r="D43" s="3">
         <v>28.0</v>
       </c>
-      <c r="E43" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
         <v>114</v>
       </c>
@@ -2301,9 +2214,7 @@
       <c r="D44" s="3">
         <v>28.0</v>
       </c>
-      <c r="E44" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
         <v>116</v>
       </c>
@@ -2325,9 +2236,7 @@
       <c r="D45" s="3">
         <v>45.0</v>
       </c>
-      <c r="E45" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
         <v>119</v>
       </c>
@@ -2349,9 +2258,7 @@
       <c r="D46" s="3">
         <v>20.0</v>
       </c>
-      <c r="E46" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
         <v>121</v>
       </c>
@@ -2373,9 +2280,7 @@
       <c r="D47" s="3">
         <v>40.0</v>
       </c>
-      <c r="E47" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
         <v>123</v>
       </c>
@@ -2397,9 +2302,7 @@
       <c r="D48" s="3">
         <v>40.0</v>
       </c>
-      <c r="E48" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
         <v>125</v>
       </c>
@@ -2425,9 +2328,7 @@
       <c r="D49" s="3">
         <v>40.0</v>
       </c>
-      <c r="E49" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
         <v>129</v>
       </c>
@@ -2449,9 +2350,7 @@
       <c r="D50" s="3">
         <v>25.0</v>
       </c>
-      <c r="E50" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
         <v>131</v>
       </c>
@@ -2473,9 +2372,7 @@
       <c r="D51" s="3">
         <v>25.0</v>
       </c>
-      <c r="E51" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
         <v>133</v>
       </c>
@@ -2497,9 +2394,7 @@
       <c r="D52" s="3">
         <v>30.0</v>
       </c>
-      <c r="E52" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
         <v>135</v>
       </c>
@@ -2521,9 +2416,7 @@
       <c r="D53" s="3">
         <v>22.0</v>
       </c>
-      <c r="E53" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
         <v>138</v>
       </c>
@@ -2545,9 +2438,7 @@
       <c r="D54" s="3">
         <v>22.0</v>
       </c>
-      <c r="E54" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
         <v>140</v>
       </c>
@@ -2572,9 +2463,7 @@
       <c r="D55" s="3">
         <v>22.0</v>
       </c>
-      <c r="E55" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
         <v>144</v>
       </c>
@@ -2596,9 +2485,7 @@
       <c r="D56" s="3">
         <v>22.0</v>
       </c>
-      <c r="E56" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
         <v>146</v>
       </c>
@@ -2620,9 +2507,7 @@
       <c r="D57" s="3">
         <v>30.0</v>
       </c>
-      <c r="E57" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
         <v>149</v>
       </c>
@@ -2646,9 +2531,7 @@
       <c r="D58" s="3">
         <v>30.0</v>
       </c>
-      <c r="E58" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
         <v>152</v>
       </c>
@@ -2671,9 +2554,7 @@
       <c r="D59" s="3">
         <v>25.0</v>
       </c>
-      <c r="E59" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
         <v>156</v>
       </c>
@@ -2695,9 +2576,7 @@
       <c r="D60" s="3">
         <v>25.0</v>
       </c>
-      <c r="E60" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
         <v>158</v>
       </c>
@@ -2719,9 +2598,7 @@
       <c r="D61" s="3">
         <v>25.0</v>
       </c>
-      <c r="E61" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
         <v>160</v>
       </c>
@@ -2743,9 +2620,7 @@
       <c r="D62" s="3">
         <v>25.0</v>
       </c>
-      <c r="E62" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
         <v>162</v>
       </c>
@@ -2767,9 +2642,7 @@
       <c r="D63" s="3">
         <v>25.0</v>
       </c>
-      <c r="E63" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
         <v>164</v>
       </c>
@@ -2791,9 +2664,7 @@
       <c r="D64" s="3">
         <v>25.0</v>
       </c>
-      <c r="E64" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
         <v>166</v>
       </c>
@@ -2815,9 +2686,7 @@
       <c r="D65" s="3">
         <v>25.0</v>
       </c>
-      <c r="E65" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
         <v>169</v>
       </c>
@@ -2839,9 +2708,7 @@
       <c r="D66" s="3">
         <v>30.0</v>
       </c>
-      <c r="E66" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
         <v>171</v>
       </c>
@@ -2863,9 +2730,7 @@
       <c r="D67" s="3">
         <v>30.0</v>
       </c>
-      <c r="E67" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
         <v>174</v>
       </c>
@@ -2887,9 +2752,7 @@
       <c r="D68" s="3">
         <v>30.0</v>
       </c>
-      <c r="E68" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
         <v>176</v>
       </c>
@@ -2911,9 +2774,7 @@
       <c r="D69" s="3">
         <v>30.0</v>
       </c>
-      <c r="E69" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
         <v>178</v>
       </c>
@@ -2935,9 +2796,7 @@
       <c r="D70" s="3">
         <v>12.0</v>
       </c>
-      <c r="E70" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
         <v>182</v>
       </c>
@@ -2960,9 +2819,7 @@
       <c r="D71" s="3">
         <v>12.0</v>
       </c>
-      <c r="E71" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
         <v>185</v>
       </c>
@@ -2984,9 +2841,7 @@
       <c r="D72" s="3">
         <v>12.0</v>
       </c>
-      <c r="E72" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
         <v>187</v>
       </c>
@@ -3008,9 +2863,7 @@
       <c r="D73" s="3">
         <v>12.0</v>
       </c>
-      <c r="E73" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
         <v>189</v>
       </c>
@@ -3032,9 +2885,7 @@
       <c r="D74" s="3">
         <v>12.0</v>
       </c>
-      <c r="E74" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
         <v>191</v>
       </c>
@@ -3056,9 +2907,7 @@
       <c r="D75" s="3">
         <v>15.0</v>
       </c>
-      <c r="E75" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
         <v>195</v>
       </c>
@@ -3080,9 +2929,7 @@
       <c r="D76" s="3">
         <v>15.0</v>
       </c>
-      <c r="E76" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
         <v>197</v>
       </c>
@@ -3104,9 +2951,7 @@
       <c r="D77" s="3">
         <v>15.0</v>
       </c>
-      <c r="E77" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
         <v>199</v>
       </c>
@@ -3128,9 +2973,7 @@
       <c r="D78" s="3">
         <v>15.0</v>
       </c>
-      <c r="E78" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
         <v>201</v>
       </c>
@@ -3152,9 +2995,7 @@
       <c r="D79" s="3">
         <v>15.0</v>
       </c>
-      <c r="E79" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
         <v>203</v>
       </c>
@@ -3175,9 +3016,7 @@
       <c r="D80" s="3">
         <v>15.0</v>
       </c>
-      <c r="E80" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
         <v>205</v>
       </c>
@@ -3198,9 +3037,7 @@
       <c r="D81" s="3">
         <v>5.0</v>
       </c>
-      <c r="E81" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
         <v>209</v>
       </c>
@@ -3222,9 +3059,7 @@
       <c r="D82" s="3">
         <v>10.0</v>
       </c>
-      <c r="E82" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
         <v>211</v>
       </c>
@@ -3246,9 +3081,7 @@
       <c r="D83" s="3">
         <v>4.0</v>
       </c>
-      <c r="E83" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
         <v>212</v>
       </c>
@@ -3270,9 +3103,7 @@
       <c r="D84" s="3">
         <v>8.0</v>
       </c>
-      <c r="E84" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
         <v>213</v>
       </c>
@@ -3294,9 +3125,7 @@
       <c r="D85" s="3">
         <v>11.0</v>
       </c>
-      <c r="E85" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
         <v>215</v>
       </c>
@@ -3318,9 +3147,7 @@
       <c r="D86" s="3">
         <v>11.0</v>
       </c>
-      <c r="E86" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
         <v>217</v>
       </c>
@@ -3342,9 +3169,7 @@
       <c r="D87" s="3">
         <v>11.0</v>
       </c>
-      <c r="E87" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
         <v>219</v>
       </c>
@@ -3366,9 +3191,7 @@
       <c r="D88" s="3">
         <v>11.0</v>
       </c>
-      <c r="E88" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
         <v>221</v>
       </c>
@@ -3390,9 +3213,7 @@
       <c r="D89" s="3">
         <v>12.0</v>
       </c>
-      <c r="E89" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
         <v>224</v>
       </c>
@@ -3412,9 +3233,7 @@
       <c r="D90" s="3">
         <v>12.0</v>
       </c>
-      <c r="E90" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
         <v>225</v>
       </c>
@@ -3434,9 +3253,7 @@
       <c r="D91" s="3">
         <v>13.0</v>
       </c>
-      <c r="E91" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
         <v>228</v>
       </c>
@@ -3464,9 +3281,7 @@
       <c r="D92" s="3">
         <v>20.0</v>
       </c>
-      <c r="E92" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
         <v>233</v>
       </c>
@@ -3488,9 +3303,7 @@
       <c r="D93" s="3">
         <v>9.0</v>
       </c>
-      <c r="E93" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
         <v>236</v>
       </c>
@@ -3515,9 +3328,6 @@
       </c>
       <c r="D94" s="3">
         <v>15.0</v>
-      </c>
-      <c r="E94" s="4">
-        <v>1.0</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>241</v>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="sElMmEI8C2J1LfMmdhuflHWNc8M1yCCqoYSHzdZTttg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="uyJ0StLGd6x9KECAyySpX4gHJS19vprj+5FNhw3bpdE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="256">
   <si>
     <t>nombre</t>
   </si>
@@ -118,6 +118,12 @@
     <t>pontevedra beige.jpg</t>
   </si>
   <si>
+    <t>Pontevedra Blanco</t>
+  </si>
+  <si>
+    <t>Pontevedra Verde</t>
+  </si>
+  <si>
     <t>Kioto Dorado Lux</t>
   </si>
   <si>
@@ -193,7 +199,7 @@
     <t>Kioto Japo Beige</t>
   </si>
   <si>
-    <t>Kioto japo beige</t>
+    <t>Kioto bordado beige</t>
   </si>
   <si>
     <t>Kioto Japo Sombrillas</t>
@@ -424,6 +430,9 @@
     <t>vancouver vintage f k.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">Vancouver Vintage </t>
+  </si>
+  <si>
     <t>Vancouver Velvet</t>
   </si>
   <si>
@@ -739,7 +748,7 @@
     <t>choker flor 3.jpg</t>
   </si>
   <si>
-    <t>Bandana Venecia</t>
+    <t>Bandana Venecia Azul</t>
   </si>
   <si>
     <t>Venecia</t>
@@ -748,6 +757,24 @@
     <t>venecia azul k.jpg</t>
   </si>
   <si>
+    <t>Bandana Venecia Beige</t>
+  </si>
+  <si>
+    <t>Bandana beige</t>
+  </si>
+  <si>
+    <t>Collar California</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Collares California</t>
+  </si>
+  <si>
+    <t>California verde</t>
+  </si>
+  <si>
     <t>tipos</t>
   </si>
   <si>
@@ -758,6 +785,9 @@
   </si>
   <si>
     <t>Londres</t>
+  </si>
+  <si>
+    <t>Mallorca</t>
   </si>
 </sst>
 </file>
@@ -908,7 +938,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J67" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J70" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="10">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -926,7 +956,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A68:J68" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:J71" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -944,7 +974,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A69:J74" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:J77" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -962,7 +992,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A75:J88" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A78:J91" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -980,7 +1010,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A89:J89" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A92:J92" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -998,7 +1028,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A90:J93" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A93:J96" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1025,7 +1055,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C23" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="C1:C25" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="1">
     <tableColumn name="categoría" id="1"/>
   </tableColumns>
@@ -1237,8 +1267,9 @@
     <col customWidth="1" min="1" max="1" width="28.14"/>
     <col customWidth="1" min="2" max="2" width="17.71"/>
     <col customWidth="1" min="3" max="3" width="16.43"/>
-    <col customWidth="1" min="4" max="4" width="14.86"/>
-    <col customWidth="1" min="5" max="6" width="29.29"/>
+    <col customWidth="1" min="4" max="4" width="13.0"/>
+    <col customWidth="1" min="5" max="5" width="17.86"/>
+    <col customWidth="1" min="6" max="6" width="29.29"/>
     <col customWidth="1" min="7" max="7" width="27.0"/>
     <col customWidth="1" min="8" max="8" width="32.0"/>
     <col customWidth="1" min="9" max="9" width="26.71"/>
@@ -1311,7 +1342,9 @@
       <c r="D3" s="3">
         <v>30.0</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1351,7 +1384,9 @@
       <c r="D5" s="3">
         <v>30.0</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1476,558 +1511,570 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D12" s="3">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D13" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3">
         <v>30.0</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
+      <c r="C17" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="3">
         <v>30.0</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" ht="15.0" customHeight="1">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3">
         <v>30.0</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" ht="15.0" customHeight="1">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3">
         <v>30.0</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D20" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D21" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D22" s="3">
         <v>25.0</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G22" s="2"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E23" s="2"/>
+        <v>25.0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>67</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G23" s="2"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="G24" s="2"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D25" s="3">
         <v>13.0</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="J25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="3">
         <v>13.0</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D27" s="3">
         <v>13.0</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" s="3">
         <v>13.0</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D29" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>78</v>
+      <c r="A30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="D30" s="3">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="G30" s="2"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>78</v>
+      <c r="C31" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="D31" s="3">
         <v>20.0</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F31" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="1"/>
+        <v>82</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="J31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>78</v>
+      <c r="A32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D32" s="3">
         <v>20.0</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I32" s="1"/>
+      <c r="E32" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D33" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E33" s="2"/>
+        <v>20.0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2.0</v>
+      </c>
       <c r="F33" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="H33" s="2"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3">
         <v>20.0</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="E34" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D35" s="3">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="I35" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -2038,14 +2085,14 @@
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D36" s="3">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2054,213 +2101,212 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D37" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3">
-        <v>28.0</v>
+        <v>35.0</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D39" s="3">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>105</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40">
       <c r="A40" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="2"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="1"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="J41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D42" s="3">
         <v>28.0</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" s="2"/>
+      <c r="F42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D43" s="3">
         <v>28.0</v>
       </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="F43" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D44" s="3">
         <v>28.0</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G44" s="2"/>
+        <v>114</v>
+      </c>
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D45" s="3">
-        <v>45.0</v>
+        <v>28.0</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G45" s="2"/>
+        <v>116</v>
+      </c>
       <c r="H45" s="2"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D46" s="3">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -2269,20 +2315,20 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D47" s="3">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -2291,181 +2337,178 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D48" s="3">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>127</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D49" s="3">
         <v>40.0</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G49" s="2"/>
-      <c r="H49" s="1"/>
+      <c r="H49" s="2"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D50" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D51" s="3">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D52" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G52" s="1"/>
+        <v>133</v>
+      </c>
+      <c r="G52" s="2"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D53" s="3">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+        <v>135</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D54" s="3">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>142</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D55" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2474,20 +2517,20 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D56" s="3">
         <v>22.0</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2496,67 +2539,67 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D57" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
+        <v>144</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="J57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D58" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>153</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D59" s="3">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -2565,64 +2608,67 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D60" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G60" s="1"/>
+        <v>152</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D61" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D62" s="3">
         <v>25.0</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -2631,20 +2677,20 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D63" s="3">
         <v>25.0</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -2653,20 +2699,20 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D64" s="3">
         <v>25.0</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -2675,20 +2721,20 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D65" s="3">
         <v>25.0</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -2697,64 +2743,64 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D66" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G66" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D67" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G67" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D68" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2763,20 +2809,20 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D69" s="3">
         <v>30.0</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="1"/>
@@ -2785,109 +2831,109 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D70" s="3">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>183</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D71" s="3">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G71" s="5"/>
+        <v>179</v>
+      </c>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D72" s="3">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G72" s="5"/>
+        <v>181</v>
+      </c>
+      <c r="G72" s="2"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D73" s="3">
         <v>12.0</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D74" s="3">
         <v>12.0</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1"/>
@@ -2896,86 +2942,86 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D75" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G75" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="G75" s="5"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D76" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G76" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="G76" s="5"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D77" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G77" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="G77" s="5"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D78" s="3">
         <v>15.0</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="1"/>
@@ -2984,62 +3030,64 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D79" s="3">
         <v>15.0</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G79" s="2"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D80" s="3">
         <v>15.0</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G80" s="2"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D81" s="3">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="1"/>
@@ -3048,64 +3096,62 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D82" s="3">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G82" s="2"/>
+        <v>206</v>
+      </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D83" s="3">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G83" s="2"/>
+        <v>208</v>
+      </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D84" s="3">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="1"/>
@@ -3114,20 +3160,20 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D85" s="3">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="1"/>
@@ -3136,20 +3182,20 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D86" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="1"/>
@@ -3158,20 +3204,20 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D87" s="3">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="1"/>
@@ -3180,20 +3226,20 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D88" s="3">
         <v>11.0</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="1"/>
@@ -3202,166 +3248,253 @@
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D89" s="3">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G89" s="2"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
       <c r="J89" s="1"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D90" s="3">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G90" s="2"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
       <c r="J90" s="1"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="D91" s="3">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>231</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
       <c r="J91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D92" s="3">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="5"/>
       <c r="J92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D93" s="3">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G93" s="2"/>
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
+      <c r="A94" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D94" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D95" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="B96" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="I93" s="5"/>
-      <c r="J93" s="1"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="s">
+      <c r="D96" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="G96" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D94" s="3">
+      <c r="H96" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I96" s="5"/>
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D97" s="3">
         <v>15.0</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="3"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="3"/>
+      <c r="F97" s="4" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="98">
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="3"/>
+      <c r="A98" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D98" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="99">
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="3"/>
+      <c r="A99" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D99" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="100">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="3"/>
+      <c r="A100" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D100" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="2"/>
@@ -3403,9 +3536,21 @@
       <c r="C108" s="2"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="109">
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="3"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="3"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="3"/>
+    </row>
     <row r="112" ht="14.25" customHeight="1"/>
     <row r="113" ht="14.25" customHeight="1"/>
     <row r="114" ht="14.25" customHeight="1"/>
@@ -4326,13 +4471,16 @@
     <row r="1029" ht="14.25" customHeight="1"/>
     <row r="1030" ht="14.25" customHeight="1"/>
     <row r="1031" ht="14.25" customHeight="1"/>
+    <row r="1032" ht="14.25" customHeight="1"/>
+    <row r="1033" ht="14.25" customHeight="1"/>
+    <row r="1034" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B108">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C111">
+      <formula1>datos!$C$2:$C$25</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B111">
       <formula1>datos!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C108">
-      <formula1>datos!$C$2:$C$23</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -4364,7 +4512,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4375,104 +4523,104 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4482,12 +4630,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -4495,8 +4643,16 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="C24" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="C25" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
     <row r="26" ht="14.25" customHeight="1"/>
     <row r="27" ht="14.25" customHeight="1"/>
     <row r="28" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="262">
   <si>
     <t>nombre</t>
   </si>
@@ -121,9 +121,15 @@
     <t>Pontevedra Blanco</t>
   </si>
   <si>
+    <t>Pontevedra blanco</t>
+  </si>
+  <si>
     <t>Pontevedra Verde</t>
   </si>
   <si>
+    <t>Pontevedra verde</t>
+  </si>
+  <si>
     <t>Kioto Dorado Lux</t>
   </si>
   <si>
@@ -205,7 +211,7 @@
     <t>Kioto Japo Sombrillas</t>
   </si>
   <si>
-    <t>Kioto japo sombrillas</t>
+    <t xml:space="preserve">Kioto japo </t>
   </si>
   <si>
     <t>Kioto Zebra</t>
@@ -376,7 +382,7 @@
     <t>San Francisco Cotton Fucsia</t>
   </si>
   <si>
-    <t>San Fran fucsia</t>
+    <t>San Francisco fucsia</t>
   </si>
   <si>
     <t>Vancouver Lux</t>
@@ -772,7 +778,19 @@
     <t>Collares California</t>
   </si>
   <si>
+    <t>Collar California Verde</t>
+  </si>
+  <si>
     <t>California verde</t>
+  </si>
+  <si>
+    <t>California verde 2</t>
+  </si>
+  <si>
+    <t>Collar California Turquesa</t>
+  </si>
+  <si>
+    <t>California turquesa</t>
   </si>
   <si>
     <t>tipos</t>
@@ -1268,7 +1286,7 @@
     <col customWidth="1" min="2" max="2" width="17.71"/>
     <col customWidth="1" min="3" max="3" width="16.43"/>
     <col customWidth="1" min="4" max="4" width="13.0"/>
-    <col customWidth="1" min="5" max="5" width="17.86"/>
+    <col customWidth="1" min="5" max="5" width="10.14"/>
     <col customWidth="1" min="6" max="6" width="29.29"/>
     <col customWidth="1" min="7" max="7" width="27.0"/>
     <col customWidth="1" min="8" max="8" width="32.0"/>
@@ -1517,7 +1535,9 @@
         <v>38.0</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1525,7 +1545,7 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>11</v>
@@ -1537,7 +1557,9 @@
         <v>38.0</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1545,20 +1567,20 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3">
         <v>35.0</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1567,74 +1589,74 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3">
         <v>30.0</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -1643,46 +1665,46 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" s="3">
         <v>30.0</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D18" s="3">
         <v>30.0</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1690,76 +1712,76 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D19" s="3">
         <v>30.0</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D20" s="3">
         <v>30.0</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" s="2"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D21" s="3">
         <v>30.0</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D22" s="3">
         <v>25.0</v>
@@ -1768,20 +1790,20 @@
         <v>1.0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" s="3">
         <v>25.0</v>
@@ -1790,20 +1812,20 @@
         <v>1.0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G23" s="2"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="3">
         <v>25.0</v>
@@ -1812,52 +1834,52 @@
         <v>1.0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D25" s="3">
         <v>13.0</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3">
         <v>13.0</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1866,20 +1888,20 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D27" s="3">
         <v>13.0</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1888,20 +1910,20 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3">
         <v>13.0</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="1"/>
@@ -1910,20 +1932,20 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D29" s="3">
         <v>13.0</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="1"/>
@@ -1932,33 +1954,33 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D30" s="3">
         <v>13.0</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G30" s="2"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D31" s="3">
         <v>20.0</v>
@@ -1967,25 +1989,25 @@
         <v>1.0</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D32" s="3">
         <v>20.0</v>
@@ -1994,10 +2016,10 @@
         <v>1.0</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2005,13 +2027,13 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D33" s="3">
         <v>20.0</v>
@@ -2020,10 +2042,10 @@
         <v>2.0</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="1"/>
@@ -2031,13 +2053,13 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D34" s="3">
         <v>20.0</v>
@@ -2046,53 +2068,53 @@
         <v>1.0</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D35" s="3">
         <v>30.0</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D36" s="3">
         <v>20.0</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2101,20 +2123,20 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D37" s="3">
         <v>35.0</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G37" s="2"/>
       <c r="I37" s="2"/>
@@ -2122,20 +2144,20 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D38" s="3">
         <v>35.0</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -2144,20 +2166,20 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D39" s="3">
         <v>30.0</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -2166,83 +2188,83 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G40" s="2"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D42" s="3">
         <v>28.0</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D43" s="3">
         <v>28.0</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -2251,20 +2273,20 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D44" s="3">
         <v>28.0</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
@@ -2272,20 +2294,20 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D45" s="3">
         <v>28.0</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="1"/>
@@ -2293,20 +2315,20 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D46" s="3">
         <v>28.0</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -2315,20 +2337,20 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D47" s="3">
         <v>45.0</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -2337,20 +2359,20 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D48" s="3">
         <v>20.0</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -2359,20 +2381,20 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D49" s="3">
         <v>40.0</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -2381,46 +2403,46 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D50" s="3">
         <v>40.0</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D51" s="3">
         <v>40.0</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="1"/>
@@ -2429,20 +2451,20 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D52" s="3">
         <v>25.0</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="1"/>
@@ -2451,20 +2473,20 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D53" s="3">
         <v>25.0</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -2473,13 +2495,13 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D54" s="3">
         <v>25.0</v>
@@ -2495,20 +2517,20 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D55" s="3">
         <v>30.0</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2517,20 +2539,20 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D56" s="3">
         <v>22.0</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2539,45 +2561,45 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D57" s="3">
         <v>22.0</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D58" s="3">
         <v>22.0</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -2586,20 +2608,20 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D59" s="3">
         <v>22.0</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -2608,23 +2630,23 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D60" s="3">
         <v>30.0</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2632,43 +2654,43 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D61" s="3">
         <v>30.0</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D62" s="3">
         <v>25.0</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -2677,20 +2699,20 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="D63" s="3">
         <v>25.0</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -2699,20 +2721,20 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D64" s="3">
         <v>25.0</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -2721,20 +2743,20 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D65" s="3">
         <v>25.0</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -2743,20 +2765,20 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D66" s="3">
         <v>25.0</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -2765,20 +2787,20 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D67" s="3">
         <v>25.0</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -2787,20 +2809,20 @@
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D68" s="3">
         <v>25.0</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2809,20 +2831,20 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D69" s="3">
         <v>30.0</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="1"/>
@@ -2831,20 +2853,20 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D70" s="3">
         <v>30.0</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="1"/>
@@ -2853,20 +2875,20 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D71" s="3">
         <v>30.0</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -2875,20 +2897,20 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D72" s="3">
         <v>30.0</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="1"/>
@@ -2897,43 +2919,43 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D73" s="3">
         <v>12.0</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D74" s="3">
         <v>12.0</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1"/>
@@ -2942,20 +2964,20 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D75" s="3">
         <v>12.0</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="1"/>
@@ -2964,20 +2986,20 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D76" s="3">
         <v>12.0</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="1"/>
@@ -2986,20 +3008,20 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D77" s="3">
         <v>12.0</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="1"/>
@@ -3008,20 +3030,20 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D78" s="3">
         <v>15.0</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="1"/>
@@ -3030,20 +3052,20 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="D79" s="3">
         <v>15.0</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="1"/>
@@ -3052,20 +3074,20 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D80" s="3">
         <v>15.0</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="1"/>
@@ -3074,20 +3096,20 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D81" s="3">
         <v>15.0</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="1"/>
@@ -3096,20 +3118,20 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D82" s="3">
         <v>15.0</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -3117,20 +3139,20 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D83" s="3">
         <v>15.0</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -3138,20 +3160,20 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D84" s="3">
         <v>5.0</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="1"/>
@@ -3160,20 +3182,20 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D85" s="3">
         <v>10.0</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="1"/>
@@ -3182,20 +3204,20 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D86" s="3">
         <v>4.0</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="1"/>
@@ -3204,20 +3226,20 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D87" s="3">
         <v>8.0</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="1"/>
@@ -3226,20 +3248,20 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D88" s="3">
         <v>11.0</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="1"/>
@@ -3248,20 +3270,20 @@
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D89" s="3">
         <v>11.0</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="1"/>
@@ -3270,20 +3292,20 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D90" s="3">
         <v>11.0</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="1"/>
@@ -3292,20 +3314,20 @@
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D91" s="3">
         <v>11.0</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="1"/>
@@ -3314,88 +3336,88 @@
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D92" s="3">
         <v>12.0</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G92" s="2"/>
       <c r="J92" s="1"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D93" s="3">
         <v>12.0</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G93" s="2"/>
       <c r="J93" s="1"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D94" s="3">
         <v>13.0</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J94" s="1"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D95" s="3">
         <v>20.0</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -3404,102 +3426,117 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D96" s="3">
         <v>9.0</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I96" s="5"/>
       <c r="J96" s="1"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D97" s="3">
         <v>15.0</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="D98" s="3">
         <v>15.0</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D99" s="3">
         <v>12.0</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D100" s="3">
         <v>12.0</v>
       </c>
       <c r="F100" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="3"/>
+      <c r="D101" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="2"/>
@@ -4512,7 +4549,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4523,104 +4560,104 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4630,12 +4667,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -4645,12 +4682,12 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="C24" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="C25" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="uyJ0StLGd6x9KECAyySpX4gHJS19vprj+5FNhw3bpdE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="U4Lr33XSQVfeNhJUeGqq+P9i0yHBaKJcmCrloycTylQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="268">
   <si>
     <t>nombre</t>
   </si>
@@ -163,33 +163,33 @@
     <t>kioto plateado 2</t>
   </si>
   <si>
+    <t>Kioto Verde Claro</t>
+  </si>
+  <si>
+    <t>kioto verde claro k.jpg</t>
+  </si>
+  <si>
+    <t>kioto verde claro 2.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Burdeos</t>
+  </si>
+  <si>
+    <t>kioto burdeos fb.jpg</t>
+  </si>
+  <si>
+    <t>Kioto Negro</t>
+  </si>
+  <si>
+    <t>kioto negro k.jpg</t>
+  </si>
+  <si>
     <t>Kioto Rosa Palo</t>
   </si>
   <si>
     <t>kioto rosa palo fb.jpg</t>
   </si>
   <si>
-    <t>Kioto Verde Claro</t>
-  </si>
-  <si>
-    <t>kioto verde claro k.jpg</t>
-  </si>
-  <si>
-    <t>kioto verde claro 2.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Burdeos</t>
-  </si>
-  <si>
-    <t>kioto burdeos fb.jpg</t>
-  </si>
-  <si>
-    <t>Kioto Negro</t>
-  </si>
-  <si>
-    <t>kioto negro k.jpg</t>
-  </si>
-  <si>
     <t>Kioto Morado</t>
   </si>
   <si>
@@ -424,6 +424,12 @@
     <t>vancouver lazo negro k.jpg</t>
   </si>
   <si>
+    <t>Vancouver Lazo Rojo</t>
+  </si>
+  <si>
+    <t>Vancouver lazo rojo</t>
+  </si>
+  <si>
     <t>Vancouver Vintage Rosa</t>
   </si>
   <si>
@@ -496,7 +502,7 @@
     <t>madrid chocolate 2.jpg</t>
   </si>
   <si>
-    <t>madrid choco k.jpg</t>
+    <t>Madrid Marron 2</t>
   </si>
   <si>
     <t>Huesca Cotton Beige</t>
@@ -715,6 +721,12 @@
     <t>3 granadas.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">Collar Granada </t>
+  </si>
+  <si>
+    <t>Granadas verano</t>
+  </si>
+  <si>
     <t>Choker Milán</t>
   </si>
   <si>
@@ -791,6 +803,12 @@
   </si>
   <si>
     <t>California turquesa</t>
+  </si>
+  <si>
+    <t>Collar California Rosa</t>
+  </si>
+  <si>
+    <t>California Rosa</t>
   </si>
   <si>
     <t>tipos</t>
@@ -956,7 +974,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J70" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J71" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="10">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -974,7 +992,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:J71" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:J72" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -992,7 +1010,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:J77" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A73:J78" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1010,7 +1028,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A78:J91" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A79:J92" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1028,7 +1046,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A92:J92" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A93:J93" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1046,7 +1064,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A93:J96" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A94:J98" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1648,7 +1666,7 @@
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D16" s="3">
@@ -1658,19 +1676,23 @@
       <c r="F16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="3">
@@ -1678,14 +1700,9 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
@@ -1706,7 +1723,9 @@
       <c r="F18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="G18" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
@@ -1727,9 +1746,8 @@
       <c r="F19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
@@ -2460,9 +2478,11 @@
         <v>122</v>
       </c>
       <c r="D52" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E52" s="2"/>
+        <v>35.0</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F52" s="2" t="s">
         <v>135</v>
       </c>
@@ -2489,7 +2509,7 @@
         <v>137</v>
       </c>
       <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
+      <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
@@ -2508,16 +2528,16 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>11</v>
@@ -2526,11 +2546,11 @@
         <v>122</v>
       </c>
       <c r="D55" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2545,14 +2565,14 @@
         <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D56" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2561,13 +2581,13 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="D57" s="3">
         <v>22.0</v>
@@ -2576,34 +2596,34 @@
       <c r="F57" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D58" s="3">
         <v>22.0</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -2614,7 +2634,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D59" s="3">
         <v>22.0</v>
@@ -2636,76 +2656,76 @@
         <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D60" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D61" s="3">
         <v>30.0</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D62" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D63" s="3">
         <v>25.0</v>
@@ -2727,7 +2747,7 @@
         <v>11</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D64" s="3">
         <v>25.0</v>
@@ -2749,7 +2769,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D65" s="3">
         <v>25.0</v>
@@ -2771,7 +2791,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3">
         <v>25.0</v>
@@ -2793,7 +2813,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D67" s="3">
         <v>25.0</v>
@@ -2815,14 +2835,14 @@
         <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D68" s="3">
         <v>25.0</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2831,22 +2851,22 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="D69" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G69" s="2"/>
+      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -2859,14 +2879,14 @@
         <v>11</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D70" s="3">
         <v>30.0</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="1"/>
@@ -2875,13 +2895,13 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="D71" s="3">
         <v>30.0</v>
@@ -2890,7 +2910,7 @@
       <c r="F71" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G71" s="1"/>
+      <c r="G71" s="2"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -2903,7 +2923,7 @@
         <v>11</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D72" s="3">
         <v>30.0</v>
@@ -2912,7 +2932,7 @@
       <c r="F72" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G72" s="2"/>
+      <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -2922,43 +2942,43 @@
         <v>184</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>185</v>
+        <v>11</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D73" s="3">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D74" s="3">
         <v>12.0</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
@@ -2967,10 +2987,10 @@
         <v>191</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D75" s="3">
         <v>12.0</v>
@@ -2989,10 +3009,10 @@
         <v>193</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D76" s="3">
         <v>12.0</v>
@@ -3011,10 +3031,10 @@
         <v>195</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D77" s="3">
         <v>12.0</v>
@@ -3033,32 +3053,32 @@
         <v>197</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D78" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G78" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="D79" s="3">
         <v>15.0</v>
@@ -3077,10 +3097,10 @@
         <v>203</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D80" s="3">
         <v>15.0</v>
@@ -3099,10 +3119,10 @@
         <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D81" s="3">
         <v>15.0</v>
@@ -3121,10 +3141,10 @@
         <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D82" s="3">
         <v>15.0</v>
@@ -3133,6 +3153,7 @@
       <c r="F82" s="2" t="s">
         <v>208</v>
       </c>
+      <c r="G82" s="2"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3142,10 +3163,10 @@
         <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D83" s="3">
         <v>15.0</v>
@@ -3163,35 +3184,34 @@
         <v>211</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D84" s="3">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G84" s="2"/>
+        <v>212</v>
+      </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="D85" s="3">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -3204,20 +3224,20 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D86" s="3">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="1"/>
@@ -3226,20 +3246,20 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="D87" s="3">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="1"/>
@@ -3248,16 +3268,16 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D88" s="3">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
@@ -3273,10 +3293,10 @@
         <v>221</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D89" s="3">
         <v>11.0</v>
@@ -3295,10 +3315,10 @@
         <v>223</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D90" s="3">
         <v>11.0</v>
@@ -3317,10 +3337,10 @@
         <v>225</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D91" s="3">
         <v>11.0</v>
@@ -3339,219 +3359,265 @@
         <v>227</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D92" s="3">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G92" s="2"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
       <c r="J92" s="1"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D93" s="3">
         <v>12.0</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G93" s="2"/>
       <c r="J93" s="1"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D94" s="3">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="A95" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="B95" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D95" s="3">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="5"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
       <c r="J95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D96" s="3">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="B97" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D97" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H96" s="2" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I96" s="5"/>
-      <c r="J96" s="1"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="s">
+      <c r="B98" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="D98" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D97" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F97" s="4" t="s">
+      <c r="G98" s="2" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="s">
+      <c r="H98" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D98" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>248</v>
-      </c>
+      <c r="I98" s="5"/>
+      <c r="J98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C99" s="2" t="s">
+      <c r="D99" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="D99" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D100" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D100" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D101" s="3">
         <v>12.0</v>
       </c>
       <c r="F101" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="3"/>
+      <c r="B102" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D102" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="103">
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="3"/>
+      <c r="A103" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D103" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="104">
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="3"/>
+      <c r="A104" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D104" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="2"/>
@@ -3588,8 +3654,16 @@
       <c r="C111" s="2"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="112">
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="3"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="3"/>
+    </row>
     <row r="114" ht="14.25" customHeight="1"/>
     <row r="115" ht="14.25" customHeight="1"/>
     <row r="116" ht="14.25" customHeight="1"/>
@@ -4511,12 +4585,14 @@
     <row r="1032" ht="14.25" customHeight="1"/>
     <row r="1033" ht="14.25" customHeight="1"/>
     <row r="1034" ht="14.25" customHeight="1"/>
+    <row r="1035" ht="14.25" customHeight="1"/>
+    <row r="1036" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C111">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C113">
       <formula1>datos!$C$2:$C$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B111">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B113">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4549,7 +4625,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4565,7 +4641,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>37</v>
@@ -4581,15 +4657,15 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>122</v>
@@ -4597,17 +4673,17 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -4617,47 +4693,47 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4667,12 +4743,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
@@ -4682,12 +4758,12 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="C24" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="C25" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="U4Lr33XSQVfeNhJUeGqq+P9i0yHBaKJcmCrloycTylQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="uyJ0StLGd6x9KECAyySpX4gHJS19vprj+5FNhw3bpdE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="263">
   <si>
     <t>nombre</t>
   </si>
@@ -64,25 +64,10 @@
     <t>tenerife primavera.jpg</t>
   </si>
   <si>
-    <t>Tenerife Marrón Bordado</t>
-  </si>
-  <si>
-    <t>tenerife bordado marron.jpg</t>
-  </si>
-  <si>
     <t>Tenerife Tie Dye</t>
   </si>
   <si>
     <t>tenerife tie die.jpg</t>
-  </si>
-  <si>
-    <t>Tenerife Pana</t>
-  </si>
-  <si>
-    <t>tenerife pana k.jpg</t>
-  </si>
-  <si>
-    <t>tenerife pana 2.jpg</t>
   </si>
   <si>
     <t>Tenerife Flores</t>
@@ -974,7 +959,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J71" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J69" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="10">
     <tableColumn name="nombre" id="1"/>
     <tableColumn name="tipo" id="2"/>
@@ -992,7 +977,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A72:J72" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A70:J70" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1010,7 +995,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A73:J78" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A71:J76" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1028,7 +1013,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A79:J92" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A77:J90" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1046,7 +1031,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A93:J93" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A91:J91" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1064,7 +1049,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A94:J98" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A92:J96" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="10">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1378,9 +1363,7 @@
       <c r="D3" s="3">
         <v>30.0</v>
       </c>
-      <c r="E3" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1407,7 +1390,7 @@
       <c r="G4" s="2"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1420,20 +1403,18 @@
       <c r="D5" s="3">
         <v>30.0</v>
       </c>
-      <c r="E5" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -1442,27 +1423,29 @@
         <v>12</v>
       </c>
       <c r="D6" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D7" s="3">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
@@ -1481,10 +1464,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3">
-        <v>25.0</v>
+        <v>38.0</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
@@ -1503,14 +1486,14 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3">
         <v>38.0</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -1519,20 +1502,20 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3">
         <v>38.0</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1541,16 +1524,16 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="D11" s="3">
-        <v>38.0</v>
+        <v>35.0</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
@@ -1562,100 +1545,103 @@
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>28</v>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D12" s="3">
-        <v>38.0</v>
+        <v>30.0</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="J12" s="1"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D13" s="3">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3">
         <v>30.0</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D15" s="3">
         <v>30.0</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
@@ -1666,8 +1652,8 @@
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>37</v>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D16" s="3">
         <v>30.0</v>
@@ -1677,129 +1663,126 @@
         <v>48</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" s="3">
         <v>30.0</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D18" s="3">
         <v>30.0</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" ht="15.0" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D19" s="3">
         <v>30.0</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="G20" s="2"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" ht="15.0" customHeight="1">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="G21" s="2"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D22" s="3">
         <v>25.0</v>
@@ -1808,331 +1791,330 @@
         <v>1.0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G22" s="2"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1.0</v>
-      </c>
+        <v>13.0</v>
+      </c>
+      <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="J23" s="1"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D24" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1.0</v>
-      </c>
+        <v>13.0</v>
+      </c>
+      <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D25" s="3">
         <v>13.0</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3">
         <v>13.0</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="G26" s="2"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3">
         <v>13.0</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="G27" s="2"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D28" s="3">
         <v>13.0</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="H29" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="J29" s="1"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>68</v>
+      <c r="A30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D30" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="E30" s="2"/>
+        <v>20.0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>82</v>
+      <c r="C31" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D31" s="3">
         <v>20.0</v>
       </c>
       <c r="E31" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>85</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>82</v>
+      <c r="A32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="D32" s="3">
         <v>20.0</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="4">
         <v>1.0</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="F32" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="G32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D33" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E33" s="2">
-        <v>2.0</v>
-      </c>
+        <v>30.0</v>
+      </c>
+      <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33" s="2"/>
+        <v>92</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D34" s="3">
         <v>20.0</v>
       </c>
-      <c r="E34" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>82</v>
+      <c r="B35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="D35" s="3">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="I35" s="2"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D36" s="3">
-        <v>20.0</v>
+        <v>35.0</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2141,26 +2123,27 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D37" s="3">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38">
       <c r="A38" s="2" t="s">
         <v>100</v>
       </c>
@@ -2168,43 +2151,41 @@
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D38" s="3">
-        <v>35.0</v>
+        <v>28.0</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D39" s="3">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
         <v>105</v>
       </c>
@@ -2212,38 +2193,39 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D40" s="3">
         <v>28.0</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D41" s="3">
         <v>28.0</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="F41" s="4" t="s">
         <v>109</v>
       </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -2254,79 +2236,80 @@
         <v>11</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3">
         <v>28.0</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D43" s="3">
         <v>28.0</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="H43" s="2"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D44" s="3">
         <v>28.0</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>116</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D45" s="3">
-        <v>28.0</v>
+        <v>45.0</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2339,10 +2322,10 @@
         <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D46" s="3">
-        <v>28.0</v>
+        <v>20.0</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
@@ -2361,14 +2344,14 @@
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D47" s="3">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -2377,90 +2360,92 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D48" s="3">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D49" s="3">
         <v>40.0</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D50" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="E50" s="2"/>
+        <v>35.0</v>
+      </c>
+      <c r="E50" s="2">
+        <v>1.0</v>
+      </c>
       <c r="F50" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G50" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D51" s="3">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="1"/>
@@ -2469,88 +2454,86 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D52" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="E52" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="G52" s="2"/>
-      <c r="H52" s="1"/>
+      <c r="H52" s="2"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D53" s="3">
         <v>25.0</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G53" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D54" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D55" s="3">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2565,36 +2548,39 @@
         <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D56" s="3">
-        <v>30.0</v>
+        <v>22.0</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+      <c r="G56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="J56" s="1"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D57" s="3">
         <v>22.0</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -2603,117 +2589,114 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D58" s="3">
         <v>22.0</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G58" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H58" s="2" t="s">
-        <v>149</v>
-      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D59" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G59" s="1"/>
+      <c r="G59" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D60" s="3">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+        <v>154</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D61" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>157</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D62" s="3">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G62" s="2" t="s">
         <v>160</v>
       </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
@@ -2725,14 +2708,14 @@
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D63" s="3">
         <v>25.0</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -2741,20 +2724,20 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D64" s="3">
         <v>25.0</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -2763,20 +2746,20 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D65" s="3">
         <v>25.0</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -2785,20 +2768,20 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D66" s="3">
         <v>25.0</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -2807,13 +2790,13 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D67" s="3">
         <v>25.0</v>
@@ -2835,16 +2818,16 @@
         <v>11</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D68" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G68" s="1"/>
+      <c r="G68" s="2"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -2860,13 +2843,13 @@
         <v>175</v>
       </c>
       <c r="D69" s="3">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G69" s="1"/>
+      <c r="G69" s="2"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
@@ -2888,7 +2871,7 @@
       <c r="F70" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G70" s="2"/>
+      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -2901,14 +2884,14 @@
         <v>11</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D71" s="3">
         <v>30.0</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="1"/>
@@ -2917,57 +2900,58 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="C72" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D72" s="3">
-        <v>30.0</v>
+        <v>12.0</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>11</v>
+        <v>182</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D73" s="3">
-        <v>30.0</v>
+        <v>12.0</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G73" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="G73" s="5"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D74" s="3">
         <v>12.0</v>
@@ -2976,28 +2960,27 @@
       <c r="F74" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="G74" s="5"/>
+      <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D75" s="3">
         <v>12.0</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="1"/>
@@ -3006,20 +2989,20 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D76" s="3">
         <v>12.0</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="1"/>
@@ -3028,64 +3011,64 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="C77" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D77" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G77" s="5"/>
+        <v>197</v>
+      </c>
+      <c r="G77" s="2"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D78" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G78" s="5"/>
+        <v>199</v>
+      </c>
+      <c r="G78" s="2"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D79" s="3">
         <v>15.0</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="1"/>
@@ -3094,20 +3077,20 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D80" s="3">
         <v>15.0</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="1"/>
@@ -3116,106 +3099,106 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D81" s="3">
         <v>15.0</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G81" s="2"/>
+        <v>205</v>
+      </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D82" s="3">
         <v>15.0</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G82" s="2"/>
+        <v>207</v>
+      </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="C83" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D83" s="3">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>210</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="G83" s="2"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D84" s="3">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>212</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G84" s="2"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D85" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="1"/>
@@ -3224,20 +3207,20 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D86" s="3">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="1"/>
@@ -3246,20 +3229,20 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D87" s="3">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="1"/>
@@ -3268,20 +3251,20 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D88" s="3">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="1"/>
@@ -3290,20 +3273,20 @@
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D89" s="3">
         <v>11.0</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="1"/>
@@ -3312,20 +3295,20 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D90" s="3">
         <v>11.0</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="1"/>
@@ -3334,198 +3317,188 @@
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="D91" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
         <v>226</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
       <c r="J91" s="1"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D92" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
       <c r="J92" s="1"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D93" s="3">
         <v>12.0</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G93" s="2"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
       <c r="J93" s="1"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D94" s="3">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G94" s="2"/>
+      <c r="G94" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>235</v>
+      </c>
       <c r="J94" s="1"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95">
       <c r="A95" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D95" s="3">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="5"/>
       <c r="J95" s="1"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96">
       <c r="A96" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D96" s="3">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>240</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I96" s="5"/>
       <c r="J96" s="1"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="s">
-        <v>241</v>
+      <c r="A97" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>200</v>
+        <v>62</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D97" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="1"/>
+        <v>15.0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="s">
-        <v>243</v>
+      <c r="A98" s="4" t="s">
+        <v>246</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>200</v>
+        <v>62</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D98" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="H98" s="2" t="s">
+        <v>15.0</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="I98" s="5"/>
-      <c r="J98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
         <v>248</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>249</v>
       </c>
       <c r="D99" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>250</v>
@@ -3536,27 +3509,30 @@
         <v>251</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>249</v>
       </c>
       <c r="D100" s="3">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>252</v>
       </c>
+      <c r="G100" s="4" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D101" s="3">
         <v>12.0</v>
@@ -3570,10 +3546,10 @@
         <v>256</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D102" s="3">
         <v>12.0</v>
@@ -3581,43 +3557,16 @@
       <c r="F102" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="G102" s="4" t="s">
-        <v>258</v>
-      </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D103" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>260</v>
-      </c>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="3"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D104" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>262</v>
-      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="3"/>
     </row>
     <row r="105">
       <c r="B105" s="2"/>
@@ -3654,16 +3603,8 @@
       <c r="C111" s="2"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112">
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="3"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="3"/>
-    </row>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
     <row r="114" ht="14.25" customHeight="1"/>
     <row r="115" ht="14.25" customHeight="1"/>
     <row r="116" ht="14.25" customHeight="1"/>
@@ -4585,14 +4526,12 @@
     <row r="1032" ht="14.25" customHeight="1"/>
     <row r="1033" ht="14.25" customHeight="1"/>
     <row r="1034" ht="14.25" customHeight="1"/>
-    <row r="1035" ht="14.25" customHeight="1"/>
-    <row r="1036" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C113">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C111">
       <formula1>datos!$C$2:$C$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B113">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B111">
       <formula1>datos!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4625,7 +4564,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4636,104 +4575,104 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="C7" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="C9" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="C10" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="C12" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="C13" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="C14" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="C15" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="C16" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="C17" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="C18" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="C19" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -4743,27 +4682,27 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="C21" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="C22" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="C23" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="C24" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="C25" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1"/>
